--- a/11.xlsx
+++ b/11.xlsx
@@ -4,16 +4,16 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255" firstSheet="2"/>
+    <workbookView windowWidth="28800" windowHeight="12255" firstSheet="2" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="存款限量" sheetId="10" r:id="rId2"/>
-    <sheet name="Sheet2" sheetId="16" r:id="rId3"/>
+    <sheet name="Sheet2" sheetId="17" r:id="rId3"/>
     <sheet name="Sheet3" sheetId="6" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Sheet2!$B$1:$O$74</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Sheet2!$B$1:$S$74</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,6 +40,72 @@
   </authors>
   <commentList>
     <comment ref="H1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>余泽鑫:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+（存款价格）低于当前定价以存款价格为准 高于当前定价则以当前定价为准</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>余泽鑫:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+（存款价格）低于当前定价以存款价格为准 高于当前定价则以当前定价为准</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>余泽鑫:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+（存款价格）低于当前定价以存款价格为准 高于当前定价则以当前定价为准</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -280,7 +346,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="166">
   <si>
     <t>客户名称</t>
   </si>
@@ -504,13 +570,43 @@
     <t>BDM</t>
   </si>
   <si>
+    <t>DP</t>
+  </si>
+  <si>
+    <t>FJ2</t>
+  </si>
+  <si>
+    <t>SRD</t>
+  </si>
+  <si>
+    <t>SAD</t>
+  </si>
+  <si>
+    <t>PPC</t>
+  </si>
+  <si>
+    <t>TCML</t>
+  </si>
+  <si>
+    <t>KEP</t>
+  </si>
+  <si>
+    <t>JJMI</t>
+  </si>
+  <si>
+    <t>HMI税</t>
+  </si>
+  <si>
+    <t>DWN</t>
+  </si>
+  <si>
+    <t>CD</t>
+  </si>
+  <si>
+    <t>BIG</t>
+  </si>
+  <si>
     <t>TM</t>
-  </si>
-  <si>
-    <t>TH</t>
-  </si>
-  <si>
-    <t>DP</t>
   </si>
   <si>
     <r>
@@ -554,9 +650,6 @@
     <t>JH/YS</t>
   </si>
   <si>
-    <t>BIG</t>
-  </si>
-  <si>
     <t>4000-8000</t>
   </si>
   <si>
@@ -626,15 +719,9 @@
     <t>LY/JI</t>
   </si>
   <si>
-    <t>CD</t>
-  </si>
-  <si>
     <t>500以下</t>
   </si>
   <si>
-    <t>KEP</t>
-  </si>
-  <si>
     <t>1月3账户存款用完后价格如下</t>
   </si>
   <si>
@@ -653,6 +740,18 @@
     <t>2月23日起价格</t>
   </si>
   <si>
+    <t>3月2日起价格</t>
+  </si>
+  <si>
+    <t>3月9日起价格</t>
+  </si>
+  <si>
+    <t>4月3日起价格</t>
+  </si>
+  <si>
+    <t>4月8日起价格</t>
+  </si>
+  <si>
     <t>4月15日起价格</t>
   </si>
   <si>
@@ -743,12 +842,12 @@
     <t>ZZ</t>
   </si>
   <si>
+    <t>PPN</t>
+  </si>
+  <si>
     <t>PDS</t>
   </si>
   <si>
-    <t>PPC</t>
-  </si>
-  <si>
     <t>TPM</t>
   </si>
   <si>
@@ -762,12 +861,6 @@
   </si>
   <si>
     <t>APW</t>
-  </si>
-  <si>
-    <t>SAD</t>
-  </si>
-  <si>
-    <t>SRD</t>
   </si>
 </sst>
 </file>
@@ -1046,13 +1139,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE6E4E4"/>
+        <fgColor theme="6" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFBDD7EE"/>
+        <fgColor rgb="FFE6E4E4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1532,7 +1625,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1575,13 +1668,16 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
@@ -1603,28 +1699,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="2" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="176" fontId="10" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1636,16 +1720,22 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="2" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="10" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1959,41 +2049,42 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AC46"/>
+  <dimension ref="A1:AJ56"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="7.875" style="23" customWidth="1"/>
-    <col min="2" max="2" width="12.625" style="23" customWidth="1"/>
-    <col min="3" max="3" width="7.875" style="23" customWidth="1"/>
-    <col min="4" max="5" width="9.75" style="23" customWidth="1"/>
-    <col min="6" max="6" width="10.125" style="23" customWidth="1"/>
-    <col min="7" max="7" width="8.75" style="23" customWidth="1"/>
-    <col min="8" max="8" width="12.375" style="23" customWidth="1"/>
-    <col min="9" max="9" width="10.125" style="23" customWidth="1"/>
-    <col min="10" max="10" width="8.75" style="23" customWidth="1"/>
-    <col min="11" max="11" width="12.375" style="23" customWidth="1"/>
-    <col min="12" max="12" width="10.125" style="23" customWidth="1"/>
-    <col min="13" max="13" width="8.75" style="23" customWidth="1"/>
-    <col min="14" max="14" width="12.375" style="23" customWidth="1"/>
-    <col min="15" max="15" width="10.125" style="23" customWidth="1"/>
-    <col min="16" max="16" width="8.75" style="23" customWidth="1"/>
-    <col min="17" max="17" width="12.375" style="23" customWidth="1"/>
-    <col min="18" max="18" width="10.125" style="23" customWidth="1"/>
-    <col min="19" max="19" width="8.75" style="23" customWidth="1"/>
-    <col min="20" max="20" width="12.375" style="23" customWidth="1"/>
-    <col min="21" max="21" width="10.125" style="23" customWidth="1"/>
-    <col min="22" max="22" width="8.75" style="23" customWidth="1"/>
-    <col min="23" max="23" width="13.5" style="23" customWidth="1"/>
-    <col min="24" max="24" width="10.125" style="23" customWidth="1"/>
-    <col min="25" max="25" width="8.75" style="23" customWidth="1"/>
-    <col min="26" max="26" width="7.25" style="23" customWidth="1"/>
-    <col min="27" max="27" width="10.125" style="23" customWidth="1"/>
-    <col min="28" max="28" width="7.375" style="23" customWidth="1"/>
-    <col min="29" max="29" width="8.375" style="23" customWidth="1"/>
-    <col min="30" max="16384" width="9" style="23"/>
+    <col min="1" max="1" width="7.875" style="24" customWidth="1"/>
+    <col min="2" max="2" width="12.625" style="24" customWidth="1"/>
+    <col min="3" max="3" width="7.875" style="24" customWidth="1"/>
+    <col min="4" max="5" width="9.75" style="24" customWidth="1"/>
+    <col min="6" max="6" width="10.125" style="24" customWidth="1"/>
+    <col min="7" max="7" width="8.75" style="25" customWidth="1"/>
+    <col min="8" max="8" width="12.375" style="25" customWidth="1"/>
+    <col min="9" max="9" width="11.25" style="25" customWidth="1"/>
+    <col min="10" max="10" width="12.125" style="25" customWidth="1"/>
+    <col min="11" max="11" width="13.5" style="25" customWidth="1"/>
+    <col min="12" max="12" width="11.25" style="25" customWidth="1"/>
+    <col min="13" max="13" width="8.75" style="25" customWidth="1"/>
+    <col min="14" max="14" width="12.375" style="25" customWidth="1"/>
+    <col min="15" max="15" width="11.25" style="25" customWidth="1"/>
+    <col min="16" max="16" width="8.75" style="25" customWidth="1"/>
+    <col min="17" max="17" width="12.375" style="25" customWidth="1"/>
+    <col min="18" max="18" width="11.25" style="25" customWidth="1"/>
+    <col min="19" max="19" width="8.75" style="25" customWidth="1"/>
+    <col min="20" max="20" width="13.5" style="25" customWidth="1"/>
+    <col min="21" max="21" width="11.25" style="25" customWidth="1"/>
+    <col min="22" max="22" width="8.75" style="25" customWidth="1"/>
+    <col min="23" max="23" width="12.375" style="25" customWidth="1"/>
+    <col min="24" max="24" width="11.25" style="25" customWidth="1"/>
+    <col min="25" max="25" width="8.75" style="25" customWidth="1"/>
+    <col min="26" max="26" width="12.375" style="25" customWidth="1"/>
+    <col min="27" max="27" width="11.25" style="25" customWidth="1"/>
+    <col min="28" max="28" width="8.75" style="25" customWidth="1"/>
+    <col min="29" max="29" width="10.125" style="25" customWidth="1"/>
+    <col min="30" max="36" width="9" style="25"/>
+    <col min="37" max="16384" width="9" style="24"/>
   </cols>
   <sheetData>
-    <row r="1" s="23" customFormat="1" ht="22" customHeight="1" spans="1:29">
+    <row r="1" s="24" customFormat="1" ht="22" customHeight="1" spans="1:36">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2012,77 +2103,84 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="X1" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Y1" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="Z1" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="24" t="s">
+      <c r="AA1" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="24" t="s">
+      <c r="AB1" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="24" t="s">
+      <c r="AC1" s="26" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="2" s="23" customFormat="1" ht="16.5" spans="1:29">
+      <c r="AD1" s="25"/>
+      <c r="AE1" s="25"/>
+      <c r="AF1" s="25"/>
+      <c r="AG1" s="25"/>
+      <c r="AH1" s="25"/>
+      <c r="AI1" s="25"/>
+      <c r="AJ1" s="25"/>
+    </row>
+    <row r="2" s="24" customFormat="1" ht="16.5" spans="1:36">
       <c r="A2" s="2" t="s">
         <v>29</v>
       </c>
@@ -2095,55 +2193,62 @@
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="5"/>
-      <c r="G2" s="25">
+      <c r="G2" s="27">
         <v>455000</v>
       </c>
-      <c r="H2" s="25">
+      <c r="H2" s="27">
         <v>0</v>
       </c>
       <c r="I2" s="5"/>
-      <c r="J2" s="25">
+      <c r="J2" s="27">
         <v>465000</v>
       </c>
-      <c r="K2" s="25">
+      <c r="K2" s="27">
         <v>0</v>
       </c>
       <c r="L2" s="5"/>
-      <c r="M2" s="25">
+      <c r="M2" s="27">
         <v>485000</v>
       </c>
-      <c r="N2" s="25">
+      <c r="N2" s="27">
         <v>0</v>
       </c>
       <c r="O2" s="5"/>
-      <c r="P2" s="25">
+      <c r="P2" s="27">
         <v>495000</v>
       </c>
-      <c r="Q2" s="25">
+      <c r="Q2" s="27">
         <v>0</v>
       </c>
       <c r="R2" s="5"/>
-      <c r="S2" s="25">
+      <c r="S2" s="27">
         <v>515000</v>
       </c>
-      <c r="T2" s="25">
+      <c r="T2" s="27">
         <v>0</v>
       </c>
       <c r="U2" s="5"/>
-      <c r="V2" s="25">
+      <c r="V2" s="27">
         <v>525000</v>
       </c>
-      <c r="W2" s="25">
+      <c r="W2" s="27">
         <v>111963402.5</v>
       </c>
       <c r="X2" s="5"/>
-      <c r="Y2" s="25"/>
-      <c r="Z2" s="25"/>
-      <c r="AA2" s="26"/>
+      <c r="Y2" s="27"/>
+      <c r="Z2" s="27"/>
+      <c r="AA2" s="5"/>
       <c r="AB2" s="27"/>
       <c r="AC2" s="27"/>
-    </row>
-    <row r="3" s="23" customFormat="1" ht="16.5" spans="1:29">
+      <c r="AD2" s="25"/>
+      <c r="AE2" s="25"/>
+      <c r="AF2" s="25"/>
+      <c r="AG2" s="25"/>
+      <c r="AH2" s="25"/>
+      <c r="AI2" s="25"/>
+      <c r="AJ2" s="25"/>
+    </row>
+    <row r="3" s="24" customFormat="1" ht="16.5" spans="1:36">
       <c r="A3" s="2" t="s">
         <v>31</v>
       </c>
@@ -2158,43 +2263,50 @@
       </c>
       <c r="E3" s="3"/>
       <c r="F3" s="5"/>
-      <c r="G3" s="25">
+      <c r="G3" s="27">
         <v>430000</v>
       </c>
-      <c r="H3" s="25">
+      <c r="H3" s="27">
         <v>0</v>
       </c>
       <c r="I3" s="5"/>
-      <c r="J3" s="25">
+      <c r="J3" s="27">
         <v>460000</v>
       </c>
-      <c r="K3" s="25">
+      <c r="K3" s="27">
         <v>0</v>
       </c>
       <c r="L3" s="5"/>
-      <c r="M3" s="25">
+      <c r="M3" s="27">
         <v>490000</v>
       </c>
       <c r="N3" s="28">
-        <v>-19051863.75</v>
+        <v>-45619863.75</v>
       </c>
       <c r="O3" s="5"/>
-      <c r="P3" s="25"/>
-      <c r="Q3" s="25"/>
+      <c r="P3" s="27"/>
+      <c r="Q3" s="27"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="25"/>
-      <c r="T3" s="25"/>
+      <c r="S3" s="27"/>
+      <c r="T3" s="27"/>
       <c r="U3" s="5"/>
-      <c r="V3" s="25"/>
-      <c r="W3" s="25"/>
+      <c r="V3" s="27"/>
+      <c r="W3" s="27"/>
       <c r="X3" s="5"/>
-      <c r="Y3" s="25"/>
-      <c r="Z3" s="25"/>
-      <c r="AA3" s="26"/>
+      <c r="Y3" s="27"/>
+      <c r="Z3" s="27"/>
+      <c r="AA3" s="5"/>
       <c r="AB3" s="27"/>
       <c r="AC3" s="27"/>
-    </row>
-    <row r="4" s="23" customFormat="1" ht="16.5" spans="1:29">
+      <c r="AD3" s="25"/>
+      <c r="AE3" s="25"/>
+      <c r="AF3" s="25"/>
+      <c r="AG3" s="25"/>
+      <c r="AH3" s="25"/>
+      <c r="AI3" s="25"/>
+      <c r="AJ3" s="25"/>
+    </row>
+    <row r="4" s="24" customFormat="1" ht="16.5" spans="1:36">
       <c r="A4" s="2" t="s">
         <v>32</v>
       </c>
@@ -2207,35 +2319,42 @@
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
       <c r="F4" s="5"/>
-      <c r="G4" s="25">
+      <c r="G4" s="27">
         <v>450000</v>
       </c>
-      <c r="H4" s="25">
+      <c r="H4" s="27">
         <v>51577120</v>
       </c>
       <c r="I4" s="5"/>
-      <c r="J4" s="25"/>
-      <c r="K4" s="25"/>
+      <c r="J4" s="27"/>
+      <c r="K4" s="27"/>
       <c r="L4" s="5"/>
-      <c r="M4" s="25"/>
-      <c r="N4" s="25"/>
+      <c r="M4" s="27"/>
+      <c r="N4" s="27"/>
       <c r="O4" s="5"/>
-      <c r="P4" s="25"/>
-      <c r="Q4" s="25"/>
+      <c r="P4" s="27"/>
+      <c r="Q4" s="27"/>
       <c r="R4" s="5"/>
-      <c r="S4" s="25"/>
-      <c r="T4" s="25"/>
+      <c r="S4" s="27"/>
+      <c r="T4" s="27"/>
       <c r="U4" s="5"/>
-      <c r="V4" s="25"/>
-      <c r="W4" s="25"/>
+      <c r="V4" s="27"/>
+      <c r="W4" s="27"/>
       <c r="X4" s="5"/>
-      <c r="Y4" s="25"/>
-      <c r="Z4" s="25"/>
-      <c r="AA4" s="26"/>
+      <c r="Y4" s="27"/>
+      <c r="Z4" s="27"/>
+      <c r="AA4" s="5"/>
       <c r="AB4" s="27"/>
       <c r="AC4" s="27"/>
-    </row>
-    <row r="5" s="23" customFormat="1" ht="16.5" spans="1:29">
+      <c r="AD4" s="25"/>
+      <c r="AE4" s="25"/>
+      <c r="AF4" s="25"/>
+      <c r="AG4" s="25"/>
+      <c r="AH4" s="25"/>
+      <c r="AI4" s="25"/>
+      <c r="AJ4" s="25"/>
+    </row>
+    <row r="5" s="24" customFormat="1" ht="16.5" spans="1:36">
       <c r="A5" s="2" t="s">
         <v>33</v>
       </c>
@@ -2252,55 +2371,66 @@
         <v>170000</v>
       </c>
       <c r="F5" s="5"/>
-      <c r="G5" s="25">
+      <c r="G5" s="27">
         <v>440000</v>
       </c>
-      <c r="H5" s="25">
+      <c r="H5" s="27">
         <v>0</v>
       </c>
       <c r="I5" s="5"/>
-      <c r="J5" s="25">
+      <c r="J5" s="27">
         <v>450000</v>
       </c>
-      <c r="K5" s="25">
+      <c r="K5" s="27">
         <v>0</v>
       </c>
       <c r="L5" s="5"/>
-      <c r="M5" s="25">
+      <c r="M5" s="27">
         <v>470000</v>
       </c>
-      <c r="N5" s="25">
+      <c r="N5" s="27">
         <v>0</v>
       </c>
       <c r="O5" s="5"/>
-      <c r="P5" s="25">
+      <c r="P5" s="27">
         <v>500000</v>
       </c>
-      <c r="Q5" s="25">
+      <c r="Q5" s="27">
         <v>0</v>
       </c>
       <c r="R5" s="5"/>
-      <c r="S5" s="25">
+      <c r="S5" s="27">
         <v>510000</v>
       </c>
-      <c r="T5" s="25">
+      <c r="T5" s="27">
         <v>0</v>
       </c>
       <c r="U5" s="5"/>
-      <c r="V5" s="25">
+      <c r="V5" s="27">
         <v>520000</v>
       </c>
-      <c r="W5" s="28">
-        <v>-167603864.46</v>
+      <c r="W5" s="27">
+        <v>0</v>
       </c>
       <c r="X5" s="5"/>
-      <c r="Y5" s="25"/>
-      <c r="Z5" s="25"/>
-      <c r="AA5" s="26"/>
+      <c r="Y5" s="27">
+        <v>510000</v>
+      </c>
+      <c r="Z5" s="28">
+        <v>-67603864.46</v>
+      </c>
+      <c r="AA5" s="5"/>
       <c r="AB5" s="27"/>
       <c r="AC5" s="27"/>
-    </row>
-    <row r="6" s="23" customFormat="1" ht="16.5" spans="1:29">
+      <c r="AD5" s="25"/>
+      <c r="AE5" s="25"/>
+      <c r="AF5" s="25"/>
+      <c r="AG5" s="25"/>
+      <c r="AH5" s="25"/>
+      <c r="AI5" s="25"/>
+      <c r="AJ5" s="25"/>
+    </row>
+    <row r="6" s="24" customFormat="1" ht="16.5" spans="1:36">
       <c r="A6" s="2" t="s">
         <v>34</v>
       </c>
@@ -2313,39 +2443,46 @@
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
       <c r="F6" s="5"/>
-      <c r="G6" s="25">
+      <c r="G6" s="27">
         <v>460000</v>
       </c>
-      <c r="H6" s="25">
+      <c r="H6" s="27">
         <v>0</v>
       </c>
       <c r="I6" s="5"/>
-      <c r="J6" s="25">
+      <c r="J6" s="27">
         <v>520000</v>
       </c>
-      <c r="K6" s="25">
+      <c r="K6" s="27">
         <v>321676136.2</v>
       </c>
       <c r="L6" s="5"/>
-      <c r="M6" s="25"/>
-      <c r="N6" s="25"/>
+      <c r="M6" s="27"/>
+      <c r="N6" s="27"/>
       <c r="O6" s="5"/>
-      <c r="P6" s="25"/>
-      <c r="Q6" s="25"/>
+      <c r="P6" s="27"/>
+      <c r="Q6" s="27"/>
       <c r="R6" s="5"/>
-      <c r="S6" s="25"/>
-      <c r="T6" s="25"/>
+      <c r="S6" s="27"/>
+      <c r="T6" s="27"/>
       <c r="U6" s="5"/>
-      <c r="V6" s="25"/>
-      <c r="W6" s="25"/>
+      <c r="V6" s="27"/>
+      <c r="W6" s="27"/>
       <c r="X6" s="5"/>
-      <c r="Y6" s="25"/>
-      <c r="Z6" s="25"/>
-      <c r="AA6" s="26"/>
+      <c r="Y6" s="27"/>
+      <c r="Z6" s="27"/>
+      <c r="AA6" s="5"/>
       <c r="AB6" s="27"/>
       <c r="AC6" s="27"/>
-    </row>
-    <row r="7" s="23" customFormat="1" ht="16.5" spans="1:29">
+      <c r="AD6" s="25"/>
+      <c r="AE6" s="25"/>
+      <c r="AF6" s="25"/>
+      <c r="AG6" s="25"/>
+      <c r="AH6" s="25"/>
+      <c r="AI6" s="25"/>
+      <c r="AJ6" s="25"/>
+    </row>
+    <row r="7" s="24" customFormat="1" ht="16.5" spans="1:36">
       <c r="A7" s="2" t="s">
         <v>35</v>
       </c>
@@ -2358,47 +2495,58 @@
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
       <c r="F7" s="5"/>
-      <c r="G7" s="25">
+      <c r="G7" s="27">
         <v>450000</v>
       </c>
-      <c r="H7" s="25">
+      <c r="H7" s="27">
         <v>0</v>
       </c>
       <c r="I7" s="5"/>
-      <c r="J7" s="25">
+      <c r="J7" s="27">
         <v>460000</v>
       </c>
-      <c r="K7" s="25">
+      <c r="K7" s="27">
         <v>0</v>
       </c>
       <c r="L7" s="5"/>
-      <c r="M7" s="25">
+      <c r="M7" s="27">
         <v>480000</v>
       </c>
-      <c r="N7" s="25">
+      <c r="N7" s="27">
         <v>0</v>
       </c>
       <c r="O7" s="5"/>
-      <c r="P7" s="25">
+      <c r="P7" s="27">
         <v>520000</v>
       </c>
-      <c r="Q7" s="25">
-        <v>2062316</v>
+      <c r="Q7" s="27">
+        <v>0</v>
       </c>
       <c r="R7" s="5"/>
-      <c r="S7" s="25"/>
-      <c r="T7" s="25"/>
+      <c r="S7" s="27">
+        <v>520000</v>
+      </c>
+      <c r="T7" s="27">
+        <v>2566316</v>
+      </c>
       <c r="U7" s="5"/>
-      <c r="V7" s="25"/>
-      <c r="W7" s="25"/>
+      <c r="V7" s="27"/>
+      <c r="W7" s="27"/>
       <c r="X7" s="5"/>
-      <c r="Y7" s="25"/>
-      <c r="Z7" s="25"/>
-      <c r="AA7" s="26"/>
+      <c r="Y7" s="27"/>
+      <c r="Z7" s="27"/>
+      <c r="AA7" s="5"/>
       <c r="AB7" s="27"/>
       <c r="AC7" s="27"/>
-    </row>
-    <row r="8" s="23" customFormat="1" ht="16.5" spans="1:29">
+      <c r="AD7" s="25"/>
+      <c r="AE7" s="25"/>
+      <c r="AF7" s="25"/>
+      <c r="AG7" s="25"/>
+      <c r="AH7" s="25"/>
+      <c r="AI7" s="25"/>
+      <c r="AJ7" s="25"/>
+    </row>
+    <row r="8" s="24" customFormat="1" ht="16.5" spans="1:36">
       <c r="A8" s="2" t="s">
         <v>36</v>
       </c>
@@ -2413,43 +2561,50 @@
         <v>200000</v>
       </c>
       <c r="F8" s="5"/>
-      <c r="G8" s="25">
+      <c r="G8" s="27">
         <v>430000</v>
       </c>
-      <c r="H8" s="25">
+      <c r="H8" s="27">
         <v>0</v>
       </c>
       <c r="I8" s="5"/>
-      <c r="J8" s="25">
+      <c r="J8" s="27">
         <v>440000</v>
       </c>
-      <c r="K8" s="25">
+      <c r="K8" s="27">
         <v>0</v>
       </c>
       <c r="L8" s="5"/>
-      <c r="M8" s="25">
+      <c r="M8" s="27">
         <v>460000</v>
       </c>
-      <c r="N8" s="25">
+      <c r="N8" s="27">
         <v>187959990.62</v>
       </c>
       <c r="O8" s="5"/>
-      <c r="P8" s="25"/>
-      <c r="Q8" s="25"/>
+      <c r="P8" s="27"/>
+      <c r="Q8" s="27"/>
       <c r="R8" s="5"/>
-      <c r="S8" s="25"/>
-      <c r="T8" s="25"/>
+      <c r="S8" s="27"/>
+      <c r="T8" s="27"/>
       <c r="U8" s="5"/>
-      <c r="V8" s="25"/>
-      <c r="W8" s="25"/>
+      <c r="V8" s="27"/>
+      <c r="W8" s="27"/>
       <c r="X8" s="5"/>
-      <c r="Y8" s="25"/>
-      <c r="Z8" s="25"/>
-      <c r="AA8" s="26"/>
+      <c r="Y8" s="27"/>
+      <c r="Z8" s="27"/>
+      <c r="AA8" s="5"/>
       <c r="AB8" s="27"/>
       <c r="AC8" s="27"/>
-    </row>
-    <row r="9" s="23" customFormat="1" ht="16.5" spans="1:29">
+      <c r="AD8" s="25"/>
+      <c r="AE8" s="25"/>
+      <c r="AF8" s="25"/>
+      <c r="AG8" s="25"/>
+      <c r="AH8" s="25"/>
+      <c r="AI8" s="25"/>
+      <c r="AJ8" s="25"/>
+    </row>
+    <row r="9" s="24" customFormat="1" ht="16.5" spans="1:36">
       <c r="A9" s="2" t="s">
         <v>37</v>
       </c>
@@ -2462,47 +2617,54 @@
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
       <c r="F9" s="5"/>
-      <c r="G9" s="25">
+      <c r="G9" s="27">
         <v>450000</v>
       </c>
-      <c r="H9" s="25">
+      <c r="H9" s="27">
         <v>0</v>
       </c>
       <c r="I9" s="5"/>
-      <c r="J9" s="25">
+      <c r="J9" s="27">
         <v>480000</v>
       </c>
-      <c r="K9" s="25">
+      <c r="K9" s="27">
         <v>0</v>
       </c>
       <c r="L9" s="5"/>
-      <c r="M9" s="25">
+      <c r="M9" s="27">
         <v>500000</v>
       </c>
-      <c r="N9" s="25">
+      <c r="N9" s="27">
         <v>0</v>
       </c>
       <c r="O9" s="5"/>
-      <c r="P9" s="25">
+      <c r="P9" s="27">
         <v>510000</v>
       </c>
-      <c r="Q9" s="25">
-        <v>100530160</v>
+      <c r="Q9" s="27">
+        <v>76294960</v>
       </c>
       <c r="R9" s="5"/>
-      <c r="S9" s="25"/>
-      <c r="T9" s="25"/>
+      <c r="S9" s="27"/>
+      <c r="T9" s="27"/>
       <c r="U9" s="5"/>
-      <c r="V9" s="25"/>
-      <c r="W9" s="25"/>
+      <c r="V9" s="27"/>
+      <c r="W9" s="27"/>
       <c r="X9" s="5"/>
-      <c r="Y9" s="25"/>
-      <c r="Z9" s="25"/>
-      <c r="AA9" s="26"/>
+      <c r="Y9" s="27"/>
+      <c r="Z9" s="27"/>
+      <c r="AA9" s="5"/>
       <c r="AB9" s="27"/>
       <c r="AC9" s="27"/>
-    </row>
-    <row r="10" s="23" customFormat="1" ht="16.5" spans="1:29">
+      <c r="AD9" s="25"/>
+      <c r="AE9" s="25"/>
+      <c r="AF9" s="25"/>
+      <c r="AG9" s="25"/>
+      <c r="AH9" s="25"/>
+      <c r="AI9" s="25"/>
+      <c r="AJ9" s="25"/>
+    </row>
+    <row r="10" s="24" customFormat="1" ht="16.5" spans="1:36">
       <c r="A10" s="2" t="s">
         <v>38</v>
       </c>
@@ -2515,43 +2677,50 @@
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
       <c r="F10" s="5"/>
-      <c r="G10" s="25">
+      <c r="G10" s="27">
         <v>430000</v>
       </c>
-      <c r="H10" s="25">
+      <c r="H10" s="27">
         <v>9672860</v>
       </c>
       <c r="I10" s="5"/>
-      <c r="J10" s="25">
+      <c r="J10" s="27">
         <v>460000</v>
       </c>
-      <c r="K10" s="25">
+      <c r="K10" s="27">
         <v>500000000</v>
       </c>
       <c r="L10" s="5"/>
-      <c r="M10" s="25">
+      <c r="M10" s="27">
         <v>490000</v>
       </c>
-      <c r="N10" s="25">
+      <c r="N10" s="27">
         <v>300000000</v>
       </c>
       <c r="O10" s="5"/>
-      <c r="P10" s="25"/>
-      <c r="Q10" s="25"/>
+      <c r="P10" s="27"/>
+      <c r="Q10" s="27"/>
       <c r="R10" s="5"/>
-      <c r="S10" s="25"/>
-      <c r="T10" s="25"/>
+      <c r="S10" s="27"/>
+      <c r="T10" s="27"/>
       <c r="U10" s="5"/>
-      <c r="V10" s="25"/>
-      <c r="W10" s="25"/>
+      <c r="V10" s="27"/>
+      <c r="W10" s="27"/>
       <c r="X10" s="5"/>
-      <c r="Y10" s="25"/>
-      <c r="Z10" s="25"/>
-      <c r="AA10" s="26"/>
+      <c r="Y10" s="27"/>
+      <c r="Z10" s="27"/>
+      <c r="AA10" s="5"/>
       <c r="AB10" s="27"/>
       <c r="AC10" s="27"/>
-    </row>
-    <row r="11" s="23" customFormat="1" ht="16.5" spans="1:29">
+      <c r="AD10" s="25"/>
+      <c r="AE10" s="25"/>
+      <c r="AF10" s="25"/>
+      <c r="AG10" s="25"/>
+      <c r="AH10" s="25"/>
+      <c r="AI10" s="25"/>
+      <c r="AJ10" s="25"/>
+    </row>
+    <row r="11" s="24" customFormat="1" ht="16.5" spans="1:36">
       <c r="A11" s="2" t="s">
         <v>39</v>
       </c>
@@ -2564,51 +2733,58 @@
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
       <c r="F11" s="5"/>
-      <c r="G11" s="25">
+      <c r="G11" s="27">
         <v>410000</v>
       </c>
-      <c r="H11" s="25">
+      <c r="H11" s="27">
         <v>0</v>
       </c>
       <c r="I11" s="5"/>
-      <c r="J11" s="25">
+      <c r="J11" s="27">
         <v>425000</v>
       </c>
-      <c r="K11" s="25">
+      <c r="K11" s="27">
         <v>0</v>
       </c>
       <c r="L11" s="5"/>
-      <c r="M11" s="25">
+      <c r="M11" s="27">
         <v>430000</v>
       </c>
-      <c r="N11" s="25">
+      <c r="N11" s="27">
         <v>0</v>
       </c>
       <c r="O11" s="5"/>
-      <c r="P11" s="25">
+      <c r="P11" s="27">
         <v>500000</v>
       </c>
-      <c r="Q11" s="25">
-        <v>257732623</v>
+      <c r="Q11" s="27">
+        <v>251702623</v>
       </c>
       <c r="R11" s="5"/>
-      <c r="S11" s="25">
+      <c r="S11" s="27">
         <v>500000</v>
       </c>
-      <c r="T11" s="25">
+      <c r="T11" s="27">
         <v>300000000</v>
       </c>
       <c r="U11" s="5"/>
-      <c r="V11" s="25"/>
-      <c r="W11" s="25"/>
+      <c r="V11" s="27"/>
+      <c r="W11" s="27"/>
       <c r="X11" s="5"/>
-      <c r="Y11" s="25"/>
-      <c r="Z11" s="25"/>
-      <c r="AA11" s="26"/>
+      <c r="Y11" s="27"/>
+      <c r="Z11" s="27"/>
+      <c r="AA11" s="5"/>
       <c r="AB11" s="27"/>
       <c r="AC11" s="27"/>
-    </row>
-    <row r="12" s="23" customFormat="1" ht="16.5" spans="1:29">
+      <c r="AD11" s="25"/>
+      <c r="AE11" s="25"/>
+      <c r="AF11" s="25"/>
+      <c r="AG11" s="25"/>
+      <c r="AH11" s="25"/>
+      <c r="AI11" s="25"/>
+      <c r="AJ11" s="25"/>
+    </row>
+    <row r="12" s="24" customFormat="1" ht="16.5" spans="1:36">
       <c r="A12" s="2" t="s">
         <v>40</v>
       </c>
@@ -2621,51 +2797,62 @@
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
       <c r="F12" s="5"/>
-      <c r="G12" s="25">
+      <c r="G12" s="27">
         <v>440000</v>
       </c>
-      <c r="H12" s="25">
+      <c r="H12" s="27">
         <v>0</v>
       </c>
       <c r="I12" s="5"/>
-      <c r="J12" s="25">
+      <c r="J12" s="27">
         <v>450000</v>
       </c>
-      <c r="K12" s="25">
+      <c r="K12" s="27">
         <v>0</v>
       </c>
       <c r="L12" s="5"/>
-      <c r="M12" s="25">
+      <c r="M12" s="27">
         <v>470000</v>
       </c>
-      <c r="N12" s="25">
+      <c r="N12" s="27">
         <v>0</v>
       </c>
       <c r="O12" s="5"/>
-      <c r="P12" s="25">
+      <c r="P12" s="27">
         <v>500000</v>
       </c>
-      <c r="Q12" s="25">
+      <c r="Q12" s="27">
         <v>0</v>
       </c>
       <c r="R12" s="5"/>
-      <c r="S12" s="25">
+      <c r="S12" s="27">
         <v>520000</v>
       </c>
-      <c r="T12" s="28">
-        <v>-19457190</v>
+      <c r="T12" s="27">
+        <v>0</v>
       </c>
       <c r="U12" s="5"/>
-      <c r="V12" s="25"/>
-      <c r="W12" s="25"/>
+      <c r="V12" s="27">
+        <v>510000</v>
+      </c>
+      <c r="W12" s="27">
+        <v>92371210</v>
+      </c>
       <c r="X12" s="5"/>
-      <c r="Y12" s="25"/>
-      <c r="Z12" s="25"/>
-      <c r="AA12" s="26"/>
+      <c r="Y12" s="27"/>
+      <c r="Z12" s="27"/>
+      <c r="AA12" s="5"/>
       <c r="AB12" s="27"/>
       <c r="AC12" s="27"/>
-    </row>
-    <row r="13" s="23" customFormat="1" ht="16.5" spans="1:29">
+      <c r="AD12" s="25"/>
+      <c r="AE12" s="25"/>
+      <c r="AF12" s="25"/>
+      <c r="AG12" s="25"/>
+      <c r="AH12" s="25"/>
+      <c r="AI12" s="25"/>
+      <c r="AJ12" s="25"/>
+    </row>
+    <row r="13" s="24" customFormat="1" ht="16.5" spans="1:36">
       <c r="A13" s="2" t="s">
         <v>41</v>
       </c>
@@ -2682,63 +2869,70 @@
         <v>220000</v>
       </c>
       <c r="F13" s="5"/>
-      <c r="G13" s="25">
+      <c r="G13" s="27">
         <v>460000</v>
       </c>
-      <c r="H13" s="25">
+      <c r="H13" s="27">
         <v>0</v>
       </c>
       <c r="I13" s="5"/>
-      <c r="J13" s="25">
+      <c r="J13" s="27">
         <v>470000</v>
       </c>
-      <c r="K13" s="25">
+      <c r="K13" s="27">
         <v>0</v>
       </c>
       <c r="L13" s="5"/>
-      <c r="M13" s="25">
+      <c r="M13" s="27">
         <v>480000</v>
       </c>
-      <c r="N13" s="25">
+      <c r="N13" s="27">
         <v>0</v>
       </c>
       <c r="O13" s="5"/>
-      <c r="P13" s="25">
+      <c r="P13" s="27">
         <v>490000</v>
       </c>
-      <c r="Q13" s="25">
+      <c r="Q13" s="27">
         <v>0</v>
       </c>
       <c r="R13" s="5"/>
-      <c r="S13" s="25">
+      <c r="S13" s="27">
         <v>500000</v>
       </c>
-      <c r="T13" s="25">
+      <c r="T13" s="27">
         <v>0</v>
       </c>
       <c r="U13" s="5"/>
-      <c r="V13" s="25">
+      <c r="V13" s="27">
         <v>510000</v>
       </c>
-      <c r="W13" s="25">
+      <c r="W13" s="27">
         <v>0</v>
       </c>
       <c r="X13" s="5"/>
-      <c r="Y13" s="25">
+      <c r="Y13" s="27">
         <v>520000</v>
       </c>
-      <c r="Z13" s="25">
-        <v>0</v>
-      </c>
-      <c r="AA13" s="26"/>
+      <c r="Z13" s="27">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="5"/>
       <c r="AB13" s="27">
         <v>530000</v>
       </c>
-      <c r="AC13" s="29">
-        <v>-363800</v>
-      </c>
-    </row>
-    <row r="14" s="23" customFormat="1" ht="16.5" spans="1:29">
+      <c r="AC13" s="27">
+        <v>2498200</v>
+      </c>
+      <c r="AD13" s="25"/>
+      <c r="AE13" s="25"/>
+      <c r="AF13" s="25"/>
+      <c r="AG13" s="25"/>
+      <c r="AH13" s="25"/>
+      <c r="AI13" s="25"/>
+      <c r="AJ13" s="25"/>
+    </row>
+    <row r="14" s="24" customFormat="1" ht="16.5" spans="1:36">
       <c r="A14" s="2" t="s">
         <v>42</v>
       </c>
@@ -2751,47 +2945,54 @@
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
       <c r="F14" s="5"/>
-      <c r="G14" s="25">
+      <c r="G14" s="27">
         <v>480000</v>
       </c>
-      <c r="H14" s="25">
+      <c r="H14" s="27">
         <v>0</v>
       </c>
       <c r="I14" s="5"/>
-      <c r="J14" s="25">
+      <c r="J14" s="27">
         <v>490000</v>
       </c>
-      <c r="K14" s="25">
+      <c r="K14" s="27">
         <v>0</v>
       </c>
       <c r="L14" s="5"/>
-      <c r="M14" s="25">
+      <c r="M14" s="27">
         <v>510000</v>
       </c>
-      <c r="N14" s="25">
+      <c r="N14" s="27">
         <v>0</v>
       </c>
       <c r="O14" s="5"/>
-      <c r="P14" s="25">
+      <c r="P14" s="27">
         <v>520000</v>
       </c>
-      <c r="Q14" s="25">
+      <c r="Q14" s="27">
         <v>1251360</v>
       </c>
       <c r="R14" s="5"/>
-      <c r="S14" s="25"/>
-      <c r="T14" s="25"/>
+      <c r="S14" s="27"/>
+      <c r="T14" s="27"/>
       <c r="U14" s="5"/>
-      <c r="V14" s="25"/>
-      <c r="W14" s="25"/>
+      <c r="V14" s="27"/>
+      <c r="W14" s="27"/>
       <c r="X14" s="5"/>
-      <c r="Y14" s="25"/>
-      <c r="Z14" s="25"/>
-      <c r="AA14" s="26"/>
+      <c r="Y14" s="27"/>
+      <c r="Z14" s="27"/>
+      <c r="AA14" s="5"/>
       <c r="AB14" s="27"/>
       <c r="AC14" s="27"/>
-    </row>
-    <row r="15" s="23" customFormat="1" ht="16.5" spans="1:29">
+      <c r="AD14" s="25"/>
+      <c r="AE14" s="25"/>
+      <c r="AF14" s="25"/>
+      <c r="AG14" s="25"/>
+      <c r="AH14" s="25"/>
+      <c r="AI14" s="25"/>
+      <c r="AJ14" s="25"/>
+    </row>
+    <row r="15" s="24" customFormat="1" ht="16.5" spans="1:36">
       <c r="A15" s="2" t="s">
         <v>43</v>
       </c>
@@ -2808,43 +3009,50 @@
         <v>190000</v>
       </c>
       <c r="F15" s="5"/>
-      <c r="G15" s="25">
+      <c r="G15" s="27">
         <v>480000</v>
       </c>
-      <c r="H15" s="25">
+      <c r="H15" s="27">
         <v>0</v>
       </c>
       <c r="I15" s="5"/>
-      <c r="J15" s="25">
+      <c r="J15" s="27">
         <v>490000</v>
       </c>
-      <c r="K15" s="25">
+      <c r="K15" s="27">
         <v>0</v>
       </c>
       <c r="L15" s="5"/>
-      <c r="M15" s="25">
+      <c r="M15" s="27">
         <v>510000</v>
       </c>
-      <c r="N15" s="25">
+      <c r="N15" s="27">
         <v>22032000</v>
       </c>
       <c r="O15" s="5"/>
-      <c r="P15" s="25"/>
-      <c r="Q15" s="25"/>
+      <c r="P15" s="27"/>
+      <c r="Q15" s="27"/>
       <c r="R15" s="5"/>
-      <c r="S15" s="25"/>
-      <c r="T15" s="25"/>
+      <c r="S15" s="27"/>
+      <c r="T15" s="27"/>
       <c r="U15" s="5"/>
-      <c r="V15" s="25"/>
-      <c r="W15" s="25"/>
+      <c r="V15" s="27"/>
+      <c r="W15" s="27"/>
       <c r="X15" s="5"/>
-      <c r="Y15" s="25"/>
-      <c r="Z15" s="25"/>
-      <c r="AA15" s="26"/>
+      <c r="Y15" s="27"/>
+      <c r="Z15" s="27"/>
+      <c r="AA15" s="5"/>
       <c r="AB15" s="27"/>
       <c r="AC15" s="27"/>
-    </row>
-    <row r="16" s="23" customFormat="1" ht="16.5" spans="1:29">
+      <c r="AD15" s="25"/>
+      <c r="AE15" s="25"/>
+      <c r="AF15" s="25"/>
+      <c r="AG15" s="25"/>
+      <c r="AH15" s="25"/>
+      <c r="AI15" s="25"/>
+      <c r="AJ15" s="25"/>
+    </row>
+    <row r="16" s="24" customFormat="1" ht="16.5" spans="1:36">
       <c r="A16" s="2" t="s">
         <v>44</v>
       </c>
@@ -2857,35 +3065,42 @@
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="5"/>
-      <c r="G16" s="25">
+      <c r="G16" s="27">
         <v>530000</v>
       </c>
-      <c r="H16" s="25">
+      <c r="H16" s="27">
         <v>16920</v>
       </c>
       <c r="I16" s="5"/>
-      <c r="J16" s="25"/>
-      <c r="K16" s="25"/>
+      <c r="J16" s="27"/>
+      <c r="K16" s="27"/>
       <c r="L16" s="5"/>
-      <c r="M16" s="25"/>
-      <c r="N16" s="25"/>
+      <c r="M16" s="27"/>
+      <c r="N16" s="27"/>
       <c r="O16" s="5"/>
-      <c r="P16" s="25"/>
-      <c r="Q16" s="25"/>
+      <c r="P16" s="27"/>
+      <c r="Q16" s="27"/>
       <c r="R16" s="5"/>
-      <c r="S16" s="25"/>
-      <c r="T16" s="25"/>
+      <c r="S16" s="27"/>
+      <c r="T16" s="27"/>
       <c r="U16" s="5"/>
-      <c r="V16" s="25"/>
-      <c r="W16" s="25"/>
+      <c r="V16" s="27"/>
+      <c r="W16" s="27"/>
       <c r="X16" s="5"/>
-      <c r="Y16" s="25"/>
-      <c r="Z16" s="25"/>
-      <c r="AA16" s="26"/>
+      <c r="Y16" s="27"/>
+      <c r="Z16" s="27"/>
+      <c r="AA16" s="5"/>
       <c r="AB16" s="27"/>
       <c r="AC16" s="27"/>
-    </row>
-    <row r="17" s="23" customFormat="1" ht="16.5" spans="1:29">
+      <c r="AD16" s="25"/>
+      <c r="AE16" s="25"/>
+      <c r="AF16" s="25"/>
+      <c r="AG16" s="25"/>
+      <c r="AH16" s="25"/>
+      <c r="AI16" s="25"/>
+      <c r="AJ16" s="25"/>
+    </row>
+    <row r="17" s="24" customFormat="1" ht="16.5" spans="1:36">
       <c r="A17" s="2" t="s">
         <v>45</v>
       </c>
@@ -2898,51 +3113,58 @@
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
       <c r="F17" s="5"/>
-      <c r="G17" s="25">
+      <c r="G17" s="27">
         <v>440000</v>
       </c>
-      <c r="H17" s="25">
+      <c r="H17" s="27">
         <v>0</v>
       </c>
       <c r="I17" s="5"/>
-      <c r="J17" s="25">
+      <c r="J17" s="27">
         <v>450000</v>
       </c>
-      <c r="K17" s="25">
+      <c r="K17" s="27">
         <v>0</v>
       </c>
       <c r="L17" s="5"/>
-      <c r="M17" s="25">
+      <c r="M17" s="27">
         <v>470000</v>
       </c>
-      <c r="N17" s="25">
+      <c r="N17" s="27">
         <v>0</v>
       </c>
       <c r="O17" s="5"/>
-      <c r="P17" s="25">
+      <c r="P17" s="27">
         <v>500000</v>
       </c>
-      <c r="Q17" s="25">
+      <c r="Q17" s="27">
         <v>0</v>
       </c>
       <c r="R17" s="5"/>
-      <c r="S17" s="25">
+      <c r="S17" s="27">
         <v>520000</v>
       </c>
       <c r="T17" s="28">
-        <v>-88738865.75</v>
+        <v>-190281905.75</v>
       </c>
       <c r="U17" s="5"/>
-      <c r="V17" s="25"/>
-      <c r="W17" s="25"/>
+      <c r="V17" s="27"/>
+      <c r="W17" s="27"/>
       <c r="X17" s="5"/>
-      <c r="Y17" s="25"/>
-      <c r="Z17" s="25"/>
-      <c r="AA17" s="26"/>
+      <c r="Y17" s="27"/>
+      <c r="Z17" s="27"/>
+      <c r="AA17" s="5"/>
       <c r="AB17" s="27"/>
       <c r="AC17" s="27"/>
-    </row>
-    <row r="18" s="23" customFormat="1" ht="16.5" spans="1:29">
+      <c r="AD17" s="25"/>
+      <c r="AE17" s="25"/>
+      <c r="AF17" s="25"/>
+      <c r="AG17" s="25"/>
+      <c r="AH17" s="25"/>
+      <c r="AI17" s="25"/>
+      <c r="AJ17" s="25"/>
+    </row>
+    <row r="18" s="24" customFormat="1" ht="16.5" spans="1:36">
       <c r="A18" s="2" t="s">
         <v>46</v>
       </c>
@@ -2955,39 +3177,46 @@
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
       <c r="F18" s="5"/>
-      <c r="G18" s="25">
+      <c r="G18" s="27">
         <v>465000</v>
       </c>
-      <c r="H18" s="25">
+      <c r="H18" s="27">
         <v>0</v>
       </c>
       <c r="I18" s="5"/>
-      <c r="J18" s="25">
+      <c r="J18" s="27">
         <v>495000</v>
       </c>
-      <c r="K18" s="25">
+      <c r="K18" s="27">
         <v>846480</v>
       </c>
       <c r="L18" s="5"/>
-      <c r="M18" s="25"/>
-      <c r="N18" s="25"/>
+      <c r="M18" s="27"/>
+      <c r="N18" s="27"/>
       <c r="O18" s="5"/>
-      <c r="P18" s="25"/>
-      <c r="Q18" s="25"/>
+      <c r="P18" s="27"/>
+      <c r="Q18" s="27"/>
       <c r="R18" s="5"/>
-      <c r="S18" s="25"/>
-      <c r="T18" s="25"/>
+      <c r="S18" s="27"/>
+      <c r="T18" s="27"/>
       <c r="U18" s="5"/>
-      <c r="V18" s="25"/>
-      <c r="W18" s="25"/>
+      <c r="V18" s="27"/>
+      <c r="W18" s="27"/>
       <c r="X18" s="5"/>
-      <c r="Y18" s="25"/>
-      <c r="Z18" s="25"/>
-      <c r="AA18" s="26"/>
+      <c r="Y18" s="27"/>
+      <c r="Z18" s="27"/>
+      <c r="AA18" s="5"/>
       <c r="AB18" s="27"/>
       <c r="AC18" s="27"/>
-    </row>
-    <row r="19" s="23" customFormat="1" ht="16.5" spans="1:29">
+      <c r="AD18" s="25"/>
+      <c r="AE18" s="25"/>
+      <c r="AF18" s="25"/>
+      <c r="AG18" s="25"/>
+      <c r="AH18" s="25"/>
+      <c r="AI18" s="25"/>
+      <c r="AJ18" s="25"/>
+    </row>
+    <row r="19" s="24" customFormat="1" ht="16.5" spans="1:36">
       <c r="A19" s="2" t="s">
         <v>47</v>
       </c>
@@ -3000,47 +3229,54 @@
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
       <c r="F19" s="5"/>
-      <c r="G19" s="25">
+      <c r="G19" s="27">
         <v>430000</v>
       </c>
-      <c r="H19" s="25">
+      <c r="H19" s="27">
         <v>0</v>
       </c>
       <c r="I19" s="5"/>
-      <c r="J19" s="25">
+      <c r="J19" s="27">
         <v>470000</v>
       </c>
-      <c r="K19" s="25">
+      <c r="K19" s="27">
         <v>0</v>
       </c>
       <c r="L19" s="5"/>
-      <c r="M19" s="25">
+      <c r="M19" s="27">
         <v>490000</v>
       </c>
-      <c r="N19" s="25">
-        <v>215652525</v>
+      <c r="N19" s="27">
+        <v>57648525</v>
       </c>
       <c r="O19" s="5"/>
-      <c r="P19" s="25">
+      <c r="P19" s="27">
         <v>500000</v>
       </c>
-      <c r="Q19" s="25">
+      <c r="Q19" s="27">
         <v>500000000</v>
       </c>
       <c r="R19" s="5"/>
-      <c r="S19" s="25"/>
-      <c r="T19" s="25"/>
+      <c r="S19" s="27"/>
+      <c r="T19" s="27"/>
       <c r="U19" s="5"/>
-      <c r="V19" s="25"/>
-      <c r="W19" s="25"/>
+      <c r="V19" s="27"/>
+      <c r="W19" s="27"/>
       <c r="X19" s="5"/>
-      <c r="Y19" s="25"/>
-      <c r="Z19" s="25"/>
-      <c r="AA19" s="26"/>
+      <c r="Y19" s="27"/>
+      <c r="Z19" s="27"/>
+      <c r="AA19" s="5"/>
       <c r="AB19" s="27"/>
       <c r="AC19" s="27"/>
-    </row>
-    <row r="20" s="23" customFormat="1" ht="16.5" spans="1:29">
+      <c r="AD19" s="25"/>
+      <c r="AE19" s="25"/>
+      <c r="AF19" s="25"/>
+      <c r="AG19" s="25"/>
+      <c r="AH19" s="25"/>
+      <c r="AI19" s="25"/>
+      <c r="AJ19" s="25"/>
+    </row>
+    <row r="20" s="24" customFormat="1" ht="16.5" spans="1:36">
       <c r="A20" s="2" t="s">
         <v>48</v>
       </c>
@@ -3053,39 +3289,46 @@
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
       <c r="F20" s="5"/>
-      <c r="G20" s="25">
+      <c r="G20" s="27">
         <v>445000</v>
       </c>
-      <c r="H20" s="25">
+      <c r="H20" s="27">
         <v>0</v>
       </c>
       <c r="I20" s="5"/>
-      <c r="J20" s="25">
+      <c r="J20" s="27">
         <v>475000</v>
       </c>
-      <c r="K20" s="25">
+      <c r="K20" s="27">
         <v>434057045</v>
       </c>
       <c r="L20" s="5"/>
-      <c r="M20" s="25"/>
-      <c r="N20" s="25"/>
+      <c r="M20" s="27"/>
+      <c r="N20" s="27"/>
       <c r="O20" s="5"/>
-      <c r="P20" s="25"/>
-      <c r="Q20" s="25"/>
+      <c r="P20" s="27"/>
+      <c r="Q20" s="27"/>
       <c r="R20" s="5"/>
-      <c r="S20" s="25"/>
-      <c r="T20" s="25"/>
+      <c r="S20" s="27"/>
+      <c r="T20" s="27"/>
       <c r="U20" s="5"/>
-      <c r="V20" s="25"/>
-      <c r="W20" s="25"/>
+      <c r="V20" s="27"/>
+      <c r="W20" s="27"/>
       <c r="X20" s="5"/>
-      <c r="Y20" s="25"/>
-      <c r="Z20" s="25"/>
-      <c r="AA20" s="26"/>
+      <c r="Y20" s="27"/>
+      <c r="Z20" s="27"/>
+      <c r="AA20" s="5"/>
       <c r="AB20" s="27"/>
       <c r="AC20" s="27"/>
-    </row>
-    <row r="21" s="23" customFormat="1" ht="16.5" spans="1:29">
+      <c r="AD20" s="25"/>
+      <c r="AE20" s="25"/>
+      <c r="AF20" s="25"/>
+      <c r="AG20" s="25"/>
+      <c r="AH20" s="25"/>
+      <c r="AI20" s="25"/>
+      <c r="AJ20" s="25"/>
+    </row>
+    <row r="21" s="24" customFormat="1" ht="16.5" spans="1:36">
       <c r="A21" s="2" t="s">
         <v>49</v>
       </c>
@@ -3098,39 +3341,46 @@
       <c r="D21" s="3"/>
       <c r="E21" s="3"/>
       <c r="F21" s="5"/>
-      <c r="G21" s="25">
+      <c r="G21" s="27">
         <v>455000</v>
       </c>
-      <c r="H21" s="25">
+      <c r="H21" s="27">
         <v>0</v>
       </c>
       <c r="I21" s="5"/>
-      <c r="J21" s="25">
+      <c r="J21" s="27">
         <v>515000</v>
       </c>
-      <c r="K21" s="25">
+      <c r="K21" s="27">
         <v>220703770</v>
       </c>
       <c r="L21" s="5"/>
-      <c r="M21" s="25"/>
-      <c r="N21" s="25"/>
+      <c r="M21" s="27"/>
+      <c r="N21" s="27"/>
       <c r="O21" s="5"/>
-      <c r="P21" s="25"/>
-      <c r="Q21" s="25"/>
+      <c r="P21" s="27"/>
+      <c r="Q21" s="27"/>
       <c r="R21" s="5"/>
-      <c r="S21" s="25"/>
-      <c r="T21" s="25"/>
+      <c r="S21" s="27"/>
+      <c r="T21" s="27"/>
       <c r="U21" s="5"/>
-      <c r="V21" s="25"/>
-      <c r="W21" s="25"/>
+      <c r="V21" s="27"/>
+      <c r="W21" s="27"/>
       <c r="X21" s="5"/>
-      <c r="Y21" s="25"/>
-      <c r="Z21" s="25"/>
-      <c r="AA21" s="26"/>
+      <c r="Y21" s="27"/>
+      <c r="Z21" s="27"/>
+      <c r="AA21" s="5"/>
       <c r="AB21" s="27"/>
       <c r="AC21" s="27"/>
-    </row>
-    <row r="22" s="23" customFormat="1" ht="16.5" spans="1:29">
+      <c r="AD21" s="25"/>
+      <c r="AE21" s="25"/>
+      <c r="AF21" s="25"/>
+      <c r="AG21" s="25"/>
+      <c r="AH21" s="25"/>
+      <c r="AI21" s="25"/>
+      <c r="AJ21" s="25"/>
+    </row>
+    <row r="22" s="24" customFormat="1" ht="16.5" spans="1:36">
       <c r="A22" s="2" t="s">
         <v>50</v>
       </c>
@@ -3143,39 +3393,46 @@
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
       <c r="F22" s="5"/>
-      <c r="G22" s="25">
+      <c r="G22" s="27">
         <v>450000</v>
       </c>
-      <c r="H22" s="25">
+      <c r="H22" s="27">
         <v>0</v>
       </c>
       <c r="I22" s="5"/>
-      <c r="J22" s="25">
+      <c r="J22" s="27">
         <v>460000</v>
       </c>
-      <c r="K22" s="25">
+      <c r="K22" s="27">
         <v>7370045.5</v>
       </c>
       <c r="L22" s="5"/>
-      <c r="M22" s="25"/>
-      <c r="N22" s="25"/>
+      <c r="M22" s="27"/>
+      <c r="N22" s="27"/>
       <c r="O22" s="5"/>
-      <c r="P22" s="25"/>
-      <c r="Q22" s="25"/>
+      <c r="P22" s="27"/>
+      <c r="Q22" s="27"/>
       <c r="R22" s="5"/>
-      <c r="S22" s="25"/>
-      <c r="T22" s="25"/>
+      <c r="S22" s="27"/>
+      <c r="T22" s="27"/>
       <c r="U22" s="5"/>
-      <c r="V22" s="25"/>
-      <c r="W22" s="25"/>
+      <c r="V22" s="27"/>
+      <c r="W22" s="27"/>
       <c r="X22" s="5"/>
-      <c r="Y22" s="25"/>
-      <c r="Z22" s="25"/>
-      <c r="AA22" s="26"/>
+      <c r="Y22" s="27"/>
+      <c r="Z22" s="27"/>
+      <c r="AA22" s="5"/>
       <c r="AB22" s="27"/>
       <c r="AC22" s="27"/>
-    </row>
-    <row r="23" s="23" customFormat="1" ht="16.5" spans="1:29">
+      <c r="AD22" s="25"/>
+      <c r="AE22" s="25"/>
+      <c r="AF22" s="25"/>
+      <c r="AG22" s="25"/>
+      <c r="AH22" s="25"/>
+      <c r="AI22" s="25"/>
+      <c r="AJ22" s="25"/>
+    </row>
+    <row r="23" s="24" customFormat="1" ht="16.5" spans="1:36">
       <c r="A23" s="2" t="s">
         <v>51</v>
       </c>
@@ -3188,35 +3445,42 @@
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
       <c r="F23" s="5"/>
-      <c r="G23" s="25">
+      <c r="G23" s="27">
         <v>445000</v>
       </c>
-      <c r="H23" s="25">
+      <c r="H23" s="27">
         <v>62173237.5</v>
       </c>
       <c r="I23" s="5"/>
-      <c r="J23" s="25"/>
-      <c r="K23" s="25"/>
+      <c r="J23" s="27"/>
+      <c r="K23" s="27"/>
       <c r="L23" s="5"/>
-      <c r="M23" s="25"/>
-      <c r="N23" s="25"/>
+      <c r="M23" s="27"/>
+      <c r="N23" s="27"/>
       <c r="O23" s="5"/>
-      <c r="P23" s="25"/>
-      <c r="Q23" s="25"/>
+      <c r="P23" s="27"/>
+      <c r="Q23" s="27"/>
       <c r="R23" s="5"/>
-      <c r="S23" s="25"/>
-      <c r="T23" s="25"/>
+      <c r="S23" s="27"/>
+      <c r="T23" s="27"/>
       <c r="U23" s="5"/>
-      <c r="V23" s="25"/>
-      <c r="W23" s="25"/>
+      <c r="V23" s="27"/>
+      <c r="W23" s="27"/>
       <c r="X23" s="5"/>
-      <c r="Y23" s="25"/>
-      <c r="Z23" s="25"/>
-      <c r="AA23" s="26"/>
+      <c r="Y23" s="27"/>
+      <c r="Z23" s="27"/>
+      <c r="AA23" s="5"/>
       <c r="AB23" s="27"/>
       <c r="AC23" s="27"/>
-    </row>
-    <row r="24" s="23" customFormat="1" ht="16.5" spans="1:29">
+      <c r="AD23" s="25"/>
+      <c r="AE23" s="25"/>
+      <c r="AF23" s="25"/>
+      <c r="AG23" s="25"/>
+      <c r="AH23" s="25"/>
+      <c r="AI23" s="25"/>
+      <c r="AJ23" s="25"/>
+    </row>
+    <row r="24" s="24" customFormat="1" ht="16.5" spans="1:36">
       <c r="A24" s="2" t="s">
         <v>52</v>
       </c>
@@ -3229,43 +3493,50 @@
       <c r="D24" s="3"/>
       <c r="E24" s="3"/>
       <c r="F24" s="5"/>
-      <c r="G24" s="25">
+      <c r="G24" s="27">
         <v>490000</v>
       </c>
-      <c r="H24" s="25">
+      <c r="H24" s="27">
         <v>0</v>
       </c>
       <c r="I24" s="5"/>
-      <c r="J24" s="25">
+      <c r="J24" s="27">
         <v>500000</v>
       </c>
-      <c r="K24" s="25">
+      <c r="K24" s="27">
         <v>0</v>
       </c>
       <c r="L24" s="5"/>
-      <c r="M24" s="25">
+      <c r="M24" s="27">
         <v>540000</v>
       </c>
-      <c r="N24" s="25">
+      <c r="N24" s="27">
         <v>0</v>
       </c>
       <c r="O24" s="5"/>
-      <c r="P24" s="25"/>
-      <c r="Q24" s="25"/>
+      <c r="P24" s="27"/>
+      <c r="Q24" s="27"/>
       <c r="R24" s="5"/>
-      <c r="S24" s="25"/>
-      <c r="T24" s="25"/>
+      <c r="S24" s="27"/>
+      <c r="T24" s="27"/>
       <c r="U24" s="5"/>
-      <c r="V24" s="25"/>
-      <c r="W24" s="25"/>
+      <c r="V24" s="27"/>
+      <c r="W24" s="27"/>
       <c r="X24" s="5"/>
-      <c r="Y24" s="25"/>
-      <c r="Z24" s="25"/>
-      <c r="AA24" s="26"/>
+      <c r="Y24" s="27"/>
+      <c r="Z24" s="27"/>
+      <c r="AA24" s="5"/>
       <c r="AB24" s="27"/>
       <c r="AC24" s="27"/>
-    </row>
-    <row r="25" s="23" customFormat="1" ht="16.5" spans="1:29">
+      <c r="AD24" s="25"/>
+      <c r="AE24" s="25"/>
+      <c r="AF24" s="25"/>
+      <c r="AG24" s="25"/>
+      <c r="AH24" s="25"/>
+      <c r="AI24" s="25"/>
+      <c r="AJ24" s="25"/>
+    </row>
+    <row r="25" s="24" customFormat="1" ht="16.5" spans="1:36">
       <c r="A25" s="2" t="s">
         <v>53</v>
       </c>
@@ -3278,55 +3549,66 @@
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
       <c r="F25" s="5"/>
-      <c r="G25" s="25">
+      <c r="G25" s="27">
         <v>455000</v>
       </c>
-      <c r="H25" s="25">
+      <c r="H25" s="27">
         <v>0</v>
       </c>
       <c r="I25" s="5"/>
-      <c r="J25" s="25">
+      <c r="J25" s="27">
         <v>465000</v>
       </c>
-      <c r="K25" s="25">
+      <c r="K25" s="27">
         <v>0</v>
       </c>
       <c r="L25" s="5"/>
-      <c r="M25" s="25">
+      <c r="M25" s="27">
         <v>470000</v>
       </c>
-      <c r="N25" s="25">
+      <c r="N25" s="27">
         <v>0</v>
       </c>
       <c r="O25" s="5"/>
-      <c r="P25" s="25">
+      <c r="P25" s="27">
         <v>500000</v>
       </c>
-      <c r="Q25" s="25">
+      <c r="Q25" s="27">
         <v>0</v>
       </c>
       <c r="R25" s="5"/>
-      <c r="S25" s="25">
+      <c r="S25" s="27">
         <v>510000</v>
       </c>
-      <c r="T25" s="25">
+      <c r="T25" s="27">
         <v>0</v>
       </c>
       <c r="U25" s="5"/>
-      <c r="V25" s="25">
+      <c r="V25" s="27">
         <v>520000</v>
       </c>
-      <c r="W25" s="25">
-        <v>2236510</v>
+      <c r="W25" s="27">
+        <v>0</v>
       </c>
       <c r="X25" s="5"/>
-      <c r="Y25" s="25"/>
-      <c r="Z25" s="25"/>
-      <c r="AA25" s="26"/>
+      <c r="Y25" s="27">
+        <v>520000</v>
+      </c>
+      <c r="Z25" s="27">
+        <v>87494510</v>
+      </c>
+      <c r="AA25" s="5"/>
       <c r="AB25" s="27"/>
       <c r="AC25" s="27"/>
-    </row>
-    <row r="26" s="23" customFormat="1" ht="16.5" spans="1:29">
+      <c r="AD25" s="25"/>
+      <c r="AE25" s="25"/>
+      <c r="AF25" s="25"/>
+      <c r="AG25" s="25"/>
+      <c r="AH25" s="25"/>
+      <c r="AI25" s="25"/>
+      <c r="AJ25" s="25"/>
+    </row>
+    <row r="26" s="24" customFormat="1" ht="16.5" spans="1:36">
       <c r="A26" s="2" t="s">
         <v>54</v>
       </c>
@@ -3343,55 +3625,62 @@
         <v>190000</v>
       </c>
       <c r="F26" s="5"/>
-      <c r="G26" s="25">
+      <c r="G26" s="27">
         <v>430000</v>
       </c>
-      <c r="H26" s="25">
+      <c r="H26" s="27">
         <v>0</v>
       </c>
       <c r="I26" s="5"/>
-      <c r="J26" s="25">
+      <c r="J26" s="27">
         <v>440000</v>
       </c>
-      <c r="K26" s="25">
+      <c r="K26" s="27">
         <v>0</v>
       </c>
       <c r="L26" s="5"/>
-      <c r="M26" s="25">
+      <c r="M26" s="27">
         <v>460000</v>
       </c>
-      <c r="N26" s="25">
+      <c r="N26" s="27">
         <v>0</v>
       </c>
       <c r="O26" s="5"/>
-      <c r="P26" s="25">
+      <c r="P26" s="27">
         <v>490000</v>
       </c>
-      <c r="Q26" s="25">
+      <c r="Q26" s="27">
         <v>0</v>
       </c>
       <c r="R26" s="5"/>
-      <c r="S26" s="25">
+      <c r="S26" s="27">
         <v>510000</v>
       </c>
-      <c r="T26" s="25">
+      <c r="T26" s="27">
         <v>0</v>
       </c>
       <c r="U26" s="5"/>
-      <c r="V26" s="25">
+      <c r="V26" s="27">
         <v>500000</v>
       </c>
       <c r="W26" s="28">
-        <v>-20292816.5</v>
+        <v>-56283816.5</v>
       </c>
       <c r="X26" s="5"/>
-      <c r="Y26" s="25"/>
-      <c r="Z26" s="25"/>
-      <c r="AA26" s="26"/>
+      <c r="Y26" s="27"/>
+      <c r="Z26" s="27"/>
+      <c r="AA26" s="5"/>
       <c r="AB26" s="27"/>
       <c r="AC26" s="27"/>
-    </row>
-    <row r="27" s="23" customFormat="1" ht="16.5" spans="1:29">
+      <c r="AD26" s="25"/>
+      <c r="AE26" s="25"/>
+      <c r="AF26" s="25"/>
+      <c r="AG26" s="25"/>
+      <c r="AH26" s="25"/>
+      <c r="AI26" s="25"/>
+      <c r="AJ26" s="25"/>
+    </row>
+    <row r="27" s="24" customFormat="1" ht="16.5" spans="1:36">
       <c r="A27" s="2" t="s">
         <v>55</v>
       </c>
@@ -3404,35 +3693,42 @@
       <c r="D27" s="3"/>
       <c r="E27" s="3"/>
       <c r="F27" s="5"/>
-      <c r="G27" s="25">
+      <c r="G27" s="27">
         <v>460000</v>
       </c>
-      <c r="H27" s="25">
+      <c r="H27" s="27">
         <v>0</v>
       </c>
       <c r="I27" s="5"/>
-      <c r="J27" s="25"/>
-      <c r="K27" s="25"/>
+      <c r="J27" s="27"/>
+      <c r="K27" s="27"/>
       <c r="L27" s="5"/>
-      <c r="M27" s="25"/>
-      <c r="N27" s="25"/>
+      <c r="M27" s="27"/>
+      <c r="N27" s="27"/>
       <c r="O27" s="5"/>
-      <c r="P27" s="25"/>
-      <c r="Q27" s="25"/>
+      <c r="P27" s="27"/>
+      <c r="Q27" s="27"/>
       <c r="R27" s="5"/>
-      <c r="S27" s="25"/>
-      <c r="T27" s="25"/>
+      <c r="S27" s="27"/>
+      <c r="T27" s="27"/>
       <c r="U27" s="5"/>
-      <c r="V27" s="25"/>
-      <c r="W27" s="25"/>
+      <c r="V27" s="27"/>
+      <c r="W27" s="27"/>
       <c r="X27" s="5"/>
-      <c r="Y27" s="25"/>
-      <c r="Z27" s="25"/>
-      <c r="AA27" s="26"/>
+      <c r="Y27" s="27"/>
+      <c r="Z27" s="27"/>
+      <c r="AA27" s="5"/>
       <c r="AB27" s="27"/>
       <c r="AC27" s="27"/>
-    </row>
-    <row r="28" s="23" customFormat="1" ht="16.5" spans="1:29">
+      <c r="AD27" s="25"/>
+      <c r="AE27" s="25"/>
+      <c r="AF27" s="25"/>
+      <c r="AG27" s="25"/>
+      <c r="AH27" s="25"/>
+      <c r="AI27" s="25"/>
+      <c r="AJ27" s="25"/>
+    </row>
+    <row r="28" s="24" customFormat="1" ht="16.5" spans="1:36">
       <c r="A28" s="2" t="s">
         <v>56</v>
       </c>
@@ -3445,47 +3741,54 @@
       <c r="D28" s="3"/>
       <c r="E28" s="3"/>
       <c r="F28" s="5"/>
-      <c r="G28" s="25">
+      <c r="G28" s="27">
         <v>460000</v>
       </c>
-      <c r="H28" s="25">
+      <c r="H28" s="27">
         <v>0</v>
       </c>
       <c r="I28" s="5"/>
-      <c r="J28" s="25">
+      <c r="J28" s="27">
         <v>490000</v>
       </c>
-      <c r="K28" s="25">
+      <c r="K28" s="27">
         <v>0</v>
       </c>
       <c r="L28" s="5"/>
-      <c r="M28" s="25">
+      <c r="M28" s="27">
         <v>500000</v>
       </c>
-      <c r="N28" s="25">
+      <c r="N28" s="27">
         <v>0</v>
       </c>
       <c r="O28" s="5"/>
-      <c r="P28" s="25">
+      <c r="P28" s="27">
         <v>530000</v>
       </c>
-      <c r="Q28" s="25">
+      <c r="Q28" s="27">
         <v>1248600</v>
       </c>
       <c r="R28" s="5"/>
-      <c r="S28" s="25"/>
-      <c r="T28" s="25"/>
+      <c r="S28" s="27"/>
+      <c r="T28" s="27"/>
       <c r="U28" s="5"/>
-      <c r="V28" s="25"/>
-      <c r="W28" s="25"/>
+      <c r="V28" s="27"/>
+      <c r="W28" s="27"/>
       <c r="X28" s="5"/>
-      <c r="Y28" s="25"/>
-      <c r="Z28" s="25"/>
-      <c r="AA28" s="26"/>
+      <c r="Y28" s="27"/>
+      <c r="Z28" s="27"/>
+      <c r="AA28" s="5"/>
       <c r="AB28" s="27"/>
       <c r="AC28" s="27"/>
-    </row>
-    <row r="29" s="23" customFormat="1" ht="16.5" spans="1:29">
+      <c r="AD28" s="25"/>
+      <c r="AE28" s="25"/>
+      <c r="AF28" s="25"/>
+      <c r="AG28" s="25"/>
+      <c r="AH28" s="25"/>
+      <c r="AI28" s="25"/>
+      <c r="AJ28" s="25"/>
+    </row>
+    <row r="29" s="24" customFormat="1" ht="16.5" spans="1:36">
       <c r="A29" s="2" t="s">
         <v>57</v>
       </c>
@@ -3502,55 +3805,62 @@
         <v>190000</v>
       </c>
       <c r="F29" s="5"/>
-      <c r="G29" s="25">
+      <c r="G29" s="27">
         <v>450000</v>
       </c>
-      <c r="H29" s="25">
+      <c r="H29" s="27">
         <v>0</v>
       </c>
       <c r="I29" s="5"/>
-      <c r="J29" s="25">
+      <c r="J29" s="27">
         <v>470000</v>
       </c>
-      <c r="K29" s="25">
+      <c r="K29" s="27">
         <v>0</v>
       </c>
       <c r="L29" s="5"/>
-      <c r="M29" s="25">
+      <c r="M29" s="27">
         <v>480000</v>
       </c>
-      <c r="N29" s="25">
+      <c r="N29" s="27">
         <v>0</v>
       </c>
       <c r="O29" s="5"/>
-      <c r="P29" s="25">
+      <c r="P29" s="27">
         <v>500000</v>
       </c>
-      <c r="Q29" s="25">
+      <c r="Q29" s="27">
         <v>0</v>
       </c>
       <c r="R29" s="5"/>
-      <c r="S29" s="25">
+      <c r="S29" s="27">
         <v>520000</v>
       </c>
-      <c r="T29" s="25">
+      <c r="T29" s="27">
         <v>0</v>
       </c>
       <c r="U29" s="5"/>
-      <c r="V29" s="25">
+      <c r="V29" s="27">
         <v>510000</v>
       </c>
-      <c r="W29" s="25">
-        <v>5480000</v>
+      <c r="W29" s="27">
+        <v>0</v>
       </c>
       <c r="X29" s="5"/>
-      <c r="Y29" s="25"/>
-      <c r="Z29" s="25"/>
-      <c r="AA29" s="26"/>
+      <c r="Y29" s="27"/>
+      <c r="Z29" s="27"/>
+      <c r="AA29" s="5"/>
       <c r="AB29" s="27"/>
       <c r="AC29" s="27"/>
-    </row>
-    <row r="30" s="23" customFormat="1" ht="16.5" spans="1:29">
+      <c r="AD29" s="25"/>
+      <c r="AE29" s="25"/>
+      <c r="AF29" s="25"/>
+      <c r="AG29" s="25"/>
+      <c r="AH29" s="25"/>
+      <c r="AI29" s="25"/>
+      <c r="AJ29" s="25"/>
+    </row>
+    <row r="30" s="24" customFormat="1" ht="16.5" spans="1:36">
       <c r="A30" s="2" t="s">
         <v>58</v>
       </c>
@@ -3563,51 +3873,58 @@
       <c r="D30" s="3"/>
       <c r="E30" s="3"/>
       <c r="F30" s="5"/>
-      <c r="G30" s="25">
+      <c r="G30" s="27">
         <v>450000</v>
       </c>
-      <c r="H30" s="25">
+      <c r="H30" s="27">
         <v>0</v>
       </c>
       <c r="I30" s="5"/>
-      <c r="J30" s="25">
+      <c r="J30" s="27">
         <v>480000</v>
       </c>
-      <c r="K30" s="25">
+      <c r="K30" s="27">
         <v>0</v>
       </c>
       <c r="L30" s="5"/>
-      <c r="M30" s="25">
+      <c r="M30" s="27">
         <v>500000</v>
       </c>
-      <c r="N30" s="25">
+      <c r="N30" s="27">
         <v>0</v>
       </c>
       <c r="O30" s="5"/>
-      <c r="P30" s="25">
+      <c r="P30" s="27">
         <v>510000</v>
       </c>
-      <c r="Q30" s="25">
+      <c r="Q30" s="27">
         <v>0</v>
       </c>
       <c r="R30" s="5"/>
-      <c r="S30" s="25">
+      <c r="S30" s="27">
         <v>510000</v>
       </c>
-      <c r="T30" s="25">
-        <v>730480.25</v>
+      <c r="T30" s="27">
+        <v>298480.25</v>
       </c>
       <c r="U30" s="5"/>
-      <c r="V30" s="25"/>
-      <c r="W30" s="25"/>
+      <c r="V30" s="27"/>
+      <c r="W30" s="27"/>
       <c r="X30" s="5"/>
-      <c r="Y30" s="25"/>
-      <c r="Z30" s="25"/>
-      <c r="AA30" s="26"/>
+      <c r="Y30" s="27"/>
+      <c r="Z30" s="27"/>
+      <c r="AA30" s="5"/>
       <c r="AB30" s="27"/>
       <c r="AC30" s="27"/>
-    </row>
-    <row r="31" s="23" customFormat="1" ht="16.5" spans="1:29">
+      <c r="AD30" s="25"/>
+      <c r="AE30" s="25"/>
+      <c r="AF30" s="25"/>
+      <c r="AG30" s="25"/>
+      <c r="AH30" s="25"/>
+      <c r="AI30" s="25"/>
+      <c r="AJ30" s="25"/>
+    </row>
+    <row r="31" s="24" customFormat="1" ht="16.5" spans="1:36">
       <c r="A31" s="2" t="s">
         <v>59</v>
       </c>
@@ -3620,51 +3937,58 @@
       <c r="D31" s="3"/>
       <c r="E31" s="3"/>
       <c r="F31" s="5"/>
-      <c r="G31" s="25">
+      <c r="G31" s="27">
         <v>440000</v>
       </c>
-      <c r="H31" s="25">
+      <c r="H31" s="27">
         <v>0</v>
       </c>
       <c r="I31" s="5"/>
-      <c r="J31" s="25">
+      <c r="J31" s="27">
         <v>450000</v>
       </c>
-      <c r="K31" s="25">
+      <c r="K31" s="27">
         <v>0</v>
       </c>
       <c r="L31" s="5"/>
-      <c r="M31" s="25">
+      <c r="M31" s="27">
         <v>470000</v>
       </c>
-      <c r="N31" s="25">
+      <c r="N31" s="27">
         <v>0</v>
       </c>
       <c r="O31" s="5"/>
-      <c r="P31" s="25">
+      <c r="P31" s="27">
         <v>500000</v>
       </c>
-      <c r="Q31" s="25">
+      <c r="Q31" s="27">
         <v>0</v>
       </c>
       <c r="R31" s="5"/>
-      <c r="S31" s="25">
+      <c r="S31" s="27">
         <v>510000</v>
       </c>
-      <c r="T31" s="25">
-        <v>52665147.13</v>
+      <c r="T31" s="27">
+        <v>24693147.13</v>
       </c>
       <c r="U31" s="5"/>
-      <c r="V31" s="25"/>
-      <c r="W31" s="25"/>
+      <c r="V31" s="27"/>
+      <c r="W31" s="27"/>
       <c r="X31" s="5"/>
-      <c r="Y31" s="25"/>
-      <c r="Z31" s="25"/>
-      <c r="AA31" s="26"/>
+      <c r="Y31" s="27"/>
+      <c r="Z31" s="27"/>
+      <c r="AA31" s="5"/>
       <c r="AB31" s="27"/>
       <c r="AC31" s="27"/>
-    </row>
-    <row r="32" s="23" customFormat="1" ht="16.5" spans="1:29">
+      <c r="AD31" s="25"/>
+      <c r="AE31" s="25"/>
+      <c r="AF31" s="25"/>
+      <c r="AG31" s="25"/>
+      <c r="AH31" s="25"/>
+      <c r="AI31" s="25"/>
+      <c r="AJ31" s="25"/>
+    </row>
+    <row r="32" s="24" customFormat="1" ht="16.5" spans="1:36">
       <c r="A32" s="2" t="s">
         <v>60</v>
       </c>
@@ -3677,47 +4001,54 @@
       <c r="D32" s="3"/>
       <c r="E32" s="3"/>
       <c r="F32" s="5"/>
-      <c r="G32" s="25">
+      <c r="G32" s="27">
         <v>460000</v>
       </c>
-      <c r="H32" s="25">
+      <c r="H32" s="27">
         <v>0</v>
       </c>
       <c r="I32" s="5"/>
-      <c r="J32" s="25">
+      <c r="J32" s="27">
         <v>470000</v>
       </c>
-      <c r="K32" s="25">
+      <c r="K32" s="27">
         <v>0</v>
       </c>
       <c r="L32" s="5"/>
-      <c r="M32" s="25">
+      <c r="M32" s="27">
         <v>520000</v>
       </c>
-      <c r="N32" s="25">
+      <c r="N32" s="27">
         <v>0</v>
       </c>
       <c r="O32" s="5"/>
-      <c r="P32" s="25">
+      <c r="P32" s="27">
         <v>530000</v>
       </c>
-      <c r="Q32" s="25">
+      <c r="Q32" s="27">
         <v>13259415</v>
       </c>
       <c r="R32" s="5"/>
-      <c r="S32" s="25"/>
-      <c r="T32" s="25"/>
+      <c r="S32" s="27"/>
+      <c r="T32" s="27"/>
       <c r="U32" s="5"/>
-      <c r="V32" s="25"/>
-      <c r="W32" s="25"/>
+      <c r="V32" s="27"/>
+      <c r="W32" s="27"/>
       <c r="X32" s="5"/>
-      <c r="Y32" s="25"/>
-      <c r="Z32" s="25"/>
-      <c r="AA32" s="26"/>
+      <c r="Y32" s="27"/>
+      <c r="Z32" s="27"/>
+      <c r="AA32" s="5"/>
       <c r="AB32" s="27"/>
       <c r="AC32" s="27"/>
-    </row>
-    <row r="33" s="23" customFormat="1" ht="16.5" spans="1:29">
+      <c r="AD32" s="25"/>
+      <c r="AE32" s="25"/>
+      <c r="AF32" s="25"/>
+      <c r="AG32" s="25"/>
+      <c r="AH32" s="25"/>
+      <c r="AI32" s="25"/>
+      <c r="AJ32" s="25"/>
+    </row>
+    <row r="33" s="24" customFormat="1" ht="16.5" spans="1:36">
       <c r="A33" s="2" t="s">
         <v>61</v>
       </c>
@@ -3730,43 +4061,50 @@
       <c r="D33" s="3"/>
       <c r="E33" s="3"/>
       <c r="F33" s="5"/>
-      <c r="G33" s="25">
+      <c r="G33" s="27">
         <v>440000</v>
       </c>
-      <c r="H33" s="25">
+      <c r="H33" s="27">
         <v>0</v>
       </c>
       <c r="I33" s="5"/>
-      <c r="J33" s="25">
+      <c r="J33" s="27">
         <v>450000</v>
       </c>
-      <c r="K33" s="25">
+      <c r="K33" s="27">
         <v>0</v>
       </c>
       <c r="L33" s="5"/>
-      <c r="M33" s="25">
+      <c r="M33" s="27">
         <v>470000</v>
       </c>
-      <c r="N33" s="25">
+      <c r="N33" s="27">
         <v>37198700</v>
       </c>
       <c r="O33" s="5"/>
-      <c r="P33" s="25"/>
-      <c r="Q33" s="25"/>
+      <c r="P33" s="27"/>
+      <c r="Q33" s="27"/>
       <c r="R33" s="5"/>
-      <c r="S33" s="25"/>
-      <c r="T33" s="25"/>
+      <c r="S33" s="27"/>
+      <c r="T33" s="27"/>
       <c r="U33" s="5"/>
-      <c r="V33" s="25"/>
-      <c r="W33" s="25"/>
+      <c r="V33" s="27"/>
+      <c r="W33" s="27"/>
       <c r="X33" s="5"/>
-      <c r="Y33" s="25"/>
-      <c r="Z33" s="25"/>
-      <c r="AA33" s="26"/>
+      <c r="Y33" s="27"/>
+      <c r="Z33" s="27"/>
+      <c r="AA33" s="5"/>
       <c r="AB33" s="27"/>
       <c r="AC33" s="27"/>
-    </row>
-    <row r="34" s="23" customFormat="1" ht="16.5" spans="1:29">
+      <c r="AD33" s="25"/>
+      <c r="AE33" s="25"/>
+      <c r="AF33" s="25"/>
+      <c r="AG33" s="25"/>
+      <c r="AH33" s="25"/>
+      <c r="AI33" s="25"/>
+      <c r="AJ33" s="25"/>
+    </row>
+    <row r="34" s="24" customFormat="1" ht="16.5" spans="1:36">
       <c r="A34" s="2" t="s">
         <v>62</v>
       </c>
@@ -3776,42 +4114,49 @@
       <c r="C34" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D34" s="30">
+      <c r="D34" s="6">
         <v>390000</v>
       </c>
-      <c r="E34" s="30">
+      <c r="E34" s="6">
         <v>200000</v>
       </c>
       <c r="F34" s="5"/>
-      <c r="G34" s="25">
+      <c r="G34" s="27">
         <v>440000</v>
       </c>
-      <c r="H34" s="25">
+      <c r="H34" s="27">
         <v>1023091.53</v>
       </c>
       <c r="I34" s="5"/>
-      <c r="J34" s="25"/>
-      <c r="K34" s="25"/>
+      <c r="J34" s="27"/>
+      <c r="K34" s="27"/>
       <c r="L34" s="5"/>
-      <c r="M34" s="25"/>
-      <c r="N34" s="25"/>
+      <c r="M34" s="27"/>
+      <c r="N34" s="27"/>
       <c r="O34" s="5"/>
-      <c r="P34" s="25"/>
-      <c r="Q34" s="25"/>
+      <c r="P34" s="27"/>
+      <c r="Q34" s="27"/>
       <c r="R34" s="5"/>
-      <c r="S34" s="25"/>
-      <c r="T34" s="25"/>
+      <c r="S34" s="27"/>
+      <c r="T34" s="27"/>
       <c r="U34" s="5"/>
-      <c r="V34" s="25"/>
-      <c r="W34" s="25"/>
+      <c r="V34" s="27"/>
+      <c r="W34" s="27"/>
       <c r="X34" s="5"/>
-      <c r="Y34" s="25"/>
-      <c r="Z34" s="25"/>
-      <c r="AA34" s="26"/>
+      <c r="Y34" s="27"/>
+      <c r="Z34" s="27"/>
+      <c r="AA34" s="5"/>
       <c r="AB34" s="27"/>
       <c r="AC34" s="27"/>
-    </row>
-    <row r="35" s="23" customFormat="1" ht="16.5" spans="1:29">
+      <c r="AD34" s="25"/>
+      <c r="AE34" s="25"/>
+      <c r="AF34" s="25"/>
+      <c r="AG34" s="25"/>
+      <c r="AH34" s="25"/>
+      <c r="AI34" s="25"/>
+      <c r="AJ34" s="25"/>
+    </row>
+    <row r="35" s="24" customFormat="1" ht="16.5" spans="1:36">
       <c r="A35" s="2" t="s">
         <v>63</v>
       </c>
@@ -3828,31 +4173,50 @@
         <v>170000</v>
       </c>
       <c r="F35" s="5"/>
-      <c r="G35" s="25"/>
-      <c r="H35" s="25"/>
+      <c r="G35" s="27">
+        <v>480000</v>
+      </c>
+      <c r="H35" s="27">
+        <v>0</v>
+      </c>
       <c r="I35" s="5"/>
-      <c r="J35" s="25"/>
-      <c r="K35" s="25"/>
+      <c r="J35" s="27">
+        <v>500000</v>
+      </c>
+      <c r="K35" s="27">
+        <v>0</v>
+      </c>
       <c r="L35" s="5"/>
-      <c r="M35" s="25"/>
-      <c r="N35" s="25"/>
+      <c r="M35" s="27">
+        <v>510000</v>
+      </c>
+      <c r="N35" s="27">
+        <v>35175485</v>
+      </c>
       <c r="O35" s="5"/>
-      <c r="P35" s="25"/>
-      <c r="Q35" s="25"/>
+      <c r="P35" s="27"/>
+      <c r="Q35" s="27"/>
       <c r="R35" s="5"/>
-      <c r="S35" s="25"/>
-      <c r="T35" s="25"/>
+      <c r="S35" s="27"/>
+      <c r="T35" s="27"/>
       <c r="U35" s="5"/>
-      <c r="V35" s="25"/>
-      <c r="W35" s="25"/>
+      <c r="V35" s="27"/>
+      <c r="W35" s="27"/>
       <c r="X35" s="5"/>
-      <c r="Y35" s="25"/>
-      <c r="Z35" s="25"/>
-      <c r="AA35" s="26"/>
+      <c r="Y35" s="27"/>
+      <c r="Z35" s="27"/>
+      <c r="AA35" s="5"/>
       <c r="AB35" s="27"/>
       <c r="AC35" s="27"/>
-    </row>
-    <row r="36" s="23" customFormat="1" ht="16.5" spans="1:29">
+      <c r="AD35" s="25"/>
+      <c r="AE35" s="25"/>
+      <c r="AF35" s="25"/>
+      <c r="AG35" s="25"/>
+      <c r="AH35" s="25"/>
+      <c r="AI35" s="25"/>
+      <c r="AJ35" s="25"/>
+    </row>
+    <row r="36" s="24" customFormat="1" ht="16.5" spans="1:36">
       <c r="A36" s="2" t="s">
         <v>64</v>
       </c>
@@ -3865,42 +4229,49 @@
       <c r="D36" s="6"/>
       <c r="E36" s="6"/>
       <c r="F36" s="5"/>
-      <c r="G36" s="31">
+      <c r="G36" s="27">
         <v>530000</v>
       </c>
-      <c r="H36" s="31">
+      <c r="H36" s="27">
         <v>0</v>
       </c>
       <c r="I36" s="5"/>
-      <c r="J36" s="31"/>
-      <c r="K36" s="31"/>
+      <c r="J36" s="27"/>
+      <c r="K36" s="27"/>
       <c r="L36" s="5"/>
-      <c r="M36" s="31"/>
-      <c r="N36" s="31"/>
+      <c r="M36" s="27"/>
+      <c r="N36" s="27"/>
       <c r="O36" s="5"/>
-      <c r="P36" s="31"/>
-      <c r="Q36" s="31"/>
+      <c r="P36" s="27"/>
+      <c r="Q36" s="27"/>
       <c r="R36" s="5"/>
-      <c r="S36" s="31"/>
-      <c r="T36" s="31"/>
+      <c r="S36" s="27"/>
+      <c r="T36" s="27"/>
       <c r="U36" s="5"/>
-      <c r="V36" s="25"/>
-      <c r="W36" s="25"/>
+      <c r="V36" s="27"/>
+      <c r="W36" s="27"/>
       <c r="X36" s="5"/>
-      <c r="Y36" s="25"/>
-      <c r="Z36" s="25"/>
-      <c r="AA36" s="26"/>
+      <c r="Y36" s="27"/>
+      <c r="Z36" s="27"/>
+      <c r="AA36" s="5"/>
       <c r="AB36" s="27"/>
       <c r="AC36" s="27"/>
-    </row>
-    <row r="37" s="23" customFormat="1" ht="16.5" spans="1:29">
+      <c r="AD36" s="25"/>
+      <c r="AE36" s="25"/>
+      <c r="AF36" s="25"/>
+      <c r="AG36" s="25"/>
+      <c r="AH36" s="25"/>
+      <c r="AI36" s="25"/>
+      <c r="AJ36" s="25"/>
+    </row>
+    <row r="37" s="24" customFormat="1" ht="16.5" spans="1:36">
       <c r="A37" s="2" t="s">
         <v>65</v>
       </c>
       <c r="B37" s="3">
         <v>510000</v>
       </c>
-      <c r="C37" s="32" t="s">
+      <c r="C37" s="29" t="s">
         <v>30</v>
       </c>
       <c r="D37" s="3">
@@ -3910,46 +4281,53 @@
         <v>170000</v>
       </c>
       <c r="F37" s="5"/>
-      <c r="G37" s="25">
-        <v>0</v>
-      </c>
-      <c r="H37" s="25">
+      <c r="G37" s="27">
+        <v>0</v>
+      </c>
+      <c r="H37" s="27">
         <v>0</v>
       </c>
       <c r="I37" s="5"/>
-      <c r="J37" s="25">
+      <c r="J37" s="27">
         <v>500000</v>
       </c>
-      <c r="K37" s="25">
-        <v>50155000</v>
+      <c r="K37" s="27">
+        <v>17818000</v>
       </c>
       <c r="L37" s="5"/>
-      <c r="M37" s="25"/>
-      <c r="N37" s="25"/>
+      <c r="M37" s="27"/>
+      <c r="N37" s="27"/>
       <c r="O37" s="5"/>
-      <c r="P37" s="25"/>
-      <c r="Q37" s="25"/>
+      <c r="P37" s="27"/>
+      <c r="Q37" s="27"/>
       <c r="R37" s="5"/>
-      <c r="S37" s="25"/>
-      <c r="T37" s="25"/>
+      <c r="S37" s="27"/>
+      <c r="T37" s="27"/>
       <c r="U37" s="5"/>
-      <c r="V37" s="25"/>
-      <c r="W37" s="25"/>
+      <c r="V37" s="27"/>
+      <c r="W37" s="27"/>
       <c r="X37" s="5"/>
-      <c r="Y37" s="25"/>
-      <c r="Z37" s="25"/>
-      <c r="AA37" s="26"/>
+      <c r="Y37" s="27"/>
+      <c r="Z37" s="27"/>
+      <c r="AA37" s="5"/>
       <c r="AB37" s="27"/>
       <c r="AC37" s="27"/>
-    </row>
-    <row r="38" s="23" customFormat="1" ht="16.5" spans="1:29">
+      <c r="AD37" s="25"/>
+      <c r="AE37" s="25"/>
+      <c r="AF37" s="25"/>
+      <c r="AG37" s="25"/>
+      <c r="AH37" s="25"/>
+      <c r="AI37" s="25"/>
+      <c r="AJ37" s="25"/>
+    </row>
+    <row r="38" s="24" customFormat="1" ht="16.5" spans="1:36">
       <c r="A38" s="2" t="s">
         <v>66</v>
       </c>
       <c r="B38" s="3">
         <v>500000</v>
       </c>
-      <c r="C38" s="32" t="s">
+      <c r="C38" s="29" t="s">
         <v>30</v>
       </c>
       <c r="D38" s="3">
@@ -3959,58 +4337,65 @@
         <v>170000</v>
       </c>
       <c r="F38" s="5"/>
-      <c r="G38" s="25">
+      <c r="G38" s="27">
         <v>440000</v>
       </c>
-      <c r="H38" s="25">
+      <c r="H38" s="27">
         <v>0</v>
       </c>
       <c r="I38" s="5"/>
-      <c r="J38" s="25">
+      <c r="J38" s="27">
         <v>460000</v>
       </c>
-      <c r="K38" s="25">
+      <c r="K38" s="27">
         <v>0</v>
       </c>
       <c r="L38" s="5"/>
-      <c r="M38" s="25">
+      <c r="M38" s="27">
         <v>470000</v>
       </c>
-      <c r="N38" s="25">
+      <c r="N38" s="27">
         <v>0</v>
       </c>
       <c r="O38" s="5"/>
-      <c r="P38" s="25">
+      <c r="P38" s="27">
         <v>490000</v>
       </c>
-      <c r="Q38" s="25">
-        <v>256450343</v>
+      <c r="Q38" s="27">
+        <v>137006543</v>
       </c>
       <c r="R38" s="5"/>
-      <c r="S38" s="25">
+      <c r="S38" s="27">
         <v>500000</v>
       </c>
-      <c r="T38" s="25">
+      <c r="T38" s="27">
         <v>500000000</v>
       </c>
       <c r="U38" s="5"/>
-      <c r="V38" s="25"/>
-      <c r="W38" s="25"/>
+      <c r="V38" s="27"/>
+      <c r="W38" s="27"/>
       <c r="X38" s="5"/>
-      <c r="Y38" s="25"/>
-      <c r="Z38" s="25"/>
-      <c r="AA38" s="26"/>
+      <c r="Y38" s="27"/>
+      <c r="Z38" s="27"/>
+      <c r="AA38" s="5"/>
       <c r="AB38" s="27"/>
       <c r="AC38" s="27"/>
-    </row>
-    <row r="39" s="23" customFormat="1" ht="16.5" spans="1:29">
+      <c r="AD38" s="25"/>
+      <c r="AE38" s="25"/>
+      <c r="AF38" s="25"/>
+      <c r="AG38" s="25"/>
+      <c r="AH38" s="25"/>
+      <c r="AI38" s="25"/>
+      <c r="AJ38" s="25"/>
+    </row>
+    <row r="39" s="24" customFormat="1" ht="16.5" spans="1:36">
       <c r="A39" s="2" t="s">
         <v>67</v>
       </c>
       <c r="B39" s="3">
         <v>500000</v>
       </c>
-      <c r="C39" s="32" t="s">
+      <c r="C39" s="29" t="s">
         <v>30</v>
       </c>
       <c r="D39" s="3">
@@ -4020,58 +4405,65 @@
         <v>170000</v>
       </c>
       <c r="F39" s="5"/>
-      <c r="G39" s="25">
+      <c r="G39" s="27">
         <v>440000</v>
       </c>
-      <c r="H39" s="25">
+      <c r="H39" s="27">
         <v>0</v>
       </c>
       <c r="I39" s="5"/>
-      <c r="J39" s="25">
+      <c r="J39" s="27">
         <v>460000</v>
       </c>
-      <c r="K39" s="25">
+      <c r="K39" s="27">
         <v>0</v>
       </c>
       <c r="L39" s="5"/>
-      <c r="M39" s="25">
+      <c r="M39" s="27">
         <v>470000</v>
       </c>
-      <c r="N39" s="25">
+      <c r="N39" s="27">
         <v>0</v>
       </c>
       <c r="O39" s="5"/>
-      <c r="P39" s="25">
+      <c r="P39" s="27">
         <v>490000</v>
       </c>
-      <c r="Q39" s="25">
-        <v>288862575.55</v>
+      <c r="Q39" s="27">
+        <v>204947735.55</v>
       </c>
       <c r="R39" s="5"/>
-      <c r="S39" s="25">
+      <c r="S39" s="27">
         <v>500000</v>
       </c>
-      <c r="T39" s="25">
+      <c r="T39" s="27">
         <v>500000000</v>
       </c>
       <c r="U39" s="5"/>
-      <c r="V39" s="25"/>
-      <c r="W39" s="25"/>
+      <c r="V39" s="27"/>
+      <c r="W39" s="27"/>
       <c r="X39" s="5"/>
-      <c r="Y39" s="25"/>
-      <c r="Z39" s="25"/>
-      <c r="AA39" s="26"/>
+      <c r="Y39" s="27"/>
+      <c r="Z39" s="27"/>
+      <c r="AA39" s="5"/>
       <c r="AB39" s="27"/>
       <c r="AC39" s="27"/>
-    </row>
-    <row r="40" s="23" customFormat="1" ht="16.5" spans="1:29">
+      <c r="AD39" s="25"/>
+      <c r="AE39" s="25"/>
+      <c r="AF39" s="25"/>
+      <c r="AG39" s="25"/>
+      <c r="AH39" s="25"/>
+      <c r="AI39" s="25"/>
+      <c r="AJ39" s="25"/>
+    </row>
+    <row r="40" s="24" customFormat="1" ht="16.5" spans="1:36">
       <c r="A40" s="2" t="s">
         <v>68</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C40" s="33" t="s">
+      <c r="C40" s="30" t="s">
         <v>70</v>
       </c>
       <c r="D40" s="3">
@@ -4081,46 +4473,53 @@
         <v>170000</v>
       </c>
       <c r="F40" s="5"/>
-      <c r="G40" s="25">
+      <c r="G40" s="27">
         <v>430000</v>
       </c>
-      <c r="H40" s="25">
+      <c r="H40" s="27">
         <v>0</v>
       </c>
       <c r="I40" s="5"/>
-      <c r="J40" s="25">
+      <c r="J40" s="27">
         <v>440000</v>
       </c>
-      <c r="K40" s="25">
+      <c r="K40" s="27">
         <v>68779183</v>
       </c>
       <c r="L40" s="5"/>
-      <c r="M40" s="25"/>
-      <c r="N40" s="25"/>
+      <c r="M40" s="27"/>
+      <c r="N40" s="27"/>
       <c r="O40" s="5"/>
-      <c r="P40" s="25"/>
-      <c r="Q40" s="25"/>
+      <c r="P40" s="27"/>
+      <c r="Q40" s="27"/>
       <c r="R40" s="5"/>
-      <c r="S40" s="25"/>
-      <c r="T40" s="25"/>
+      <c r="S40" s="27"/>
+      <c r="T40" s="27"/>
       <c r="U40" s="5"/>
-      <c r="V40" s="25"/>
-      <c r="W40" s="25"/>
+      <c r="V40" s="27"/>
+      <c r="W40" s="27"/>
       <c r="X40" s="5"/>
-      <c r="Y40" s="25"/>
-      <c r="Z40" s="25"/>
-      <c r="AA40" s="26"/>
+      <c r="Y40" s="27"/>
+      <c r="Z40" s="27"/>
+      <c r="AA40" s="5"/>
       <c r="AB40" s="27"/>
       <c r="AC40" s="27"/>
-    </row>
-    <row r="41" s="23" customFormat="1" ht="16.5" spans="1:29">
+      <c r="AD40" s="25"/>
+      <c r="AE40" s="25"/>
+      <c r="AF40" s="25"/>
+      <c r="AG40" s="25"/>
+      <c r="AH40" s="25"/>
+      <c r="AI40" s="25"/>
+      <c r="AJ40" s="25"/>
+    </row>
+    <row r="41" s="24" customFormat="1" ht="16.5" spans="1:36">
       <c r="A41" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C41" s="33" t="s">
+      <c r="C41" s="30" t="s">
         <v>70</v>
       </c>
       <c r="D41" s="3">
@@ -4130,246 +4529,732 @@
         <v>170000</v>
       </c>
       <c r="F41" s="5"/>
-      <c r="G41" s="25">
+      <c r="G41" s="27">
         <v>430000</v>
       </c>
-      <c r="H41" s="25">
+      <c r="H41" s="27">
         <v>0</v>
       </c>
       <c r="I41" s="5"/>
-      <c r="J41" s="25">
+      <c r="J41" s="27">
         <v>440000</v>
       </c>
-      <c r="K41" s="25">
+      <c r="K41" s="27">
         <v>48922249.3</v>
       </c>
       <c r="L41" s="5"/>
-      <c r="M41" s="25"/>
-      <c r="N41" s="25"/>
+      <c r="M41" s="27"/>
+      <c r="N41" s="27"/>
       <c r="O41" s="5"/>
-      <c r="P41" s="25"/>
-      <c r="Q41" s="25"/>
+      <c r="P41" s="27"/>
+      <c r="Q41" s="27"/>
       <c r="R41" s="5"/>
-      <c r="S41" s="25"/>
-      <c r="T41" s="25"/>
+      <c r="S41" s="27"/>
+      <c r="T41" s="27"/>
       <c r="U41" s="5"/>
-      <c r="V41" s="25"/>
-      <c r="W41" s="25"/>
+      <c r="V41" s="27"/>
+      <c r="W41" s="27"/>
       <c r="X41" s="5"/>
-      <c r="Y41" s="25"/>
-      <c r="Z41" s="25"/>
-      <c r="AA41" s="26"/>
+      <c r="Y41" s="27"/>
+      <c r="Z41" s="27"/>
+      <c r="AA41" s="5"/>
       <c r="AB41" s="27"/>
       <c r="AC41" s="27"/>
-    </row>
-    <row r="42" s="23" customFormat="1" ht="16.5" spans="1:29">
-      <c r="A42" s="34" t="s">
+      <c r="AD41" s="25"/>
+      <c r="AE41" s="25"/>
+      <c r="AF41" s="25"/>
+      <c r="AG41" s="25"/>
+      <c r="AH41" s="25"/>
+      <c r="AI41" s="25"/>
+      <c r="AJ41" s="25"/>
+    </row>
+    <row r="42" s="24" customFormat="1" ht="16.5" spans="1:36">
+      <c r="A42" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="B42" s="35">
+      <c r="B42" s="3">
         <v>530000</v>
       </c>
-      <c r="C42" s="36" t="s">
+      <c r="C42" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="D42" s="35"/>
-      <c r="E42" s="35"/>
-      <c r="F42" s="26"/>
-      <c r="G42" s="37">
+      <c r="D42" s="3"/>
+      <c r="E42" s="3"/>
+      <c r="F42" s="5"/>
+      <c r="G42" s="27">
         <v>540000</v>
       </c>
-      <c r="H42" s="37">
-        <v>0</v>
-      </c>
-      <c r="I42" s="26"/>
-      <c r="J42" s="37"/>
-      <c r="K42" s="37"/>
-      <c r="L42" s="26"/>
-      <c r="M42" s="37"/>
-      <c r="N42" s="37"/>
-      <c r="O42" s="26"/>
-      <c r="P42" s="37"/>
-      <c r="Q42" s="37"/>
-      <c r="R42" s="26"/>
-      <c r="S42" s="37"/>
-      <c r="T42" s="37"/>
-      <c r="U42" s="26"/>
-      <c r="V42" s="37"/>
-      <c r="W42" s="37"/>
-      <c r="X42" s="26"/>
-      <c r="Y42" s="37"/>
-      <c r="Z42" s="37"/>
-      <c r="AA42" s="26"/>
+      <c r="H42" s="27">
+        <v>0</v>
+      </c>
+      <c r="I42" s="5"/>
+      <c r="J42" s="27"/>
+      <c r="K42" s="27"/>
+      <c r="L42" s="5"/>
+      <c r="M42" s="27"/>
+      <c r="N42" s="27"/>
+      <c r="O42" s="5"/>
+      <c r="P42" s="27"/>
+      <c r="Q42" s="27"/>
+      <c r="R42" s="5"/>
+      <c r="S42" s="27"/>
+      <c r="T42" s="27"/>
+      <c r="U42" s="5"/>
+      <c r="V42" s="27"/>
+      <c r="W42" s="27"/>
+      <c r="X42" s="5"/>
+      <c r="Y42" s="27"/>
+      <c r="Z42" s="27"/>
+      <c r="AA42" s="5"/>
       <c r="AB42" s="27"/>
       <c r="AC42" s="27"/>
-    </row>
-    <row r="43" s="23" customFormat="1" ht="16.5" spans="1:29">
-      <c r="A43" s="34" t="s">
+      <c r="AD42" s="25"/>
+      <c r="AE42" s="25"/>
+      <c r="AF42" s="25"/>
+      <c r="AG42" s="25"/>
+      <c r="AH42" s="25"/>
+      <c r="AI42" s="25"/>
+      <c r="AJ42" s="25"/>
+    </row>
+    <row r="43" s="24" customFormat="1" ht="16.5" spans="1:36">
+      <c r="A43" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B43" s="35">
+      <c r="B43" s="3">
         <v>520000</v>
       </c>
-      <c r="C43" s="36" t="s">
+      <c r="C43" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="D43" s="35"/>
-      <c r="E43" s="35"/>
-      <c r="F43" s="26"/>
-      <c r="G43" s="37">
-        <v>520000</v>
-      </c>
-      <c r="H43" s="37">
-        <v>0</v>
-      </c>
-      <c r="I43" s="26"/>
-      <c r="J43" s="37"/>
-      <c r="K43" s="37"/>
-      <c r="L43" s="26"/>
-      <c r="M43" s="37"/>
-      <c r="N43" s="37"/>
-      <c r="O43" s="26"/>
-      <c r="P43" s="37"/>
-      <c r="Q43" s="37"/>
-      <c r="R43" s="26"/>
-      <c r="S43" s="37"/>
-      <c r="T43" s="37"/>
-      <c r="U43" s="26"/>
-      <c r="V43" s="37"/>
-      <c r="W43" s="37"/>
-      <c r="X43" s="26"/>
-      <c r="Y43" s="37"/>
-      <c r="Z43" s="37"/>
-      <c r="AA43" s="26"/>
+      <c r="D43" s="3"/>
+      <c r="E43" s="3"/>
+      <c r="F43" s="5"/>
+      <c r="G43" s="27">
+        <v>500000</v>
+      </c>
+      <c r="H43" s="27">
+        <v>0</v>
+      </c>
+      <c r="I43" s="5"/>
+      <c r="J43" s="27"/>
+      <c r="K43" s="27"/>
+      <c r="L43" s="5"/>
+      <c r="M43" s="27"/>
+      <c r="N43" s="27"/>
+      <c r="O43" s="5"/>
+      <c r="P43" s="27"/>
+      <c r="Q43" s="27"/>
+      <c r="R43" s="5"/>
+      <c r="S43" s="27"/>
+      <c r="T43" s="27"/>
+      <c r="U43" s="5"/>
+      <c r="V43" s="27"/>
+      <c r="W43" s="27"/>
+      <c r="X43" s="5"/>
+      <c r="Y43" s="27"/>
+      <c r="Z43" s="27"/>
+      <c r="AA43" s="5"/>
       <c r="AB43" s="27"/>
       <c r="AC43" s="27"/>
-    </row>
-    <row r="44" s="23" customFormat="1" ht="16.5" spans="1:29">
-      <c r="A44" s="34" t="s">
+      <c r="AD43" s="25"/>
+      <c r="AE43" s="25"/>
+      <c r="AF43" s="25"/>
+      <c r="AG43" s="25"/>
+      <c r="AH43" s="25"/>
+      <c r="AI43" s="25"/>
+      <c r="AJ43" s="25"/>
+    </row>
+    <row r="44" s="24" customFormat="1" ht="16.5" spans="1:36">
+      <c r="A44" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="B44" s="35">
-        <v>530000</v>
-      </c>
-      <c r="C44" s="38" t="s">
-        <v>70</v>
-      </c>
-      <c r="D44" s="35"/>
-      <c r="E44" s="35"/>
-      <c r="F44" s="26"/>
-      <c r="G44" s="37">
-        <v>540</v>
-      </c>
-      <c r="H44" s="37">
-        <v>0</v>
-      </c>
-      <c r="I44" s="26"/>
-      <c r="J44" s="37"/>
-      <c r="K44" s="37"/>
-      <c r="L44" s="26"/>
-      <c r="M44" s="37"/>
-      <c r="N44" s="37"/>
-      <c r="O44" s="26"/>
-      <c r="P44" s="37"/>
-      <c r="Q44" s="37"/>
-      <c r="R44" s="26"/>
-      <c r="S44" s="37"/>
-      <c r="T44" s="37"/>
-      <c r="U44" s="26"/>
-      <c r="V44" s="37"/>
-      <c r="W44" s="37"/>
-      <c r="X44" s="26"/>
-      <c r="Y44" s="37"/>
-      <c r="Z44" s="37"/>
-      <c r="AA44" s="26"/>
+      <c r="B44" s="3">
+        <v>510000</v>
+      </c>
+      <c r="C44" s="29" t="s">
+        <v>30</v>
+      </c>
+      <c r="D44" s="3">
+        <v>390000</v>
+      </c>
+      <c r="E44" s="3">
+        <v>200000</v>
+      </c>
+      <c r="F44" s="5"/>
+      <c r="G44" s="27">
+        <v>510000</v>
+      </c>
+      <c r="H44" s="27">
+        <v>132256715</v>
+      </c>
+      <c r="I44" s="5"/>
+      <c r="J44" s="27"/>
+      <c r="K44" s="27"/>
+      <c r="L44" s="5"/>
+      <c r="M44" s="27"/>
+      <c r="N44" s="27"/>
+      <c r="O44" s="5"/>
+      <c r="P44" s="27"/>
+      <c r="Q44" s="27"/>
+      <c r="R44" s="5"/>
+      <c r="S44" s="27"/>
+      <c r="T44" s="27"/>
+      <c r="U44" s="5"/>
+      <c r="V44" s="27"/>
+      <c r="W44" s="27"/>
+      <c r="X44" s="5"/>
+      <c r="Y44" s="27"/>
+      <c r="Z44" s="27"/>
+      <c r="AA44" s="5"/>
       <c r="AB44" s="27"/>
       <c r="AC44" s="27"/>
-    </row>
-    <row r="45" s="23" customFormat="1" ht="16.5" spans="1:29">
-      <c r="A45" s="34" t="s">
+      <c r="AD44" s="25"/>
+      <c r="AE44" s="25"/>
+      <c r="AF44" s="25"/>
+      <c r="AG44" s="25"/>
+      <c r="AH44" s="25"/>
+      <c r="AI44" s="25"/>
+      <c r="AJ44" s="25"/>
+    </row>
+    <row r="45" ht="16.5" spans="1:36">
+      <c r="A45" s="31" t="s">
         <v>75</v>
       </c>
-      <c r="B45" s="35" t="s">
-        <v>69</v>
-      </c>
-      <c r="C45" s="38" t="s">
+      <c r="B45" s="32"/>
+      <c r="C45" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="D45" s="32"/>
+      <c r="E45" s="32"/>
+      <c r="F45" s="34"/>
+      <c r="G45" s="35">
+        <v>545000</v>
+      </c>
+      <c r="H45" s="35">
+        <v>246617600</v>
+      </c>
+      <c r="I45" s="34"/>
+      <c r="J45" s="35"/>
+      <c r="K45" s="35"/>
+      <c r="L45" s="34"/>
+      <c r="M45" s="35"/>
+      <c r="N45" s="35"/>
+      <c r="O45" s="34"/>
+      <c r="P45" s="35"/>
+      <c r="Q45" s="35"/>
+      <c r="R45" s="34"/>
+      <c r="S45" s="35"/>
+      <c r="T45" s="35"/>
+      <c r="U45" s="34"/>
+      <c r="V45" s="35"/>
+      <c r="W45" s="35"/>
+      <c r="X45" s="34"/>
+      <c r="Y45" s="35"/>
+      <c r="Z45" s="35"/>
+      <c r="AA45" s="34"/>
+      <c r="AB45" s="35"/>
+      <c r="AC45" s="35"/>
+    </row>
+    <row r="46" ht="16.5" spans="1:36">
+      <c r="A46" s="31" t="s">
+        <v>76</v>
+      </c>
+      <c r="B46" s="32">
+        <v>530000</v>
+      </c>
+      <c r="C46" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="D46" s="32"/>
+      <c r="E46" s="32"/>
+      <c r="F46" s="34"/>
+      <c r="G46" s="35">
+        <v>530000</v>
+      </c>
+      <c r="H46" s="35">
+        <v>0</v>
+      </c>
+      <c r="I46" s="34"/>
+      <c r="J46" s="35"/>
+      <c r="K46" s="35"/>
+      <c r="L46" s="34"/>
+      <c r="M46" s="35"/>
+      <c r="N46" s="35"/>
+      <c r="O46" s="34"/>
+      <c r="P46" s="35"/>
+      <c r="Q46" s="35"/>
+      <c r="R46" s="34"/>
+      <c r="S46" s="35"/>
+      <c r="T46" s="35"/>
+      <c r="U46" s="34"/>
+      <c r="V46" s="35"/>
+      <c r="W46" s="35"/>
+      <c r="X46" s="34"/>
+      <c r="Y46" s="35"/>
+      <c r="Z46" s="35"/>
+      <c r="AA46" s="34"/>
+      <c r="AB46" s="35"/>
+      <c r="AC46" s="35"/>
+    </row>
+    <row r="47" ht="16.5" spans="1:36">
+      <c r="A47" s="31" t="s">
+        <v>77</v>
+      </c>
+      <c r="B47" s="32"/>
+      <c r="C47" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="D47" s="32"/>
+      <c r="E47" s="32"/>
+      <c r="F47" s="34"/>
+      <c r="G47" s="35">
+        <v>500000</v>
+      </c>
+      <c r="H47" s="35">
+        <v>0</v>
+      </c>
+      <c r="I47" s="34"/>
+      <c r="J47" s="35">
+        <v>520000</v>
+      </c>
+      <c r="K47" s="35">
+        <v>0</v>
+      </c>
+      <c r="L47" s="34"/>
+      <c r="M47" s="35"/>
+      <c r="N47" s="35"/>
+      <c r="O47" s="34"/>
+      <c r="P47" s="35"/>
+      <c r="Q47" s="35"/>
+      <c r="R47" s="34"/>
+      <c r="S47" s="35"/>
+      <c r="T47" s="35"/>
+      <c r="U47" s="34"/>
+      <c r="V47" s="35"/>
+      <c r="W47" s="35"/>
+      <c r="X47" s="34"/>
+      <c r="Y47" s="35"/>
+      <c r="Z47" s="35"/>
+      <c r="AA47" s="34"/>
+      <c r="AB47" s="35"/>
+      <c r="AC47" s="35"/>
+    </row>
+    <row r="48" ht="16.5" spans="1:36">
+      <c r="A48" s="31" t="s">
+        <v>78</v>
+      </c>
+      <c r="B48" s="32">
+        <v>520000</v>
+      </c>
+      <c r="C48" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="D48" s="32"/>
+      <c r="E48" s="32"/>
+      <c r="F48" s="34"/>
+      <c r="G48" s="35">
+        <v>480000</v>
+      </c>
+      <c r="H48" s="35">
+        <v>0</v>
+      </c>
+      <c r="I48" s="34"/>
+      <c r="J48" s="35">
+        <v>510000</v>
+      </c>
+      <c r="K48" s="35">
+        <v>0</v>
+      </c>
+      <c r="L48" s="34"/>
+      <c r="M48" s="35">
+        <v>530000</v>
+      </c>
+      <c r="N48" s="35">
+        <v>0</v>
+      </c>
+      <c r="O48" s="34"/>
+      <c r="P48" s="35">
+        <v>520000</v>
+      </c>
+      <c r="Q48" s="35">
+        <v>196166780</v>
+      </c>
+      <c r="R48" s="34"/>
+      <c r="S48" s="35"/>
+      <c r="T48" s="35"/>
+      <c r="U48" s="34"/>
+      <c r="V48" s="35"/>
+      <c r="W48" s="35"/>
+      <c r="X48" s="34"/>
+      <c r="Y48" s="35"/>
+      <c r="Z48" s="35"/>
+      <c r="AA48" s="34"/>
+      <c r="AB48" s="35"/>
+      <c r="AC48" s="35"/>
+    </row>
+    <row r="49" ht="16.5" spans="1:29">
+      <c r="A49" s="31" t="s">
+        <v>79</v>
+      </c>
+      <c r="B49" s="32"/>
+      <c r="C49" s="36" t="s">
         <v>70</v>
       </c>
-      <c r="D45" s="35"/>
-      <c r="E45" s="35"/>
-      <c r="F45" s="26"/>
-      <c r="G45" s="37">
+      <c r="D49" s="32"/>
+      <c r="E49" s="32"/>
+      <c r="F49" s="34"/>
+      <c r="G49" s="35">
+        <v>565000</v>
+      </c>
+      <c r="H49" s="35">
+        <v>0</v>
+      </c>
+      <c r="I49" s="34"/>
+      <c r="J49" s="35">
+        <v>585000</v>
+      </c>
+      <c r="K49" s="37">
+        <v>-88720000</v>
+      </c>
+      <c r="L49" s="34"/>
+      <c r="M49" s="35"/>
+      <c r="N49" s="35"/>
+      <c r="O49" s="34"/>
+      <c r="P49" s="35"/>
+      <c r="Q49" s="35"/>
+      <c r="R49" s="34"/>
+      <c r="S49" s="35"/>
+      <c r="T49" s="35"/>
+      <c r="U49" s="34"/>
+      <c r="V49" s="35"/>
+      <c r="W49" s="35"/>
+      <c r="X49" s="34"/>
+      <c r="Y49" s="35"/>
+      <c r="Z49" s="35"/>
+      <c r="AA49" s="34"/>
+      <c r="AB49" s="35"/>
+      <c r="AC49" s="35"/>
+    </row>
+    <row r="50" ht="16.5" spans="1:29">
+      <c r="A50" s="31" t="s">
+        <v>80</v>
+      </c>
+      <c r="B50" s="32"/>
+      <c r="C50" s="36" t="s">
+        <v>70</v>
+      </c>
+      <c r="D50" s="32"/>
+      <c r="E50" s="32"/>
+      <c r="F50" s="34"/>
+      <c r="G50" s="35">
+        <v>440</v>
+      </c>
+      <c r="H50" s="35">
+        <v>0</v>
+      </c>
+      <c r="I50" s="34"/>
+      <c r="J50" s="35">
+        <v>-22952160</v>
+      </c>
+      <c r="K50" s="35">
+        <v>0</v>
+      </c>
+      <c r="L50" s="34"/>
+      <c r="M50" s="35">
+        <v>460</v>
+      </c>
+      <c r="N50" s="35">
+        <v>0</v>
+      </c>
+      <c r="O50" s="34"/>
+      <c r="P50" s="35">
+        <v>470000</v>
+      </c>
+      <c r="Q50" s="37">
+        <v>-84390960</v>
+      </c>
+      <c r="R50" s="34"/>
+      <c r="S50" s="35"/>
+      <c r="T50" s="35"/>
+      <c r="U50" s="34"/>
+      <c r="V50" s="35"/>
+      <c r="W50" s="35"/>
+      <c r="X50" s="34"/>
+      <c r="Y50" s="35"/>
+      <c r="Z50" s="35"/>
+      <c r="AA50" s="34"/>
+      <c r="AB50" s="35"/>
+      <c r="AC50" s="35"/>
+    </row>
+    <row r="51" ht="16.5" spans="1:29">
+      <c r="A51" s="31" t="s">
+        <v>81</v>
+      </c>
+      <c r="B51" s="32"/>
+      <c r="C51" s="36" t="s">
+        <v>70</v>
+      </c>
+      <c r="D51" s="32"/>
+      <c r="E51" s="32"/>
+      <c r="F51" s="34"/>
+      <c r="G51" s="35">
+        <v>420000</v>
+      </c>
+      <c r="H51" s="35">
+        <v>0</v>
+      </c>
+      <c r="I51" s="34"/>
+      <c r="J51" s="35">
+        <v>460000</v>
+      </c>
+      <c r="K51" s="37">
+        <v>-428768000</v>
+      </c>
+      <c r="L51" s="34"/>
+      <c r="M51" s="35"/>
+      <c r="N51" s="35"/>
+      <c r="O51" s="34"/>
+      <c r="P51" s="35"/>
+      <c r="Q51" s="35"/>
+      <c r="R51" s="34"/>
+      <c r="S51" s="35"/>
+      <c r="T51" s="35"/>
+      <c r="U51" s="34"/>
+      <c r="V51" s="35"/>
+      <c r="W51" s="35"/>
+      <c r="X51" s="34"/>
+      <c r="Y51" s="35"/>
+      <c r="Z51" s="35"/>
+      <c r="AA51" s="34"/>
+      <c r="AB51" s="35"/>
+      <c r="AC51" s="35"/>
+    </row>
+    <row r="52" ht="16.5" spans="1:29">
+      <c r="A52" s="31" t="s">
+        <v>82</v>
+      </c>
+      <c r="B52" s="32"/>
+      <c r="C52" s="36" t="s">
+        <v>70</v>
+      </c>
+      <c r="D52" s="32"/>
+      <c r="E52" s="32"/>
+      <c r="F52" s="34"/>
+      <c r="G52" s="35">
+        <v>495000</v>
+      </c>
+      <c r="H52" s="35">
+        <v>0</v>
+      </c>
+      <c r="I52" s="34"/>
+      <c r="J52" s="35"/>
+      <c r="K52" s="35"/>
+      <c r="L52" s="34"/>
+      <c r="M52" s="35"/>
+      <c r="N52" s="35"/>
+      <c r="O52" s="34"/>
+      <c r="P52" s="35"/>
+      <c r="Q52" s="35"/>
+      <c r="R52" s="34"/>
+      <c r="S52" s="35"/>
+      <c r="T52" s="35"/>
+      <c r="U52" s="34"/>
+      <c r="V52" s="35"/>
+      <c r="W52" s="35"/>
+      <c r="X52" s="34"/>
+      <c r="Y52" s="35"/>
+      <c r="Z52" s="35"/>
+      <c r="AA52" s="34"/>
+      <c r="AB52" s="35"/>
+      <c r="AC52" s="35"/>
+    </row>
+    <row r="53" ht="16.5" spans="1:29">
+      <c r="A53" s="31" t="s">
+        <v>83</v>
+      </c>
+      <c r="B53" s="32"/>
+      <c r="C53" s="36" t="s">
+        <v>70</v>
+      </c>
+      <c r="D53" s="32"/>
+      <c r="E53" s="32"/>
+      <c r="F53" s="34"/>
+      <c r="G53" s="35">
+        <v>590</v>
+      </c>
+      <c r="H53" s="37">
+        <v>-7434000</v>
+      </c>
+      <c r="I53" s="34"/>
+      <c r="J53" s="35"/>
+      <c r="K53" s="35"/>
+      <c r="L53" s="34"/>
+      <c r="M53" s="35"/>
+      <c r="N53" s="35"/>
+      <c r="O53" s="34"/>
+      <c r="P53" s="35"/>
+      <c r="Q53" s="35"/>
+      <c r="R53" s="34"/>
+      <c r="S53" s="35"/>
+      <c r="T53" s="35"/>
+      <c r="U53" s="34"/>
+      <c r="V53" s="35"/>
+      <c r="W53" s="35"/>
+      <c r="X53" s="34"/>
+      <c r="Y53" s="35"/>
+      <c r="Z53" s="35"/>
+      <c r="AA53" s="34"/>
+      <c r="AB53" s="35"/>
+      <c r="AC53" s="35"/>
+    </row>
+    <row r="54" ht="16.5" spans="1:29">
+      <c r="A54" s="31" t="s">
+        <v>84</v>
+      </c>
+      <c r="B54" s="32">
+        <v>530000</v>
+      </c>
+      <c r="C54" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="D54" s="32"/>
+      <c r="E54" s="32"/>
+      <c r="F54" s="34"/>
+      <c r="G54" s="35">
+        <v>460000</v>
+      </c>
+      <c r="H54" s="35">
+        <v>0</v>
+      </c>
+      <c r="I54" s="34"/>
+      <c r="J54" s="35">
+        <v>520000</v>
+      </c>
+      <c r="K54" s="35">
+        <v>36005758</v>
+      </c>
+      <c r="L54" s="34"/>
+      <c r="M54" s="35">
+        <v>540000</v>
+      </c>
+      <c r="N54" s="35">
+        <v>50000000</v>
+      </c>
+      <c r="O54" s="34"/>
+      <c r="P54" s="35"/>
+      <c r="Q54" s="35"/>
+      <c r="R54" s="34"/>
+      <c r="S54" s="35"/>
+      <c r="T54" s="35"/>
+      <c r="U54" s="34"/>
+      <c r="V54" s="35"/>
+      <c r="W54" s="35"/>
+      <c r="X54" s="34"/>
+      <c r="Y54" s="35"/>
+      <c r="Z54" s="35"/>
+      <c r="AA54" s="34"/>
+      <c r="AB54" s="35"/>
+      <c r="AC54" s="35"/>
+    </row>
+    <row r="55" ht="16.5" spans="1:29">
+      <c r="A55" s="31" t="s">
+        <v>85</v>
+      </c>
+      <c r="B55" s="32">
+        <v>510000</v>
+      </c>
+      <c r="C55" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="D55" s="32"/>
+      <c r="E55" s="32"/>
+      <c r="F55" s="34"/>
+      <c r="G55" s="35">
+        <v>450000</v>
+      </c>
+      <c r="H55" s="35">
+        <v>0</v>
+      </c>
+      <c r="I55" s="34"/>
+      <c r="J55" s="35">
+        <v>470000</v>
+      </c>
+      <c r="K55" s="35">
+        <v>0</v>
+      </c>
+      <c r="L55" s="34"/>
+      <c r="M55" s="35">
+        <v>480000</v>
+      </c>
+      <c r="N55" s="35">
+        <v>0</v>
+      </c>
+      <c r="O55" s="34"/>
+      <c r="P55" s="35">
+        <v>490000</v>
+      </c>
+      <c r="Q55" s="35">
+        <v>0</v>
+      </c>
+      <c r="R55" s="34"/>
+      <c r="S55" s="35">
+        <v>500000</v>
+      </c>
+      <c r="T55" s="35">
+        <v>0</v>
+      </c>
+      <c r="U55" s="34"/>
+      <c r="V55" s="35">
+        <v>520000</v>
+      </c>
+      <c r="W55" s="35">
+        <v>101780710</v>
+      </c>
+      <c r="X55" s="34"/>
+      <c r="Y55" s="35"/>
+      <c r="Z55" s="35"/>
+      <c r="AA55" s="34"/>
+      <c r="AB55" s="35"/>
+      <c r="AC55" s="35"/>
+    </row>
+    <row r="56" ht="16.5" spans="1:29">
+      <c r="A56" s="31" t="s">
+        <v>86</v>
+      </c>
+      <c r="B56" s="32"/>
+      <c r="C56" s="36" t="s">
+        <v>70</v>
+      </c>
+      <c r="D56" s="32"/>
+      <c r="E56" s="32"/>
+      <c r="F56" s="34"/>
+      <c r="G56" s="35">
         <v>540</v>
       </c>
-      <c r="H45" s="37">
-        <v>0</v>
-      </c>
-      <c r="I45" s="26"/>
-      <c r="J45" s="37"/>
-      <c r="K45" s="37"/>
-      <c r="L45" s="26"/>
-      <c r="M45" s="37"/>
-      <c r="N45" s="37"/>
-      <c r="O45" s="26"/>
-      <c r="P45" s="37"/>
-      <c r="Q45" s="37"/>
-      <c r="R45" s="26"/>
-      <c r="S45" s="37"/>
-      <c r="T45" s="37"/>
-      <c r="U45" s="26"/>
-      <c r="V45" s="37"/>
-      <c r="W45" s="37"/>
-      <c r="X45" s="26"/>
-      <c r="Y45" s="37"/>
-      <c r="Z45" s="37"/>
-      <c r="AA45" s="26"/>
-      <c r="AB45" s="27"/>
-      <c r="AC45" s="27"/>
-    </row>
-    <row r="46" s="23" customFormat="1" ht="16.5" spans="1:29">
-      <c r="A46" s="34" t="s">
-        <v>76</v>
-      </c>
-      <c r="B46" s="3">
-        <v>520000</v>
-      </c>
-      <c r="C46" s="36" t="s">
-        <v>30</v>
-      </c>
-      <c r="D46" s="3">
-        <v>390000</v>
-      </c>
-      <c r="E46" s="3">
-        <v>200000</v>
-      </c>
-      <c r="F46" s="26"/>
-      <c r="G46" s="37">
-        <v>520000</v>
-      </c>
-      <c r="H46" s="37">
-        <v>154231115</v>
-      </c>
-      <c r="I46" s="26"/>
-      <c r="J46" s="37"/>
-      <c r="K46" s="37"/>
-      <c r="L46" s="26"/>
-      <c r="M46" s="37"/>
-      <c r="N46" s="37"/>
-      <c r="O46" s="26"/>
-      <c r="P46" s="37"/>
-      <c r="Q46" s="37"/>
-      <c r="R46" s="26"/>
-      <c r="S46" s="37"/>
-      <c r="T46" s="37"/>
-      <c r="U46" s="26"/>
-      <c r="V46" s="37"/>
-      <c r="W46" s="37"/>
-      <c r="X46" s="26"/>
-      <c r="Y46" s="37"/>
-      <c r="Z46" s="37"/>
-      <c r="AA46" s="26"/>
-      <c r="AB46" s="27"/>
-      <c r="AC46" s="27"/>
+      <c r="H56" s="35">
+        <v>0</v>
+      </c>
+      <c r="I56" s="34"/>
+      <c r="J56" s="35"/>
+      <c r="K56" s="35"/>
+      <c r="L56" s="34"/>
+      <c r="M56" s="35"/>
+      <c r="N56" s="35"/>
+      <c r="O56" s="34"/>
+      <c r="P56" s="35"/>
+      <c r="Q56" s="35"/>
+      <c r="R56" s="34"/>
+      <c r="S56" s="35"/>
+      <c r="T56" s="35"/>
+      <c r="U56" s="34"/>
+      <c r="V56" s="35"/>
+      <c r="W56" s="35"/>
+      <c r="X56" s="34"/>
+      <c r="Y56" s="35"/>
+      <c r="Z56" s="35"/>
+      <c r="AA56" s="34"/>
+      <c r="AB56" s="35"/>
+      <c r="AC56" s="35"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4384,298 +5269,298 @@
   <dimension ref="A1:D23"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="23" style="17" customWidth="1"/>
-    <col min="2" max="2" width="23.25" style="17" customWidth="1"/>
-    <col min="3" max="3" width="31.625" style="17" customWidth="1"/>
-    <col min="4" max="4" width="23.875" style="17" customWidth="1"/>
-    <col min="5" max="16384" width="9" style="17"/>
+    <col min="1" max="1" width="23" style="18" customWidth="1"/>
+    <col min="2" max="2" width="23.25" style="18" customWidth="1"/>
+    <col min="3" max="3" width="31.625" style="18" customWidth="1"/>
+    <col min="4" max="4" width="23.875" style="18" customWidth="1"/>
+    <col min="5" max="16384" width="9" style="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="33.75" customHeight="1" spans="1:4">
-      <c r="A1" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
+      <c r="A1" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
     </row>
     <row r="2" ht="36.75" customHeight="1" spans="1:4">
-      <c r="A2" s="19" t="s">
-        <v>78</v>
-      </c>
-      <c r="B2" s="19" t="s">
-        <v>79</v>
-      </c>
-      <c r="C2" s="19" t="s">
+      <c r="A2" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="B2" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="C2" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="D2" s="20" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="3" ht="36.75" customHeight="1" spans="1:4">
+      <c r="A3" s="21"/>
+      <c r="B3" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="C3" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="D3" s="22">
+        <v>1000000000</v>
+      </c>
+    </row>
+    <row r="4" ht="36.75" customHeight="1" spans="1:4">
+      <c r="A4" s="21"/>
+      <c r="B4" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="C4" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="D4" s="22">
+        <v>1000000000</v>
+      </c>
+    </row>
+    <row r="5" ht="36.75" customHeight="1" spans="1:4">
+      <c r="A5" s="21"/>
+      <c r="B5" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="C5" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="D5" s="22">
+        <v>750000000</v>
+      </c>
+    </row>
+    <row r="6" ht="36" customHeight="1" spans="1:4">
+      <c r="A6" s="21"/>
+      <c r="B6" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="C6" s="20" t="s">
+        <v>97</v>
+      </c>
+      <c r="D6" s="22">
+        <v>750000000</v>
+      </c>
+    </row>
+    <row r="7" ht="36.75" customHeight="1" spans="1:4">
+      <c r="A7" s="21"/>
+      <c r="B7" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="C7" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="D7" s="22">
+        <v>750000000</v>
+      </c>
+    </row>
+    <row r="8" ht="36.75" customHeight="1" spans="1:4">
+      <c r="A8" s="20" t="s">
+        <v>100</v>
+      </c>
+      <c r="B8" s="20" t="s">
+        <v>101</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="D8" s="22">
+        <v>750000000</v>
+      </c>
+    </row>
+    <row r="9" ht="36.75" customHeight="1" spans="1:4">
+      <c r="A9" s="20" t="s">
+        <v>103</v>
+      </c>
+      <c r="B9" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="C9" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="D9" s="22">
+        <v>750000000</v>
+      </c>
+    </row>
+    <row r="10" ht="36.75" customHeight="1" spans="1:4">
+      <c r="A10" s="20" t="s">
+        <v>105</v>
+      </c>
+      <c r="B10" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" s="20" t="s">
+        <v>106</v>
+      </c>
+      <c r="D10" s="22">
+        <v>750000000</v>
+      </c>
+    </row>
+    <row r="11" ht="37.5" customHeight="1" spans="1:4">
+      <c r="A11" s="20" t="s">
+        <v>107</v>
+      </c>
+      <c r="B11" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="D11" s="22">
+        <v>500000000</v>
+      </c>
+    </row>
+    <row r="12" ht="36.75" customHeight="1" spans="1:4">
+      <c r="A12" s="21"/>
+      <c r="B12" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="C12" s="20" t="s">
+        <v>109</v>
+      </c>
+      <c r="D12" s="22">
+        <v>500000000</v>
+      </c>
+    </row>
+    <row r="13" ht="36.75" customHeight="1" spans="1:4">
+      <c r="A13" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="B13" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="D13" s="22">
+        <v>500000000</v>
+      </c>
+    </row>
+    <row r="14" ht="36.75" customHeight="1" spans="1:4">
+      <c r="A14" s="21"/>
+      <c r="B14" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="C14" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="D14" s="22">
+        <v>500000000</v>
+      </c>
+    </row>
+    <row r="15" ht="36.75" customHeight="1" spans="1:4">
+      <c r="A15" s="21"/>
+      <c r="B15" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="D15" s="22">
+        <v>500000000</v>
+      </c>
+    </row>
+    <row r="16" ht="36" customHeight="1" spans="1:4">
+      <c r="A16" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="B16" s="20" t="s">
+        <v>113</v>
+      </c>
+      <c r="C16" s="23">
+        <v>1000</v>
+      </c>
+      <c r="D16" s="22">
+        <v>500000000</v>
+      </c>
+    </row>
+    <row r="17" ht="36.75" customHeight="1" spans="1:4">
+      <c r="A17" s="21"/>
+      <c r="B17" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="C17" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="D17" s="22">
+        <v>200000000</v>
+      </c>
+    </row>
+    <row r="18" ht="36.75" customHeight="1" spans="1:4">
+      <c r="A18" s="21"/>
+      <c r="B18" s="20" t="s">
+        <v>116</v>
+      </c>
+      <c r="C18" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="D18" s="22">
+        <v>200000000</v>
+      </c>
+    </row>
+    <row r="19" ht="36.75" customHeight="1" spans="1:4">
+      <c r="A19" s="21"/>
+      <c r="B19" s="20" t="s">
+        <v>117</v>
+      </c>
+      <c r="C19" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="D19" s="22">
+        <v>200000000</v>
+      </c>
+    </row>
+    <row r="20" ht="36.75" customHeight="1" spans="1:4">
+      <c r="A20" s="20" t="s">
+        <v>100</v>
+      </c>
+      <c r="B20" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="C20" s="23">
+        <v>500</v>
+      </c>
+      <c r="D20" s="22">
+        <v>200000000</v>
+      </c>
+    </row>
+    <row r="21" ht="36" customHeight="1" spans="1:4">
+      <c r="A21" s="21"/>
+      <c r="B21" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="C21" s="23">
+        <v>500</v>
+      </c>
+      <c r="D21" s="22">
+        <v>100000000</v>
+      </c>
+    </row>
+    <row r="22" ht="36.75" customHeight="1" spans="1:4">
+      <c r="A22" s="21"/>
+      <c r="B22" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="C22" s="20" t="s">
+        <v>118</v>
+      </c>
+      <c r="D22" s="22">
+        <v>100000000</v>
+      </c>
+    </row>
+    <row r="23" ht="36" customHeight="1" spans="1:4">
+      <c r="A23" s="21"/>
+      <c r="B23" s="20" t="s">
         <v>80</v>
       </c>
-      <c r="D2" s="19" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="3" ht="36.75" customHeight="1" spans="1:4">
-      <c r="A3" s="20"/>
-      <c r="B3" s="19" t="s">
-        <v>82</v>
-      </c>
-      <c r="C3" s="19" t="s">
-        <v>83</v>
-      </c>
-      <c r="D3" s="21">
-        <v>1000000000</v>
-      </c>
-    </row>
-    <row r="4" ht="36.75" customHeight="1" spans="1:4">
-      <c r="A4" s="20"/>
-      <c r="B4" s="19" t="s">
-        <v>84</v>
-      </c>
-      <c r="C4" s="19" t="s">
-        <v>83</v>
-      </c>
-      <c r="D4" s="21">
-        <v>1000000000</v>
-      </c>
-    </row>
-    <row r="5" ht="36.75" customHeight="1" spans="1:4">
-      <c r="A5" s="20"/>
-      <c r="B5" s="19" t="s">
-        <v>85</v>
-      </c>
-      <c r="C5" s="19" t="s">
-        <v>86</v>
-      </c>
-      <c r="D5" s="21">
-        <v>750000000</v>
-      </c>
-    </row>
-    <row r="6" ht="36" customHeight="1" spans="1:4">
-      <c r="A6" s="20"/>
-      <c r="B6" s="19" t="s">
-        <v>87</v>
-      </c>
-      <c r="C6" s="19" t="s">
-        <v>88</v>
-      </c>
-      <c r="D6" s="21">
-        <v>750000000</v>
-      </c>
-    </row>
-    <row r="7" ht="36.75" customHeight="1" spans="1:4">
-      <c r="A7" s="20"/>
-      <c r="B7" s="19" t="s">
-        <v>89</v>
-      </c>
-      <c r="C7" s="19" t="s">
-        <v>90</v>
-      </c>
-      <c r="D7" s="21">
-        <v>750000000</v>
-      </c>
-    </row>
-    <row r="8" ht="36.75" customHeight="1" spans="1:4">
-      <c r="A8" s="19" t="s">
-        <v>91</v>
-      </c>
-      <c r="B8" s="19" t="s">
-        <v>92</v>
-      </c>
-      <c r="C8" s="19" t="s">
-        <v>93</v>
-      </c>
-      <c r="D8" s="21">
-        <v>750000000</v>
-      </c>
-    </row>
-    <row r="9" ht="36.75" customHeight="1" spans="1:4">
-      <c r="A9" s="19" t="s">
-        <v>94</v>
-      </c>
-      <c r="B9" s="19" t="s">
-        <v>95</v>
-      </c>
-      <c r="C9" s="19" t="s">
-        <v>90</v>
-      </c>
-      <c r="D9" s="21">
-        <v>750000000</v>
-      </c>
-    </row>
-    <row r="10" ht="36.75" customHeight="1" spans="1:4">
-      <c r="A10" s="19" t="s">
-        <v>96</v>
-      </c>
-      <c r="B10" s="19" t="s">
-        <v>31</v>
-      </c>
-      <c r="C10" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="D10" s="21">
-        <v>750000000</v>
-      </c>
-    </row>
-    <row r="11" ht="37.5" customHeight="1" spans="1:4">
-      <c r="A11" s="19" t="s">
-        <v>98</v>
-      </c>
-      <c r="B11" s="19" t="s">
-        <v>47</v>
-      </c>
-      <c r="C11" s="19" t="s">
-        <v>99</v>
-      </c>
-      <c r="D11" s="21">
-        <v>500000000</v>
-      </c>
-    </row>
-    <row r="12" ht="36.75" customHeight="1" spans="1:4">
-      <c r="A12" s="20"/>
-      <c r="B12" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="C12" s="19" t="s">
-        <v>100</v>
-      </c>
-      <c r="D12" s="21">
-        <v>500000000</v>
-      </c>
-    </row>
-    <row r="13" ht="36.75" customHeight="1" spans="1:4">
-      <c r="A13" s="19" t="s">
-        <v>101</v>
-      </c>
-      <c r="B13" s="19" t="s">
-        <v>36</v>
-      </c>
-      <c r="C13" s="19" t="s">
-        <v>102</v>
-      </c>
-      <c r="D13" s="21">
-        <v>500000000</v>
-      </c>
-    </row>
-    <row r="14" ht="36.75" customHeight="1" spans="1:4">
-      <c r="A14" s="20"/>
-      <c r="B14" s="19" t="s">
-        <v>62</v>
-      </c>
-      <c r="C14" s="19" t="s">
-        <v>99</v>
-      </c>
-      <c r="D14" s="21">
-        <v>500000000</v>
-      </c>
-    </row>
-    <row r="15" ht="36.75" customHeight="1" spans="1:4">
-      <c r="A15" s="20"/>
-      <c r="B15" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="C15" s="19" t="s">
-        <v>102</v>
-      </c>
-      <c r="D15" s="21">
-        <v>500000000</v>
-      </c>
-    </row>
-    <row r="16" ht="36" customHeight="1" spans="1:4">
-      <c r="A16" s="19" t="s">
-        <v>103</v>
-      </c>
-      <c r="B16" s="19" t="s">
-        <v>104</v>
-      </c>
-      <c r="C16" s="22">
-        <v>1000</v>
-      </c>
-      <c r="D16" s="21">
-        <v>500000000</v>
-      </c>
-    </row>
-    <row r="17" ht="36.75" customHeight="1" spans="1:4">
-      <c r="A17" s="20"/>
-      <c r="B17" s="19" t="s">
-        <v>105</v>
-      </c>
-      <c r="C17" s="19" t="s">
-        <v>106</v>
-      </c>
-      <c r="D17" s="21">
-        <v>200000000</v>
-      </c>
-    </row>
-    <row r="18" ht="36.75" customHeight="1" spans="1:4">
-      <c r="A18" s="20"/>
-      <c r="B18" s="19" t="s">
-        <v>107</v>
-      </c>
-      <c r="C18" s="19" t="s">
-        <v>106</v>
-      </c>
-      <c r="D18" s="21">
-        <v>200000000</v>
-      </c>
-    </row>
-    <row r="19" ht="36.75" customHeight="1" spans="1:4">
-      <c r="A19" s="20"/>
-      <c r="B19" s="19" t="s">
-        <v>108</v>
-      </c>
-      <c r="C19" s="19" t="s">
-        <v>106</v>
-      </c>
-      <c r="D19" s="21">
-        <v>200000000</v>
-      </c>
-    </row>
-    <row r="20" ht="36.75" customHeight="1" spans="1:4">
-      <c r="A20" s="19" t="s">
-        <v>91</v>
-      </c>
-      <c r="B20" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="C20" s="22">
-        <v>500</v>
-      </c>
-      <c r="D20" s="21">
-        <v>200000000</v>
-      </c>
-    </row>
-    <row r="21" ht="36" customHeight="1" spans="1:4">
-      <c r="A21" s="20"/>
-      <c r="B21" s="19" t="s">
-        <v>109</v>
-      </c>
-      <c r="C21" s="22">
-        <v>500</v>
-      </c>
-      <c r="D21" s="21">
-        <v>100000000</v>
-      </c>
-    </row>
-    <row r="22" ht="36.75" customHeight="1" spans="1:4">
-      <c r="A22" s="20"/>
-      <c r="B22" s="19" t="s">
-        <v>49</v>
-      </c>
-      <c r="C22" s="19" t="s">
-        <v>110</v>
-      </c>
-      <c r="D22" s="21">
-        <v>100000000</v>
-      </c>
-    </row>
-    <row r="23" ht="36" customHeight="1" spans="1:4">
-      <c r="A23" s="20"/>
-      <c r="B23" s="19" t="s">
-        <v>111</v>
-      </c>
-      <c r="C23" s="19" t="s">
-        <v>110</v>
-      </c>
-      <c r="D23" s="21">
+      <c r="C23" s="20" t="s">
+        <v>118</v>
+      </c>
+      <c r="D23" s="22">
         <v>100000000</v>
       </c>
     </row>
@@ -4690,8 +5575,8 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr codeName="Sheet5"/>
-  <dimension ref="B1:O74"/>
+  <sheetPr codeName="Sheet4"/>
+  <dimension ref="B1:S74"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="9" style="7"/>
@@ -4701,47 +5586,62 @@
     <col min="5" max="6" width="26.2833333333333" style="8" customWidth="1"/>
     <col min="7" max="7" width="28.9583333333333" style="8" customWidth="1"/>
     <col min="8" max="8" width="24.1583333333333" style="8" customWidth="1"/>
-    <col min="9" max="9" width="21.375" style="8" customWidth="1"/>
-    <col min="10" max="12" width="22.6" style="8" customWidth="1"/>
-    <col min="13" max="13" width="14.3333333333333" style="8" customWidth="1"/>
-    <col min="14" max="16380" width="9" style="7"/>
+    <col min="9" max="9" width="21.2" style="8" customWidth="1"/>
+    <col min="10" max="10" width="20.325" style="8" customWidth="1"/>
+    <col min="11" max="11" width="19.5583333333333" style="8" customWidth="1"/>
+    <col min="12" max="13" width="21.375" style="8" customWidth="1"/>
+    <col min="14" max="16" width="22.6" style="8" customWidth="1"/>
+    <col min="17" max="17" width="14.3333333333333" style="8" customWidth="1"/>
+    <col min="18" max="16384" width="9" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:14">
+    <row r="1" spans="2:18">
       <c r="C1" s="8" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="J1" s="9" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="K1" s="9" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="L1" s="9" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="2" spans="2:14">
+        <v>128</v>
+      </c>
+      <c r="M1" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="N1" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="O1" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="P1" s="9" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="2" spans="2:18">
       <c r="B2" s="7" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="C2" s="8">
         <v>430</v>
@@ -4764,24 +5664,43 @@
         <v>470</v>
       </c>
       <c r="I2" s="8">
+        <f>H2-10</f>
+        <v>460</v>
+      </c>
+      <c r="J2" s="8">
+        <f>I2-10</f>
+        <v>450</v>
+      </c>
+      <c r="K2" s="8">
+        <v>470</v>
+      </c>
+      <c r="L2" s="8">
+        <f>K2+20</f>
+        <v>490</v>
+      </c>
+      <c r="M2" s="8">
+        <f>L2+10</f>
         <v>500</v>
       </c>
-      <c r="J2" s="8">
+      <c r="N2" s="8">
+        <f>M2+20</f>
         <v>520</v>
       </c>
-      <c r="K2" s="8">
+      <c r="O2" s="8">
+        <f>N2+20</f>
         <v>540</v>
       </c>
-      <c r="L2" s="8">
+      <c r="P2" s="8">
+        <f>O2-10</f>
         <v>530</v>
       </c>
-      <c r="M2" s="8" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="3" spans="2:14">
+      <c r="Q2" s="8" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="3" spans="2:18">
       <c r="B3" s="7" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="C3" s="8">
         <v>430</v>
@@ -4804,22 +5723,41 @@
         <v>470</v>
       </c>
       <c r="I3" s="8">
+        <f>H3-10</f>
+        <v>460</v>
+      </c>
+      <c r="J3" s="8">
+        <f>I3-10</f>
+        <v>450</v>
+      </c>
+      <c r="K3" s="8">
+        <v>460</v>
+      </c>
+      <c r="L3" s="8">
+        <f>K3+20</f>
+        <v>480</v>
+      </c>
+      <c r="M3" s="8">
+        <f>L3+10</f>
         <v>490</v>
       </c>
-      <c r="J3" s="8">
+      <c r="N3" s="8">
+        <f>M3+20</f>
         <v>510</v>
       </c>
-      <c r="K3" s="8">
+      <c r="O3" s="8">
+        <f>N3+20</f>
         <v>530</v>
       </c>
-      <c r="L3" s="8">
+      <c r="P3" s="8">
+        <f>O3-10</f>
         <v>520</v>
       </c>
-      <c r="M3" s="8" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="4" spans="2:14">
+      <c r="Q3" s="8" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="4" spans="2:18">
       <c r="B4" s="7" t="s">
         <v>62</v>
       </c>
@@ -4844,25 +5782,44 @@
         <v>460</v>
       </c>
       <c r="I4" s="8">
+        <f>H4-10</f>
+        <v>450</v>
+      </c>
+      <c r="J4" s="8">
+        <f>I4-10</f>
+        <v>440</v>
+      </c>
+      <c r="K4" s="8">
+        <v>450</v>
+      </c>
+      <c r="L4" s="8">
+        <f>K4+20</f>
+        <v>470</v>
+      </c>
+      <c r="M4" s="8">
+        <f>L4+10</f>
         <v>480</v>
       </c>
-      <c r="J4" s="8">
+      <c r="N4" s="8">
+        <f>M4+20</f>
         <v>500</v>
       </c>
-      <c r="K4" s="8">
+      <c r="O4" s="8">
+        <f>N4+20</f>
         <v>520</v>
       </c>
-      <c r="L4" s="8">
+      <c r="P4" s="8">
+        <f>O4-10</f>
         <v>510</v>
       </c>
-      <c r="M4" s="8" t="s">
+      <c r="Q4" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="N4" s="10"/>
-    </row>
-    <row r="5" spans="2:14">
+      <c r="R4" s="10"/>
+    </row>
+    <row r="5" spans="2:18">
       <c r="B5" s="7" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="C5" s="8">
         <v>420</v>
@@ -4883,14 +5840,22 @@
       <c r="H5" s="8">
         <v>460</v>
       </c>
-      <c r="M5" s="8" t="s">
-        <v>124</v>
-      </c>
-      <c r="N5" s="10"/>
-    </row>
-    <row r="6" spans="2:14">
+      <c r="I5" s="8">
+        <f>H5-10</f>
+        <v>450</v>
+      </c>
+      <c r="J5" s="8">
+        <f>I5-10</f>
+        <v>440</v>
+      </c>
+      <c r="Q5" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="R5" s="10"/>
+    </row>
+    <row r="6" spans="2:18">
       <c r="B6" s="7" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="C6" s="8">
         <v>435</v>
@@ -4913,22 +5878,40 @@
         <v>475</v>
       </c>
       <c r="I6" s="8">
+        <f>H6-10</f>
+        <v>465</v>
+      </c>
+      <c r="J6" s="8">
+        <f>I6-10</f>
+        <v>455</v>
+      </c>
+      <c r="K6" s="8">
+        <v>465</v>
+      </c>
+      <c r="L6" s="8">
+        <f>K6+20</f>
+        <v>485</v>
+      </c>
+      <c r="M6" s="8">
+        <f>L6+10</f>
         <v>495</v>
       </c>
-      <c r="J6" s="8">
+      <c r="N6" s="8">
+        <f>M6+20</f>
         <v>515</v>
       </c>
-      <c r="K6" s="8">
+      <c r="O6" s="8">
         <v>535</v>
       </c>
-      <c r="L6" s="8">
+      <c r="P6" s="8">
+        <f>O6-10</f>
         <v>525</v>
       </c>
-      <c r="M6" s="8" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="7" spans="2:14">
+      <c r="Q6" s="8" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="7" spans="2:18">
       <c r="B7" s="7" t="s">
         <v>61</v>
       </c>
@@ -4953,22 +5936,40 @@
         <v>460</v>
       </c>
       <c r="I7" s="8">
+        <f>H7-10</f>
+        <v>450</v>
+      </c>
+      <c r="J7" s="8">
+        <f>I7-10</f>
+        <v>440</v>
+      </c>
+      <c r="K7" s="8">
+        <v>450</v>
+      </c>
+      <c r="L7" s="8">
+        <f>K7+20</f>
+        <v>470</v>
+      </c>
+      <c r="M7" s="8">
+        <f>L7+10</f>
         <v>480</v>
       </c>
-      <c r="J7" s="8">
+      <c r="N7" s="8">
+        <f>M7+20</f>
         <v>500</v>
       </c>
-      <c r="K7" s="8">
+      <c r="O7" s="8">
         <v>520</v>
       </c>
-      <c r="L7" s="8">
+      <c r="P7" s="8">
+        <f>O7-10</f>
         <v>510</v>
       </c>
-      <c r="M7" s="8" t="s">
+      <c r="Q7" s="8" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="8" spans="2:14">
+    <row r="8" spans="2:18">
       <c r="B8" s="7" t="s">
         <v>60</v>
       </c>
@@ -4993,22 +5994,40 @@
         <v>480</v>
       </c>
       <c r="I8" s="8">
+        <f>H8-10</f>
+        <v>470</v>
+      </c>
+      <c r="J8" s="8">
+        <f>I8-10</f>
+        <v>460</v>
+      </c>
+      <c r="K8" s="8">
+        <v>470</v>
+      </c>
+      <c r="L8" s="8">
+        <f>K8+20</f>
+        <v>490</v>
+      </c>
+      <c r="M8" s="8">
+        <f>L8+10</f>
         <v>500</v>
       </c>
-      <c r="J8" s="8">
+      <c r="N8" s="8">
+        <f>M8+20</f>
         <v>520</v>
       </c>
-      <c r="K8" s="8">
+      <c r="O8" s="8">
         <v>540</v>
       </c>
-      <c r="L8" s="8">
+      <c r="P8" s="8">
+        <f>O8-10</f>
         <v>530</v>
       </c>
-      <c r="M8" s="8" t="s">
+      <c r="Q8" s="8" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="9" spans="2:14">
+    <row r="9" spans="2:18">
       <c r="B9" s="7" t="s">
         <v>73</v>
       </c>
@@ -5033,22 +6052,40 @@
         <v>470</v>
       </c>
       <c r="I9" s="8">
+        <f>H9-10</f>
+        <v>460</v>
+      </c>
+      <c r="J9" s="8">
+        <f>I9-10</f>
+        <v>450</v>
+      </c>
+      <c r="K9" s="8">
+        <v>460</v>
+      </c>
+      <c r="L9" s="8">
+        <f>K9+20</f>
+        <v>480</v>
+      </c>
+      <c r="M9" s="8">
+        <f>L9+10</f>
         <v>490</v>
       </c>
-      <c r="J9" s="8">
+      <c r="N9" s="8">
+        <f>M9+20</f>
         <v>510</v>
       </c>
-      <c r="K9" s="8">
+      <c r="O9" s="8">
         <v>530</v>
       </c>
-      <c r="L9" s="8">
+      <c r="P9" s="8">
+        <f>O9-10</f>
         <v>520</v>
       </c>
-      <c r="M9" s="8" t="s">
+      <c r="Q9" s="8" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="10" spans="2:14">
+    <row r="10" spans="2:18">
       <c r="B10" s="7" t="s">
         <v>59</v>
       </c>
@@ -5073,22 +6110,40 @@
         <v>460</v>
       </c>
       <c r="I10" s="8">
+        <f>H10-10</f>
+        <v>450</v>
+      </c>
+      <c r="J10" s="8">
+        <f>I10-10</f>
+        <v>440</v>
+      </c>
+      <c r="K10" s="8">
+        <v>450</v>
+      </c>
+      <c r="L10" s="8">
+        <f>K10+20</f>
+        <v>470</v>
+      </c>
+      <c r="M10" s="8">
+        <f>L10+10</f>
         <v>480</v>
       </c>
-      <c r="J10" s="8">
+      <c r="N10" s="8">
+        <f>M10+20</f>
         <v>500</v>
       </c>
-      <c r="K10" s="8">
+      <c r="O10" s="8">
         <v>520</v>
       </c>
-      <c r="L10" s="8">
+      <c r="P10" s="8">
+        <f>O10-10</f>
         <v>510</v>
       </c>
-      <c r="M10" s="8" t="s">
+      <c r="Q10" s="8" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="11" spans="2:14">
+    <row r="11" spans="2:18">
       <c r="B11" s="7" t="s">
         <v>57</v>
       </c>
@@ -5099,22 +6154,38 @@
         <v>460</v>
       </c>
       <c r="I11" s="8">
+        <v>450</v>
+      </c>
+      <c r="J11" s="8">
+        <v>440</v>
+      </c>
+      <c r="K11" s="8">
+        <v>450</v>
+      </c>
+      <c r="L11" s="8">
+        <f>K11+20</f>
+        <v>470</v>
+      </c>
+      <c r="M11" s="8">
+        <f>L11+10</f>
         <v>480</v>
       </c>
-      <c r="J11" s="8">
+      <c r="N11" s="8">
+        <f>M11+20</f>
         <v>500</v>
       </c>
-      <c r="K11" s="8">
+      <c r="O11" s="8">
         <v>520</v>
       </c>
-      <c r="L11" s="8">
+      <c r="P11" s="8">
+        <f>O11-10</f>
         <v>510</v>
       </c>
-      <c r="M11" s="8" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="12" spans="2:14">
+      <c r="Q11" s="8" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="12" spans="2:18">
       <c r="B12" s="7" t="s">
         <v>56</v>
       </c>
@@ -5139,24 +6210,42 @@
         <v>480</v>
       </c>
       <c r="I12" s="8">
+        <f>H12-10</f>
+        <v>470</v>
+      </c>
+      <c r="J12" s="8">
+        <f>I12-10</f>
+        <v>460</v>
+      </c>
+      <c r="K12" s="8">
+        <v>470</v>
+      </c>
+      <c r="L12" s="8">
+        <f>K12+20</f>
+        <v>490</v>
+      </c>
+      <c r="M12" s="8">
+        <f>L12+10</f>
         <v>500</v>
       </c>
-      <c r="J12" s="8">
+      <c r="N12" s="8">
+        <f>M12+20</f>
         <v>520</v>
       </c>
-      <c r="K12" s="8">
+      <c r="O12" s="8">
         <v>540</v>
       </c>
-      <c r="L12" s="8">
+      <c r="P12" s="8">
+        <f>O12-10</f>
         <v>530</v>
       </c>
-      <c r="M12" s="8" t="s">
+      <c r="Q12" s="8" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="13" spans="2:14">
+    <row r="13" spans="2:18">
       <c r="B13" s="7" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="C13" s="8">
         <v>425</v>
@@ -5179,24 +6268,42 @@
         <v>465</v>
       </c>
       <c r="I13" s="8">
+        <f>H13-10</f>
+        <v>455</v>
+      </c>
+      <c r="J13" s="8">
+        <f>I13-10</f>
+        <v>445</v>
+      </c>
+      <c r="K13" s="8">
+        <v>455</v>
+      </c>
+      <c r="L13" s="8">
+        <f>K13+20</f>
+        <v>475</v>
+      </c>
+      <c r="M13" s="8">
+        <f>L13+10</f>
         <v>485</v>
       </c>
-      <c r="J13" s="8">
+      <c r="N13" s="8">
+        <f>M13+20</f>
         <v>505</v>
       </c>
-      <c r="K13" s="8">
+      <c r="O13" s="8">
         <v>525</v>
       </c>
-      <c r="L13" s="8">
+      <c r="P13" s="8">
+        <f>O13-10</f>
         <v>515</v>
       </c>
-      <c r="M13" s="8" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="14" spans="2:14">
+      <c r="Q13" s="8" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="14" spans="2:18">
       <c r="B14" s="7" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="C14" s="8">
         <v>435</v>
@@ -5219,24 +6326,42 @@
         <v>475</v>
       </c>
       <c r="I14" s="8">
+        <f>H14-10</f>
+        <v>465</v>
+      </c>
+      <c r="J14" s="8">
+        <f>I14-10</f>
+        <v>455</v>
+      </c>
+      <c r="K14" s="8">
+        <v>465</v>
+      </c>
+      <c r="L14" s="8">
+        <f>K14+20</f>
+        <v>485</v>
+      </c>
+      <c r="M14" s="8">
+        <f>L14+10</f>
         <v>495</v>
       </c>
-      <c r="J14" s="8">
+      <c r="N14" s="8">
+        <f>M14+20</f>
         <v>515</v>
       </c>
-      <c r="K14" s="8">
+      <c r="O14" s="8">
         <v>535</v>
       </c>
-      <c r="L14" s="8">
+      <c r="P14" s="8">
+        <f>O14-10</f>
         <v>525</v>
       </c>
-      <c r="M14" s="8" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="15" spans="2:14">
+      <c r="Q14" s="8" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="15" spans="2:18">
       <c r="B15" s="7" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="C15" s="8">
         <v>420</v>
@@ -5259,22 +6384,40 @@
         <v>460</v>
       </c>
       <c r="I15" s="8">
+        <f>H15-10</f>
+        <v>450</v>
+      </c>
+      <c r="J15" s="8">
+        <f>I15-10</f>
+        <v>440</v>
+      </c>
+      <c r="K15" s="8">
+        <v>450</v>
+      </c>
+      <c r="L15" s="8">
+        <f>K15+20</f>
+        <v>470</v>
+      </c>
+      <c r="M15" s="8">
+        <f>L15+10</f>
         <v>480</v>
       </c>
-      <c r="J15" s="8">
+      <c r="N15" s="8">
+        <f>M15+20</f>
         <v>500</v>
       </c>
-      <c r="K15" s="8">
+      <c r="O15" s="8">
         <v>520</v>
       </c>
-      <c r="L15" s="8">
+      <c r="P15" s="8">
+        <f>O15-10</f>
         <v>510</v>
       </c>
-      <c r="M15" s="8" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="16" spans="2:14">
+      <c r="Q15" s="8" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="16" spans="2:18">
       <c r="B16" s="12" t="s">
         <v>55</v>
       </c>
@@ -5299,22 +6442,40 @@
         <v>470</v>
       </c>
       <c r="I16" s="8">
+        <f>H16-10</f>
+        <v>460</v>
+      </c>
+      <c r="J16" s="8">
+        <f>I16-10</f>
+        <v>450</v>
+      </c>
+      <c r="K16" s="8">
+        <v>460</v>
+      </c>
+      <c r="L16" s="8">
+        <f>K16+20</f>
+        <v>480</v>
+      </c>
+      <c r="M16" s="8">
+        <f>L16+10</f>
         <v>490</v>
       </c>
-      <c r="J16" s="8">
+      <c r="N16" s="8">
+        <f>M16+20</f>
         <v>510</v>
       </c>
-      <c r="K16" s="8">
+      <c r="O16" s="8">
         <v>530</v>
       </c>
-      <c r="L16" s="8">
+      <c r="P16" s="8">
+        <f>O16-10</f>
         <v>520</v>
       </c>
-      <c r="M16" s="8" t="s">
+      <c r="Q16" s="8" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="17" spans="2:15">
+    <row r="17" spans="2:19">
       <c r="B17" s="13" t="s">
         <v>54</v>
       </c>
@@ -5339,26 +6500,44 @@
         <v>450</v>
       </c>
       <c r="I17" s="8">
+        <f>H17-10</f>
+        <v>440</v>
+      </c>
+      <c r="J17" s="8">
+        <f>I17-10</f>
+        <v>430</v>
+      </c>
+      <c r="K17" s="14">
+        <v>440</v>
+      </c>
+      <c r="L17" s="14">
+        <f>K17+20</f>
+        <v>460</v>
+      </c>
+      <c r="M17" s="8">
+        <f>L17+10</f>
         <v>470</v>
       </c>
-      <c r="J17" s="8">
+      <c r="N17" s="8">
+        <f>M17+20</f>
         <v>490</v>
       </c>
-      <c r="K17" s="8">
+      <c r="O17" s="8">
         <v>510</v>
       </c>
-      <c r="L17" s="8">
+      <c r="P17" s="8">
+        <f>O17-10</f>
         <v>500</v>
       </c>
-      <c r="M17" s="14" t="s">
+      <c r="Q17" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="N17" s="15"/>
-      <c r="O17" s="15"/>
-    </row>
-    <row r="18" spans="2:15">
+      <c r="R17" s="16"/>
+      <c r="S17" s="16"/>
+    </row>
+    <row r="18" spans="2:19">
       <c r="B18" s="12" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="C18" s="8">
         <v>435</v>
@@ -5381,24 +6560,41 @@
         <v>475</v>
       </c>
       <c r="I18" s="8">
+        <f>H18-10</f>
+        <v>465</v>
+      </c>
+      <c r="J18" s="8">
+        <f>I18-10</f>
+        <v>455</v>
+      </c>
+      <c r="K18" s="8">
+        <v>470</v>
+      </c>
+      <c r="L18" s="8">
+        <f>K18+20</f>
+        <v>490</v>
+      </c>
+      <c r="M18" s="8">
+        <f>L18+10</f>
         <v>500</v>
       </c>
-      <c r="J18" s="8">
+      <c r="N18" s="8">
         <v>515</v>
       </c>
-      <c r="K18" s="8">
+      <c r="O18" s="8">
         <v>535</v>
       </c>
-      <c r="L18" s="8">
+      <c r="P18" s="8">
+        <f>O18-10</f>
         <v>525</v>
       </c>
-      <c r="M18" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="N18" s="15"/>
-      <c r="O18" s="15"/>
-    </row>
-    <row r="19" spans="2:15">
+      <c r="Q18" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="R18" s="16"/>
+      <c r="S18" s="16"/>
+    </row>
+    <row r="19" spans="2:19">
       <c r="B19" s="7" t="s">
         <v>72</v>
       </c>
@@ -5423,24 +6619,42 @@
         <v>490</v>
       </c>
       <c r="I19" s="8">
+        <f>H19-10</f>
+        <v>480</v>
+      </c>
+      <c r="J19" s="8">
+        <f>I19-10</f>
+        <v>470</v>
+      </c>
+      <c r="K19" s="8">
+        <v>480</v>
+      </c>
+      <c r="L19" s="8">
+        <f>K19+20</f>
+        <v>500</v>
+      </c>
+      <c r="M19" s="8">
+        <f>L19+10</f>
         <v>510</v>
       </c>
-      <c r="J19" s="8">
+      <c r="N19" s="8">
+        <f>M19+20</f>
         <v>530</v>
       </c>
-      <c r="K19" s="8">
+      <c r="O19" s="8">
         <v>540</v>
       </c>
-      <c r="L19" s="8">
+      <c r="P19" s="8">
+        <f>O19-10</f>
         <v>530</v>
       </c>
-      <c r="M19" s="8" t="s">
+      <c r="Q19" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="N19" s="15"/>
-      <c r="O19" s="15"/>
-    </row>
-    <row r="20" spans="2:15">
+      <c r="R19" s="16"/>
+      <c r="S19" s="16"/>
+    </row>
+    <row r="20" spans="2:19">
       <c r="B20" s="7" t="s">
         <v>53</v>
       </c>
@@ -5465,26 +6679,44 @@
         <v>475</v>
       </c>
       <c r="I20" s="8">
+        <f>H20-10</f>
+        <v>465</v>
+      </c>
+      <c r="J20" s="8">
+        <f>I20-10</f>
+        <v>455</v>
+      </c>
+      <c r="K20" s="8">
+        <v>465</v>
+      </c>
+      <c r="L20" s="8">
+        <f>K20+20</f>
+        <v>485</v>
+      </c>
+      <c r="M20" s="8">
+        <f>L20+10</f>
         <v>495</v>
       </c>
-      <c r="J20" s="8">
+      <c r="N20" s="8">
+        <f>M20+20</f>
         <v>515</v>
       </c>
-      <c r="K20" s="8">
+      <c r="O20" s="8">
         <v>535</v>
       </c>
-      <c r="L20" s="8">
+      <c r="P20" s="8">
+        <f>O20-10</f>
         <v>525</v>
       </c>
-      <c r="M20" s="8" t="s">
+      <c r="Q20" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="N20" s="15"/>
-      <c r="O20" s="15"/>
-    </row>
-    <row r="21" spans="2:15">
+      <c r="R20" s="16"/>
+      <c r="S20" s="16"/>
+    </row>
+    <row r="21" spans="2:19">
       <c r="B21" s="7" t="s">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="C21" s="8">
         <v>430</v>
@@ -5507,26 +6739,44 @@
         <v>485</v>
       </c>
       <c r="I21" s="8">
+        <f>H21-10</f>
+        <v>475</v>
+      </c>
+      <c r="J21" s="8">
+        <f>I21-10</f>
+        <v>465</v>
+      </c>
+      <c r="K21" s="8">
+        <v>475</v>
+      </c>
+      <c r="L21" s="8">
+        <f>K21+20</f>
+        <v>495</v>
+      </c>
+      <c r="M21" s="8">
+        <f>L21+10</f>
         <v>505</v>
       </c>
-      <c r="J21" s="8">
+      <c r="N21" s="8">
+        <f>M21+20</f>
         <v>525</v>
       </c>
-      <c r="K21" s="8">
+      <c r="O21" s="8">
         <v>545</v>
       </c>
-      <c r="L21" s="8">
+      <c r="P21" s="8">
+        <f>O21-10</f>
         <v>535</v>
       </c>
-      <c r="M21" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="N21" s="15"/>
-      <c r="O21" s="15"/>
-    </row>
-    <row r="22" spans="2:15">
+      <c r="Q21" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="R21" s="16"/>
+      <c r="S21" s="16"/>
+    </row>
+    <row r="22" spans="2:19">
       <c r="B22" s="7" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="C22" s="8">
         <v>160</v>
@@ -5549,26 +6799,44 @@
         <v>490</v>
       </c>
       <c r="I22" s="8">
+        <f>H22-10</f>
+        <v>480</v>
+      </c>
+      <c r="J22" s="8">
+        <f>I22-10</f>
+        <v>470</v>
+      </c>
+      <c r="K22" s="8">
+        <v>480</v>
+      </c>
+      <c r="L22" s="8">
+        <f>K22+20</f>
+        <v>500</v>
+      </c>
+      <c r="M22" s="8">
+        <f>L22+10</f>
         <v>510</v>
       </c>
-      <c r="J22" s="8">
+      <c r="N22" s="8">
+        <f>M22+20</f>
         <v>530</v>
       </c>
-      <c r="K22" s="8">
+      <c r="O22" s="8">
         <v>550</v>
       </c>
-      <c r="L22" s="8">
+      <c r="P22" s="8">
+        <f>O22-10</f>
         <v>540</v>
       </c>
-      <c r="M22" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="N22" s="15"/>
-      <c r="O22" s="15"/>
-    </row>
-    <row r="23" spans="2:15">
+      <c r="Q22" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="R22" s="16"/>
+      <c r="S22" s="16"/>
+    </row>
+    <row r="23" spans="2:19">
       <c r="B23" s="7" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="C23" s="8">
         <v>420</v>
@@ -5589,13 +6857,22 @@
       <c r="H23" s="8">
         <v>460</v>
       </c>
-      <c r="L23" s="8">
+      <c r="I23" s="8">
+        <f>H23-10</f>
+        <v>450</v>
+      </c>
+      <c r="J23" s="8">
+        <f>I23-10</f>
+        <v>440</v>
+      </c>
+      <c r="P23" s="8">
+        <f>O23-10</f>
         <v>-10</v>
       </c>
-      <c r="N23" s="15"/>
-      <c r="O23" s="15"/>
-    </row>
-    <row r="24" spans="2:15">
+      <c r="R23" s="16"/>
+      <c r="S23" s="16"/>
+    </row>
+    <row r="24" spans="2:19">
       <c r="B24" s="7" t="s">
         <v>52</v>
       </c>
@@ -5620,24 +6897,42 @@
         <v>485</v>
       </c>
       <c r="I24" s="8">
+        <f>H24-10</f>
+        <v>475</v>
+      </c>
+      <c r="J24" s="8">
+        <v>460</v>
+      </c>
+      <c r="K24" s="8">
+        <v>470</v>
+      </c>
+      <c r="L24" s="8">
+        <f>K24+20</f>
+        <v>490</v>
+      </c>
+      <c r="M24" s="8">
+        <f>L24+10</f>
         <v>500</v>
       </c>
-      <c r="J24" s="8">
+      <c r="N24" s="8">
+        <f>M24+20</f>
         <v>520</v>
       </c>
-      <c r="K24" s="8">
+      <c r="O24" s="8">
+        <f>N24+20</f>
         <v>540</v>
       </c>
-      <c r="L24" s="8">
+      <c r="P24" s="8">
+        <f>O24-10</f>
         <v>530</v>
       </c>
-      <c r="M24" s="8" t="s">
+      <c r="Q24" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="N24" s="15"/>
-      <c r="O24" s="15"/>
-    </row>
-    <row r="25" spans="2:15">
+      <c r="R24" s="16"/>
+      <c r="S24" s="16"/>
+    </row>
+    <row r="25" spans="2:19">
       <c r="B25" s="13" t="s">
         <v>71</v>
       </c>
@@ -5662,26 +6957,45 @@
         <v>450</v>
       </c>
       <c r="I25" s="8">
+        <f>H25-10</f>
+        <v>440</v>
+      </c>
+      <c r="J25" s="8">
+        <f>I25-10</f>
+        <v>430</v>
+      </c>
+      <c r="K25" s="15">
+        <v>440</v>
+      </c>
+      <c r="L25" s="14">
+        <f>K25+20</f>
+        <v>460</v>
+      </c>
+      <c r="M25" s="8">
+        <f>L25+10</f>
         <v>470</v>
       </c>
-      <c r="J25" s="8">
+      <c r="N25" s="8">
+        <f>M25+20</f>
         <v>490</v>
       </c>
-      <c r="K25" s="8">
+      <c r="O25" s="8">
+        <f>N25+20</f>
         <v>510</v>
       </c>
-      <c r="L25" s="8">
+      <c r="P25" s="8">
+        <f>O25-10</f>
         <v>500</v>
       </c>
-      <c r="M25" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="N25" s="15"/>
-      <c r="O25" s="15"/>
-    </row>
-    <row r="26" spans="2:15">
+      <c r="Q25" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="R25" s="16"/>
+      <c r="S25" s="16"/>
+    </row>
+    <row r="26" spans="2:19">
       <c r="B26" s="7" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="C26" s="8">
         <v>440</v>
@@ -5704,26 +7018,45 @@
         <v>480</v>
       </c>
       <c r="I26" s="8">
+        <f>H26-10</f>
+        <v>470</v>
+      </c>
+      <c r="J26" s="8">
+        <f>I26-10</f>
+        <v>460</v>
+      </c>
+      <c r="K26" s="8">
+        <v>470</v>
+      </c>
+      <c r="L26" s="8">
+        <f>K26+20</f>
+        <v>490</v>
+      </c>
+      <c r="M26" s="8">
+        <f>L26+10</f>
         <v>500</v>
       </c>
-      <c r="J26" s="8">
+      <c r="N26" s="8">
+        <f>M26+20</f>
         <v>520</v>
       </c>
-      <c r="K26" s="8">
+      <c r="O26" s="8">
+        <f>N26+20</f>
         <v>540</v>
       </c>
-      <c r="L26" s="8">
+      <c r="P26" s="8">
+        <f>O26-10</f>
         <v>530</v>
       </c>
-      <c r="M26" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="N26" s="15"/>
-      <c r="O26" s="15"/>
-    </row>
-    <row r="27" spans="2:15">
+      <c r="Q26" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="R26" s="16"/>
+      <c r="S26" s="16"/>
+    </row>
+    <row r="27" spans="2:19">
       <c r="B27" s="7" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="C27" s="8">
         <v>430</v>
@@ -5746,22 +7079,41 @@
         <v>470</v>
       </c>
       <c r="I27" s="8">
+        <f>H27-10</f>
+        <v>460</v>
+      </c>
+      <c r="J27" s="8">
+        <f>I27-10</f>
+        <v>450</v>
+      </c>
+      <c r="K27" s="8">
+        <v>470</v>
+      </c>
+      <c r="L27" s="8">
+        <f>K27+20</f>
+        <v>490</v>
+      </c>
+      <c r="M27" s="8">
+        <f>L27+10</f>
         <v>500</v>
       </c>
-      <c r="J27" s="8">
+      <c r="N27" s="8">
+        <f>M27+20</f>
         <v>520</v>
       </c>
-      <c r="K27" s="8">
+      <c r="O27" s="8">
+        <f>N27+20</f>
         <v>540</v>
       </c>
-      <c r="L27" s="8">
+      <c r="P27" s="8">
+        <f>O27-10</f>
         <v>530</v>
       </c>
-      <c r="M27" s="8" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="28" spans="2:15">
+      <c r="Q27" s="8" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="28" spans="2:19">
       <c r="B28" s="7" t="s">
         <v>50</v>
       </c>
@@ -5786,22 +7138,41 @@
         <v>470</v>
       </c>
       <c r="I28" s="8">
+        <f>H28-10</f>
+        <v>460</v>
+      </c>
+      <c r="J28" s="8">
+        <f>I28-10</f>
+        <v>450</v>
+      </c>
+      <c r="K28" s="8">
+        <v>460</v>
+      </c>
+      <c r="L28" s="8">
+        <f>K28+20</f>
+        <v>480</v>
+      </c>
+      <c r="M28" s="8">
+        <f>L28+10</f>
         <v>490</v>
       </c>
-      <c r="J28" s="8">
+      <c r="N28" s="8">
+        <f>M28+20</f>
         <v>510</v>
       </c>
-      <c r="K28" s="8">
+      <c r="O28" s="8">
+        <f>N28+20</f>
         <v>530</v>
       </c>
-      <c r="L28" s="8">
+      <c r="P28" s="8">
+        <f>O28-10</f>
         <v>520</v>
       </c>
-      <c r="M28" s="8" t="s">
+      <c r="Q28" s="8" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="29" spans="2:15">
+    <row r="29" spans="2:19">
       <c r="B29" s="7" t="s">
         <v>49</v>
       </c>
@@ -5826,24 +7197,43 @@
         <v>475</v>
       </c>
       <c r="I29" s="8">
+        <f>H29-10</f>
+        <v>465</v>
+      </c>
+      <c r="J29" s="8">
+        <f>I29-10</f>
+        <v>455</v>
+      </c>
+      <c r="K29" s="8">
+        <v>465</v>
+      </c>
+      <c r="L29" s="8">
+        <f>K29+20</f>
+        <v>485</v>
+      </c>
+      <c r="M29" s="8">
+        <f>L29+10</f>
         <v>495</v>
       </c>
-      <c r="J29" s="8">
+      <c r="N29" s="8">
+        <f>M29+20</f>
         <v>515</v>
       </c>
-      <c r="K29" s="8">
+      <c r="O29" s="8">
+        <f>N29+20</f>
         <v>535</v>
       </c>
-      <c r="L29" s="8">
+      <c r="P29" s="8">
+        <f>O29-10</f>
         <v>525</v>
       </c>
-      <c r="M29" s="8" t="s">
+      <c r="Q29" s="8" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="30" spans="2:15">
+    <row r="30" spans="2:19">
       <c r="B30" s="7" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="C30" s="8">
         <v>420</v>
@@ -5865,16 +7255,25 @@
       <c r="H30" s="8">
         <v>460</v>
       </c>
+      <c r="I30" s="8">
+        <f>H30-10</f>
+        <v>450</v>
+      </c>
       <c r="J30" s="8">
+        <f>I30-10</f>
+        <v>440</v>
+      </c>
+      <c r="N30" s="8">
+        <f>M30+20</f>
         <v>20</v>
       </c>
-      <c r="M30" s="8" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="31" spans="2:15">
+      <c r="Q30" s="8" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="31" spans="2:19">
       <c r="B31" s="7" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="C31" s="8">
         <v>425</v>
@@ -5897,22 +7296,41 @@
         <v>465</v>
       </c>
       <c r="I31" s="8">
+        <f>H31-10</f>
+        <v>455</v>
+      </c>
+      <c r="J31" s="8">
+        <f>I31-10</f>
+        <v>445</v>
+      </c>
+      <c r="K31" s="8">
+        <v>455</v>
+      </c>
+      <c r="L31" s="8">
+        <f>K31+20</f>
+        <v>475</v>
+      </c>
+      <c r="M31" s="8">
+        <f>L31+10</f>
         <v>485</v>
       </c>
-      <c r="J31" s="8">
+      <c r="N31" s="8">
+        <f>M31+20</f>
         <v>505</v>
       </c>
-      <c r="K31" s="8">
+      <c r="O31" s="8">
+        <f>N31+20</f>
         <v>525</v>
       </c>
-      <c r="L31" s="8">
+      <c r="P31" s="8">
+        <f>O31-10</f>
         <v>515</v>
       </c>
-      <c r="M31" s="8" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="32" spans="2:15">
+      <c r="Q31" s="8" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="32" spans="2:19">
       <c r="B32" s="7" t="s">
         <v>48</v>
       </c>
@@ -5937,22 +7355,41 @@
         <v>465</v>
       </c>
       <c r="I32" s="8">
+        <f>H32-10</f>
+        <v>455</v>
+      </c>
+      <c r="J32" s="8">
+        <f>I32-10</f>
+        <v>445</v>
+      </c>
+      <c r="K32" s="8">
+        <v>455</v>
+      </c>
+      <c r="L32" s="8">
+        <f>K32+20</f>
+        <v>475</v>
+      </c>
+      <c r="M32" s="8">
+        <f>L32+10</f>
         <v>485</v>
       </c>
-      <c r="J32" s="8">
+      <c r="N32" s="8">
+        <f>M32+20</f>
         <v>505</v>
       </c>
-      <c r="K32" s="8">
+      <c r="O32" s="8">
+        <f>N32+20</f>
         <v>525</v>
       </c>
-      <c r="L32" s="8">
+      <c r="P32" s="8">
+        <f>O32-10</f>
         <v>515</v>
       </c>
-      <c r="M32" s="8" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="33" spans="2:13">
+      <c r="Q32" s="8" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="33" spans="2:17">
       <c r="B33" s="13" t="s">
         <v>47</v>
       </c>
@@ -5977,42 +7414,75 @@
         <v>450</v>
       </c>
       <c r="I33" s="8">
+        <f>H33-10</f>
+        <v>440</v>
+      </c>
+      <c r="J33" s="8">
+        <f>I33-10</f>
+        <v>430</v>
+      </c>
+      <c r="K33" s="15">
+        <v>440</v>
+      </c>
+      <c r="L33" s="14">
+        <f>K33+20</f>
+        <v>460</v>
+      </c>
+      <c r="M33" s="8">
+        <f>L33+10</f>
         <v>470</v>
       </c>
-      <c r="J33" s="8">
+      <c r="N33" s="8">
+        <f>M33+20</f>
         <v>490</v>
       </c>
-      <c r="K33" s="8">
+      <c r="O33" s="8">
+        <f>N33+20</f>
         <v>510</v>
       </c>
-      <c r="L33" s="8">
+      <c r="P33" s="8">
+        <f>O33-10</f>
         <v>500</v>
       </c>
-      <c r="M33" s="14" t="s">
+      <c r="Q33" s="15" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="34" spans="2:13">
+    <row r="34" spans="2:17">
       <c r="B34" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="I34" s="8">
+        <v>148</v>
+      </c>
+      <c r="J34" s="8">
+        <v>440</v>
+      </c>
+      <c r="K34" s="8">
+        <v>475</v>
+      </c>
+      <c r="L34" s="8">
+        <f>K34+20</f>
+        <v>495</v>
+      </c>
+      <c r="M34" s="8">
+        <f>L34+10</f>
         <v>505</v>
       </c>
-      <c r="J34" s="8">
+      <c r="N34" s="8">
+        <f>M34+20</f>
         <v>525</v>
       </c>
-      <c r="K34" s="8">
+      <c r="O34" s="8">
+        <f>N34+20</f>
         <v>545</v>
       </c>
-      <c r="L34" s="8">
+      <c r="P34" s="8">
+        <f>O34-10</f>
         <v>535</v>
       </c>
-      <c r="M34" s="8" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="35" spans="2:13">
+      <c r="Q34" s="8" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17">
       <c r="B35" s="7" t="s">
         <v>45</v>
       </c>
@@ -6020,29 +7490,47 @@
         <v>480</v>
       </c>
       <c r="I35" s="8">
+        <v>450</v>
+      </c>
+      <c r="J35" s="8">
+        <f>I35-10</f>
+        <v>440</v>
+      </c>
+      <c r="K35" s="8">
+        <v>450</v>
+      </c>
+      <c r="L35" s="8">
+        <f>K35+20</f>
+        <v>470</v>
+      </c>
+      <c r="M35" s="8">
+        <f>L35+10</f>
         <v>480</v>
       </c>
-      <c r="J35" s="8">
+      <c r="N35" s="8">
+        <f>M35+20</f>
         <v>500</v>
       </c>
-      <c r="K35" s="8">
+      <c r="O35" s="8">
+        <f>N35+20</f>
         <v>520</v>
       </c>
-      <c r="L35" s="8">
+      <c r="P35" s="8">
+        <f>O35-10</f>
         <v>510</v>
       </c>
-      <c r="M35" s="8" t="s">
+      <c r="Q35" s="8" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="36" spans="2:13">
+    <row r="36" spans="2:17">
       <c r="B36" s="7" t="s">
         <v>46</v>
       </c>
       <c r="C36" s="8">
         <v>445</v>
       </c>
-      <c r="D36" s="16">
+      <c r="D36" s="17">
         <v>455</v>
       </c>
       <c r="E36" s="8">
@@ -6059,42 +7547,71 @@
         <v>475</v>
       </c>
       <c r="I36" s="8">
+        <f>H36-10</f>
+        <v>465</v>
+      </c>
+      <c r="J36" s="8">
+        <f>I36-10</f>
+        <v>455</v>
+      </c>
+      <c r="K36" s="8">
+        <v>465</v>
+      </c>
+      <c r="L36" s="8">
+        <f>K36+20</f>
+        <v>485</v>
+      </c>
+      <c r="M36" s="8">
+        <f>L36+10</f>
         <v>495</v>
       </c>
-      <c r="J36" s="8">
+      <c r="N36" s="8">
+        <f>M36+20</f>
         <v>515</v>
       </c>
-      <c r="K36" s="8">
+      <c r="O36" s="8">
+        <f>N36+20</f>
         <v>535</v>
       </c>
-      <c r="L36" s="8">
+      <c r="P36" s="8">
+        <f>O36-10</f>
         <v>525</v>
       </c>
-      <c r="M36" s="8" t="s">
+      <c r="Q36" s="8" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="37" spans="2:13">
+    <row r="37" spans="2:17">
       <c r="B37" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="I37" s="8">
+      <c r="K37" s="8">
+        <v>470</v>
+      </c>
+      <c r="L37" s="8">
+        <f>K37+20</f>
+        <v>490</v>
+      </c>
+      <c r="M37" s="8">
+        <f>L37+10</f>
         <v>500</v>
       </c>
-      <c r="J37" s="8">
+      <c r="N37" s="8">
         <v>530</v>
       </c>
-      <c r="K37" s="8">
+      <c r="O37" s="8">
+        <f>N37+20</f>
         <v>550</v>
       </c>
-      <c r="L37" s="8">
+      <c r="P37" s="8">
+        <f>O37-10</f>
         <v>540</v>
       </c>
-      <c r="M37" s="8" t="s">
+      <c r="Q37" s="8" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="38" spans="2:13">
+    <row r="38" spans="2:17">
       <c r="B38" s="7" t="s">
         <v>43</v>
       </c>
@@ -6119,24 +7636,43 @@
         <v>470</v>
       </c>
       <c r="I38" s="8">
+        <f>H38-10</f>
+        <v>460</v>
+      </c>
+      <c r="J38" s="8">
+        <f>I38-10</f>
+        <v>450</v>
+      </c>
+      <c r="K38" s="8">
+        <v>460</v>
+      </c>
+      <c r="L38" s="8">
+        <f>K38+20</f>
+        <v>480</v>
+      </c>
+      <c r="M38" s="8">
+        <f>L38+10</f>
         <v>490</v>
       </c>
-      <c r="J38" s="8">
+      <c r="N38" s="8">
+        <f>M38+20</f>
         <v>510</v>
       </c>
-      <c r="K38" s="8">
+      <c r="O38" s="8">
+        <f>N38+20</f>
         <v>530</v>
       </c>
-      <c r="L38" s="8">
+      <c r="P38" s="8">
+        <f>O38-10</f>
         <v>520</v>
       </c>
-      <c r="M38" s="8" t="s">
+      <c r="Q38" s="8" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="39" spans="2:13">
+    <row r="39" spans="2:17">
       <c r="B39" s="7" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="C39" s="8">
         <v>440</v>
@@ -6159,22 +7695,41 @@
         <v>480</v>
       </c>
       <c r="I39" s="8">
+        <f>H39-10</f>
+        <v>470</v>
+      </c>
+      <c r="J39" s="8">
+        <f>I39-10</f>
+        <v>460</v>
+      </c>
+      <c r="K39" s="8">
+        <v>470</v>
+      </c>
+      <c r="L39" s="8">
+        <f>K39+20</f>
+        <v>490</v>
+      </c>
+      <c r="M39" s="8">
+        <f>L39+10</f>
         <v>500</v>
       </c>
-      <c r="J39" s="8">
+      <c r="N39" s="8">
+        <f>M39+20</f>
         <v>520</v>
       </c>
-      <c r="K39" s="8">
+      <c r="O39" s="8">
+        <f>N39+20</f>
         <v>540</v>
       </c>
-      <c r="L39" s="8">
+      <c r="P39" s="8">
+        <f>O39-10</f>
         <v>530</v>
       </c>
-      <c r="M39" s="8" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="40" spans="2:13">
+      <c r="Q39" s="8" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="40" spans="2:17">
       <c r="B40" s="7" t="s">
         <v>42</v>
       </c>
@@ -6199,22 +7754,41 @@
         <v>470</v>
       </c>
       <c r="I40" s="8">
+        <f>H40-10</f>
+        <v>460</v>
+      </c>
+      <c r="J40" s="8">
+        <f>I40-10</f>
+        <v>450</v>
+      </c>
+      <c r="K40" s="8">
+        <v>460</v>
+      </c>
+      <c r="L40" s="8">
+        <f>K40+20</f>
+        <v>480</v>
+      </c>
+      <c r="M40" s="8">
+        <f>L40+10</f>
         <v>490</v>
       </c>
-      <c r="J40" s="8">
+      <c r="N40" s="8">
+        <f>M40+20</f>
         <v>510</v>
       </c>
-      <c r="K40" s="8">
+      <c r="O40" s="8">
+        <f>N40+20</f>
         <v>530</v>
       </c>
-      <c r="L40" s="8">
+      <c r="P40" s="8">
+        <f>O40-10</f>
         <v>520</v>
       </c>
-      <c r="M40" s="8" t="s">
+      <c r="Q40" s="8" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="41" spans="2:13">
+    <row r="41" spans="2:17">
       <c r="B41" s="7" t="s">
         <v>41</v>
       </c>
@@ -6239,41 +7813,63 @@
         <v>480</v>
       </c>
       <c r="I41" s="8">
+        <f>H41-10</f>
+        <v>470</v>
+      </c>
+      <c r="J41" s="8">
+        <f>I41-10</f>
+        <v>460</v>
+      </c>
+      <c r="K41" s="8">
+        <v>470</v>
+      </c>
+      <c r="L41" s="8">
+        <f>K41+20</f>
+        <v>490</v>
+      </c>
+      <c r="M41" s="8">
+        <f>L41+10</f>
         <v>500</v>
       </c>
-      <c r="J41" s="8">
+      <c r="N41" s="8">
+        <f>M41+20</f>
         <v>520</v>
       </c>
-      <c r="K41" s="8">
+      <c r="O41" s="8">
+        <f>N41+20</f>
         <v>540</v>
       </c>
-      <c r="L41" s="8">
+      <c r="P41" s="8">
+        <f>O41-10</f>
         <v>530</v>
       </c>
-      <c r="M41" s="8" t="s">
+      <c r="Q41" s="8" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="42" spans="2:13">
-      <c r="I42" s="8">
+    <row r="42" spans="2:17">
+      <c r="M42" s="8">
         <v>480</v>
       </c>
-      <c r="J42" s="8">
+      <c r="N42" s="8">
+        <f>M42+20</f>
         <v>500</v>
       </c>
-      <c r="K42" s="8">
+      <c r="O42" s="8">
+        <f>N42+20</f>
         <v>520</v>
       </c>
-      <c r="L42" s="8">
+      <c r="P42" s="8">
+        <f>O42-10</f>
         <v>510</v>
       </c>
-      <c r="M42" s="8" t="s">
+      <c r="Q42" s="8" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="43" spans="2:13">
+    <row r="43" spans="2:17">
       <c r="B43" s="7" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="C43" s="8">
         <v>435</v>
@@ -6296,22 +7892,40 @@
         <v>485</v>
       </c>
       <c r="I43" s="8">
+        <f>H43-10</f>
+        <v>475</v>
+      </c>
+      <c r="J43" s="8">
+        <v>455</v>
+      </c>
+      <c r="K43" s="8">
+        <v>465</v>
+      </c>
+      <c r="L43" s="8">
+        <f>K43+20</f>
+        <v>485</v>
+      </c>
+      <c r="M43" s="8">
+        <f>L43+10</f>
         <v>495</v>
       </c>
-      <c r="J43" s="8">
+      <c r="N43" s="8">
+        <f>M43+20</f>
         <v>515</v>
       </c>
-      <c r="K43" s="8">
+      <c r="O43" s="8">
+        <f>N43+20</f>
         <v>535</v>
       </c>
-      <c r="L43" s="8">
+      <c r="P43" s="8">
+        <f>O43-10</f>
         <v>525</v>
       </c>
-      <c r="M43" s="8" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="44" spans="2:13">
+      <c r="Q43" s="8" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="44" spans="2:17">
       <c r="B44" s="13" t="s">
         <v>39</v>
       </c>
@@ -6336,22 +7950,41 @@
         <v>450</v>
       </c>
       <c r="I44" s="8">
+        <f>H44-10</f>
+        <v>440</v>
+      </c>
+      <c r="J44" s="8">
+        <f>I44-10</f>
+        <v>430</v>
+      </c>
+      <c r="K44" s="15">
+        <v>440</v>
+      </c>
+      <c r="L44" s="14">
+        <f>K44+20</f>
+        <v>460</v>
+      </c>
+      <c r="M44" s="8">
+        <f>L44+10</f>
         <v>470</v>
       </c>
-      <c r="J44" s="8">
+      <c r="N44" s="8">
+        <f>M44+20</f>
         <v>490</v>
       </c>
-      <c r="K44" s="8">
+      <c r="O44" s="8">
+        <f>N44+20</f>
         <v>510</v>
       </c>
-      <c r="L44" s="8">
+      <c r="P44" s="8">
+        <f>O44-10</f>
         <v>500</v>
       </c>
-      <c r="M44" s="14" t="s">
+      <c r="Q44" s="15" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="45" spans="2:13">
+    <row r="45" spans="2:17">
       <c r="B45" s="13" t="s">
         <v>38</v>
       </c>
@@ -6376,24 +8009,43 @@
         <v>450</v>
       </c>
       <c r="I45" s="8">
+        <f>H45-10</f>
+        <v>440</v>
+      </c>
+      <c r="J45" s="8">
+        <f>I45-10</f>
+        <v>430</v>
+      </c>
+      <c r="K45" s="15">
+        <v>440</v>
+      </c>
+      <c r="L45" s="14">
+        <f>K45+20</f>
+        <v>460</v>
+      </c>
+      <c r="M45" s="8">
+        <f>L45+10</f>
         <v>470</v>
       </c>
-      <c r="J45" s="8">
+      <c r="N45" s="8">
+        <f>M45+20</f>
         <v>490</v>
       </c>
-      <c r="K45" s="8">
+      <c r="O45" s="8">
+        <f>N45+20</f>
         <v>510</v>
       </c>
-      <c r="L45" s="8">
+      <c r="P45" s="8">
+        <f>O45-10</f>
         <v>500</v>
       </c>
-      <c r="M45" s="14" t="s">
+      <c r="Q45" s="15" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="46" spans="2:13">
+    <row r="46" spans="2:17">
       <c r="B46" s="7" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="C46" s="8">
         <v>420</v>
@@ -6416,24 +8068,43 @@
         <v>460</v>
       </c>
       <c r="I46" s="8">
+        <f>H46-10</f>
+        <v>450</v>
+      </c>
+      <c r="J46" s="8">
+        <f>I46-10</f>
+        <v>440</v>
+      </c>
+      <c r="K46" s="8">
+        <v>450</v>
+      </c>
+      <c r="L46" s="8">
+        <f>K46+20</f>
+        <v>470</v>
+      </c>
+      <c r="M46" s="8">
+        <f>L46+10</f>
         <v>480</v>
       </c>
-      <c r="J46" s="8">
+      <c r="N46" s="8">
+        <f>M46+20</f>
         <v>500</v>
       </c>
-      <c r="K46" s="8">
+      <c r="O46" s="8">
+        <f>N46+20</f>
         <v>520</v>
       </c>
-      <c r="L46" s="8">
+      <c r="P46" s="8">
+        <f>O46-10</f>
         <v>510</v>
       </c>
-      <c r="M46" s="8" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="47" spans="2:13">
+      <c r="Q46" s="8" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="47" spans="2:17">
       <c r="B47" s="7" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="C47" s="8">
         <v>430</v>
@@ -6456,34 +8127,56 @@
         <v>470</v>
       </c>
       <c r="I47" s="8">
+        <f>H47-10</f>
+        <v>460</v>
+      </c>
+      <c r="J47" s="8">
+        <f>I47-10</f>
+        <v>450</v>
+      </c>
+      <c r="K47" s="8">
+        <v>460</v>
+      </c>
+      <c r="L47" s="8">
+        <f>K47+20</f>
+        <v>480</v>
+      </c>
+      <c r="M47" s="8">
+        <f>L47+10</f>
         <v>490</v>
       </c>
-      <c r="J47" s="8">
+      <c r="N47" s="8">
+        <f>M47+20</f>
         <v>510</v>
       </c>
-      <c r="K47" s="8">
+      <c r="O47" s="8">
+        <f>N47+20</f>
         <v>530</v>
       </c>
-      <c r="L47" s="8">
+      <c r="P47" s="8">
+        <f>O47-10</f>
         <v>520</v>
       </c>
-      <c r="M47" s="8" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="48" spans="2:13">
+      <c r="Q47" s="8" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="48" spans="2:17">
       <c r="B48" s="13"/>
-      <c r="K48" s="8">
+      <c r="K48" s="15"/>
+      <c r="L48" s="14"/>
+      <c r="O48" s="8">
         <v>520</v>
       </c>
-      <c r="L48" s="8">
+      <c r="P48" s="8">
+        <f>O48-10</f>
         <v>510</v>
       </c>
-      <c r="M48" s="8" t="s">
+      <c r="Q48" s="8" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="49" spans="2:13">
+    <row r="49" spans="2:17">
       <c r="B49" s="13" t="s">
         <v>36</v>
       </c>
@@ -6508,24 +8201,43 @@
         <v>450</v>
       </c>
       <c r="I49" s="8">
+        <f>H49-10</f>
+        <v>440</v>
+      </c>
+      <c r="J49" s="8">
+        <f>I49-10</f>
+        <v>430</v>
+      </c>
+      <c r="K49" s="15">
+        <v>440</v>
+      </c>
+      <c r="L49" s="14">
+        <f>K49+20</f>
+        <v>460</v>
+      </c>
+      <c r="M49" s="8">
+        <f>L49+10</f>
         <v>470</v>
       </c>
-      <c r="J49" s="8">
+      <c r="N49" s="8">
+        <f>M49+20</f>
         <v>490</v>
       </c>
-      <c r="K49" s="8">
+      <c r="O49" s="8">
+        <f>N49+20</f>
         <v>510</v>
       </c>
-      <c r="L49" s="8">
+      <c r="P49" s="8">
+        <f>O49-10</f>
         <v>500</v>
       </c>
-      <c r="M49" s="14" t="s">
+      <c r="Q49" s="15" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="50" spans="2:13">
+    <row r="50" spans="2:17">
       <c r="B50" s="13" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="C50" s="8">
         <v>410</v>
@@ -6547,11 +8259,21 @@
       <c r="H50" s="8">
         <v>450</v>
       </c>
-      <c r="M50" s="14" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="51" spans="2:13">
+      <c r="I50" s="8">
+        <f>H50-10</f>
+        <v>440</v>
+      </c>
+      <c r="J50" s="8">
+        <f>I50-10</f>
+        <v>430</v>
+      </c>
+      <c r="K50" s="15"/>
+      <c r="L50" s="14"/>
+      <c r="Q50" s="15" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="51" spans="2:17">
       <c r="B51" s="7" t="s">
         <v>64</v>
       </c>
@@ -6576,22 +8298,41 @@
         <v>490</v>
       </c>
       <c r="I51" s="8">
+        <f>H51-10</f>
+        <v>480</v>
+      </c>
+      <c r="J51" s="8">
+        <f>I51-10</f>
+        <v>470</v>
+      </c>
+      <c r="K51" s="8">
+        <v>480</v>
+      </c>
+      <c r="L51" s="8">
+        <f>K51+20</f>
+        <v>500</v>
+      </c>
+      <c r="M51" s="8">
+        <f>L51+10</f>
         <v>510</v>
       </c>
-      <c r="J51" s="8">
+      <c r="N51" s="8">
+        <f>M51+20</f>
         <v>530</v>
       </c>
-      <c r="K51" s="8">
+      <c r="O51" s="8">
+        <f>N51+20</f>
         <v>550</v>
       </c>
-      <c r="L51" s="8">
+      <c r="P51" s="8">
+        <f>O51-10</f>
         <v>540</v>
       </c>
-      <c r="M51" s="8" t="s">
+      <c r="Q51" s="8" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="52" spans="2:13">
+    <row r="52" spans="2:17">
       <c r="B52" s="7" t="s">
         <v>33</v>
       </c>
@@ -6599,24 +8340,42 @@
         <v>480</v>
       </c>
       <c r="I52" s="8">
+        <f>H52-10</f>
+        <v>-10</v>
+      </c>
+      <c r="J52" s="8">
+        <v>440</v>
+      </c>
+      <c r="K52" s="8">
+        <v>450</v>
+      </c>
+      <c r="L52" s="8">
+        <f>K52+20</f>
+        <v>470</v>
+      </c>
+      <c r="M52" s="8">
+        <f>L52+10</f>
         <v>480</v>
       </c>
-      <c r="J52" s="8">
+      <c r="N52" s="8">
+        <f>M52+20</f>
         <v>500</v>
       </c>
-      <c r="K52" s="8">
+      <c r="O52" s="8">
+        <f>N52+20</f>
         <v>520</v>
       </c>
-      <c r="L52" s="8">
+      <c r="P52" s="8">
+        <f>O52-10</f>
         <v>510</v>
       </c>
-      <c r="M52" s="8" t="s">
+      <c r="Q52" s="8" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="53" spans="2:13">
+    <row r="53" spans="2:17">
       <c r="B53" s="7" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="C53" s="8">
         <v>450</v>
@@ -6639,22 +8398,41 @@
         <v>490</v>
       </c>
       <c r="I53" s="8">
+        <f>H53-10</f>
+        <v>480</v>
+      </c>
+      <c r="J53" s="8">
+        <f>I53-10</f>
+        <v>470</v>
+      </c>
+      <c r="K53" s="8">
+        <v>480</v>
+      </c>
+      <c r="L53" s="8">
+        <f>K53+20</f>
+        <v>500</v>
+      </c>
+      <c r="M53" s="8">
+        <f>L53+10</f>
         <v>510</v>
       </c>
-      <c r="J53" s="8">
+      <c r="N53" s="8">
+        <f>M53+20</f>
         <v>530</v>
       </c>
-      <c r="K53" s="8">
+      <c r="O53" s="8">
+        <f>N53+20</f>
         <v>550</v>
       </c>
-      <c r="L53" s="8">
+      <c r="P53" s="8">
+        <f>O53-10</f>
         <v>540</v>
       </c>
-      <c r="M53" s="8" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="54" spans="2:13">
+      <c r="Q53" s="8" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="54" spans="2:17">
       <c r="B54" s="7" t="s">
         <v>35</v>
       </c>
@@ -6679,22 +8457,41 @@
         <v>470</v>
       </c>
       <c r="I54" s="8">
+        <f>H54-10</f>
+        <v>460</v>
+      </c>
+      <c r="J54" s="8">
+        <f>I54-10</f>
+        <v>450</v>
+      </c>
+      <c r="K54" s="8">
+        <v>460</v>
+      </c>
+      <c r="L54" s="8">
+        <f>K54+20</f>
+        <v>480</v>
+      </c>
+      <c r="M54" s="8">
+        <f>L54+10</f>
         <v>490</v>
       </c>
-      <c r="J54" s="8">
+      <c r="N54" s="8">
+        <f>M54+20</f>
         <v>510</v>
       </c>
-      <c r="K54" s="8">
+      <c r="O54" s="8">
+        <f>N54+20</f>
         <v>530</v>
       </c>
-      <c r="L54" s="8">
+      <c r="P54" s="8">
+        <f>O54-10</f>
         <v>520</v>
       </c>
-      <c r="M54" s="8" t="s">
+      <c r="Q54" s="8" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="55" spans="2:13">
+    <row r="55" spans="2:17">
       <c r="B55" s="7" t="s">
         <v>34</v>
       </c>
@@ -6719,24 +8516,41 @@
         <v>475</v>
       </c>
       <c r="I55" s="8">
+        <v>460</v>
+      </c>
+      <c r="J55" s="8">
+        <v>450</v>
+      </c>
+      <c r="K55" s="8">
+        <v>460</v>
+      </c>
+      <c r="L55" s="8">
+        <f>K55+20</f>
+        <v>480</v>
+      </c>
+      <c r="M55" s="8">
+        <f>L55+10</f>
         <v>490</v>
       </c>
-      <c r="J55" s="8">
+      <c r="N55" s="8">
+        <f>M55+20</f>
         <v>510</v>
       </c>
-      <c r="K55" s="8">
+      <c r="O55" s="8">
+        <f>N55+20</f>
         <v>530</v>
       </c>
-      <c r="L55" s="8">
+      <c r="P55" s="8">
+        <f>O55-10</f>
         <v>520</v>
       </c>
-      <c r="M55" s="8" t="s">
+      <c r="Q55" s="8" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="56" spans="2:13">
+    <row r="56" spans="2:17">
       <c r="B56" s="7" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="C56" s="8">
         <v>425</v>
@@ -6759,24 +8573,43 @@
         <v>465</v>
       </c>
       <c r="I56" s="8">
+        <f>H56-10</f>
+        <v>455</v>
+      </c>
+      <c r="J56" s="8">
+        <f>I56-10</f>
+        <v>445</v>
+      </c>
+      <c r="K56" s="8">
+        <v>450</v>
+      </c>
+      <c r="L56" s="8">
+        <f>K56+20</f>
+        <v>470</v>
+      </c>
+      <c r="M56" s="8">
+        <f>L56+10</f>
         <v>480</v>
       </c>
-      <c r="J56" s="8">
+      <c r="N56" s="8">
+        <f>M56+20</f>
         <v>500</v>
       </c>
-      <c r="K56" s="8">
+      <c r="O56" s="8">
+        <f>N56+20</f>
         <v>520</v>
       </c>
-      <c r="L56" s="8">
+      <c r="P56" s="8">
+        <f>O56-10</f>
         <v>510</v>
       </c>
-      <c r="M56" s="8" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="57" spans="2:13">
+      <c r="Q56" s="8" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="57" spans="2:17">
       <c r="B57" s="7" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="C57" s="8">
         <v>440</v>
@@ -6799,24 +8632,43 @@
         <v>480</v>
       </c>
       <c r="I57" s="8">
+        <f>H57-10</f>
+        <v>470</v>
+      </c>
+      <c r="J57" s="8">
+        <f>I57-10</f>
+        <v>460</v>
+      </c>
+      <c r="K57" s="8">
+        <v>470</v>
+      </c>
+      <c r="L57" s="8">
+        <f>K57+20</f>
+        <v>490</v>
+      </c>
+      <c r="M57" s="8">
+        <f>L57+10</f>
         <v>500</v>
       </c>
-      <c r="J57" s="8">
+      <c r="N57" s="8">
+        <f>M57+20</f>
         <v>520</v>
       </c>
-      <c r="K57" s="8">
+      <c r="O57" s="8">
+        <f>N57+20</f>
         <v>540</v>
       </c>
-      <c r="L57" s="8">
+      <c r="P57" s="8">
+        <f>O57-10</f>
         <v>530</v>
       </c>
-      <c r="M57" s="8" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="58" spans="2:13">
+      <c r="Q57" s="8" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="58" spans="2:17">
       <c r="B58" s="7" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="C58" s="8">
         <v>440</v>
@@ -6839,22 +8691,40 @@
         <v>480</v>
       </c>
       <c r="I58" s="8">
+        <f>H58-10</f>
+        <v>470</v>
+      </c>
+      <c r="J58" s="8">
+        <f>I58-10</f>
+        <v>460</v>
+      </c>
+      <c r="K58" s="8">
+        <v>470</v>
+      </c>
+      <c r="L58" s="8">
+        <f>K58+20</f>
+        <v>490</v>
+      </c>
+      <c r="M58" s="8">
+        <f>L58+10</f>
         <v>500</v>
       </c>
-      <c r="J58" s="8">
+      <c r="N58" s="8">
         <v>530</v>
       </c>
-      <c r="K58" s="8">
+      <c r="O58" s="8">
+        <f>N58+20</f>
         <v>550</v>
       </c>
-      <c r="L58" s="8">
+      <c r="P58" s="8">
+        <f>O58-10</f>
         <v>540</v>
       </c>
-      <c r="M58" s="8" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="59" spans="2:13">
+      <c r="Q58" s="8" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="59" spans="2:17">
       <c r="B59" s="7" t="s">
         <v>32</v>
       </c>
@@ -6879,22 +8749,41 @@
         <v>480</v>
       </c>
       <c r="I59" s="8">
+        <f>H59-10</f>
+        <v>470</v>
+      </c>
+      <c r="J59" s="8">
+        <f>I59-10</f>
+        <v>460</v>
+      </c>
+      <c r="K59" s="8">
+        <v>470</v>
+      </c>
+      <c r="L59" s="8">
+        <f>K59+20</f>
+        <v>490</v>
+      </c>
+      <c r="M59" s="8">
+        <f>L59+10</f>
         <v>500</v>
       </c>
-      <c r="J59" s="8">
+      <c r="N59" s="8">
+        <f>M59+20</f>
         <v>520</v>
       </c>
-      <c r="K59" s="8">
+      <c r="O59" s="8">
+        <f>N59+20</f>
         <v>540</v>
       </c>
-      <c r="L59" s="8">
+      <c r="P59" s="8">
+        <f>O59-10</f>
         <v>530</v>
       </c>
-      <c r="M59" s="8" t="s">
+      <c r="Q59" s="8" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="60" spans="2:13">
+    <row r="60" spans="2:17">
       <c r="B60" s="13" t="s">
         <v>68</v>
       </c>
@@ -6919,24 +8808,43 @@
         <v>450</v>
       </c>
       <c r="I60" s="8">
+        <f>H60-10</f>
+        <v>440</v>
+      </c>
+      <c r="J60" s="8">
+        <f>I60-10</f>
+        <v>430</v>
+      </c>
+      <c r="K60" s="15">
+        <v>440</v>
+      </c>
+      <c r="L60" s="14">
+        <f>K60+20</f>
+        <v>460</v>
+      </c>
+      <c r="M60" s="8">
+        <f>L60+10</f>
         <v>470</v>
       </c>
-      <c r="J60" s="8">
+      <c r="N60" s="8">
+        <f>M60+20</f>
         <v>490</v>
       </c>
-      <c r="K60" s="8">
+      <c r="O60" s="8">
+        <f>N60+20</f>
         <v>510</v>
       </c>
-      <c r="L60" s="8">
+      <c r="P60" s="8">
+        <f>O60-10</f>
         <v>500</v>
       </c>
-      <c r="M60" s="14" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="61" spans="2:13">
+      <c r="Q60" s="15" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="61" spans="2:17">
       <c r="B61" s="7" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="C61" s="8">
         <v>430</v>
@@ -6959,24 +8867,43 @@
         <v>470</v>
       </c>
       <c r="I61" s="8">
+        <f>H61-10</f>
+        <v>460</v>
+      </c>
+      <c r="J61" s="8">
+        <f>I61-10</f>
+        <v>450</v>
+      </c>
+      <c r="K61" s="8">
+        <v>470</v>
+      </c>
+      <c r="L61" s="8">
+        <f>K61+20</f>
+        <v>490</v>
+      </c>
+      <c r="M61" s="8">
+        <f>L61+10</f>
         <v>500</v>
       </c>
-      <c r="J61" s="8">
+      <c r="N61" s="8">
+        <f>M61+20</f>
         <v>520</v>
       </c>
-      <c r="K61" s="8">
+      <c r="O61" s="8">
+        <f>N61+20</f>
         <v>540</v>
       </c>
-      <c r="L61" s="8">
+      <c r="P61" s="8">
+        <f>O61-10</f>
         <v>530</v>
       </c>
-      <c r="M61" s="8" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="62" spans="2:13">
+      <c r="Q61" s="8" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="62" spans="2:17">
       <c r="B62" s="13" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="C62" s="8">
         <v>410</v>
@@ -6999,22 +8926,41 @@
         <v>450</v>
       </c>
       <c r="I62" s="8">
+        <f>H62-10</f>
+        <v>440</v>
+      </c>
+      <c r="J62" s="8">
+        <f>I62-10</f>
+        <v>430</v>
+      </c>
+      <c r="K62" s="15">
+        <v>440</v>
+      </c>
+      <c r="L62" s="14">
+        <f>K62+20</f>
+        <v>460</v>
+      </c>
+      <c r="M62" s="8">
+        <f>L62+10</f>
         <v>470</v>
       </c>
-      <c r="J62" s="8">
+      <c r="N62" s="8">
+        <f>M62+20</f>
         <v>490</v>
       </c>
-      <c r="K62" s="8">
+      <c r="O62" s="8">
+        <f>N62+20</f>
         <v>510</v>
       </c>
-      <c r="L62" s="8">
+      <c r="P62" s="8">
+        <f>O62-10</f>
         <v>500</v>
       </c>
-      <c r="M62" s="14" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="63" spans="2:13">
+      <c r="Q62" s="15" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="63" spans="2:17">
       <c r="B63" s="7" t="s">
         <v>29</v>
       </c>
@@ -7039,28 +8985,50 @@
         <v>475</v>
       </c>
       <c r="I63" s="8">
+        <f>H63-10</f>
+        <v>465</v>
+      </c>
+      <c r="J63" s="8">
+        <f>I63-10</f>
+        <v>455</v>
+      </c>
+      <c r="K63" s="8">
+        <v>465</v>
+      </c>
+      <c r="L63" s="8">
+        <f>K63+20</f>
+        <v>485</v>
+      </c>
+      <c r="M63" s="8">
+        <f>L63+10</f>
         <v>495</v>
       </c>
-      <c r="J63" s="8">
+      <c r="N63" s="8">
+        <f>M63+20</f>
         <v>515</v>
       </c>
-      <c r="K63" s="8">
+      <c r="O63" s="8">
+        <f>N63+20</f>
         <v>535</v>
       </c>
-      <c r="L63" s="8">
+      <c r="P63" s="8">
+        <f>O63-10</f>
         <v>525</v>
       </c>
-      <c r="M63" s="8" t="s">
+      <c r="Q63" s="8" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="64" spans="2:13">
+    <row r="64" spans="2:17">
       <c r="D64" s="11"/>
-      <c r="M64" s="9"/>
-    </row>
-    <row r="65" spans="2:13">
+      <c r="K64" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="Q64" s="9"/>
+    </row>
+    <row r="65" spans="2:17">
       <c r="B65" s="7" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="C65" s="8">
         <v>440</v>
@@ -7081,24 +9049,40 @@
         <v>480</v>
       </c>
       <c r="I65" s="8">
+        <v>470</v>
+      </c>
+      <c r="J65" s="8">
+        <v>460</v>
+      </c>
+      <c r="K65" s="8">
+        <v>470</v>
+      </c>
+      <c r="L65" s="8">
+        <f>K65+20</f>
+        <v>490</v>
+      </c>
+      <c r="M65" s="8">
+        <f>L65+10</f>
         <v>500</v>
       </c>
-      <c r="J65" s="8">
+      <c r="N65" s="8">
+        <f>M65+20</f>
         <v>520</v>
       </c>
-      <c r="K65" s="8">
+      <c r="O65" s="8">
         <v>540</v>
       </c>
-      <c r="L65" s="8">
+      <c r="P65" s="8">
+        <f>O65-10</f>
         <v>530</v>
       </c>
-      <c r="M65" s="8" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="66" spans="2:13">
+      <c r="Q65" s="8" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17">
       <c r="B66" s="7" t="s">
-        <v>109</v>
+        <v>84</v>
       </c>
       <c r="C66" s="8">
         <v>440</v>
@@ -7119,24 +9103,40 @@
         <v>480</v>
       </c>
       <c r="I66" s="8">
+        <v>470</v>
+      </c>
+      <c r="J66" s="8">
+        <v>460</v>
+      </c>
+      <c r="K66" s="8">
+        <v>470</v>
+      </c>
+      <c r="L66" s="8">
+        <f>K66+20</f>
+        <v>490</v>
+      </c>
+      <c r="M66" s="8">
+        <f>L66+10</f>
         <v>500</v>
       </c>
-      <c r="J66" s="8">
+      <c r="N66" s="8">
+        <f>M66+20</f>
         <v>520</v>
       </c>
-      <c r="K66" s="8">
+      <c r="O66" s="8">
         <v>540</v>
       </c>
-      <c r="L66" s="8">
+      <c r="P66" s="8">
+        <f>O66-10</f>
         <v>530</v>
       </c>
-      <c r="M66" s="8" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="67" spans="2:13">
+      <c r="Q66" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="67" spans="2:17">
       <c r="B67" s="7" t="s">
-        <v>149</v>
+        <v>78</v>
       </c>
       <c r="C67" s="8">
         <v>430</v>
@@ -7157,24 +9157,40 @@
         <v>470</v>
       </c>
       <c r="I67" s="8">
+        <v>460</v>
+      </c>
+      <c r="J67" s="8">
+        <v>450</v>
+      </c>
+      <c r="K67" s="8">
+        <v>460</v>
+      </c>
+      <c r="L67" s="8">
+        <f>K67+20</f>
+        <v>480</v>
+      </c>
+      <c r="M67" s="8">
+        <f>L67+10</f>
         <v>490</v>
       </c>
-      <c r="J67" s="8">
+      <c r="N67" s="8">
+        <f>M67+20</f>
         <v>510</v>
       </c>
-      <c r="K67" s="8">
+      <c r="O67" s="8">
         <v>530</v>
       </c>
-      <c r="L67" s="8">
+      <c r="P67" s="8">
+        <f>O67-10</f>
         <v>520</v>
       </c>
-      <c r="M67" s="8" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="68" spans="2:13">
+      <c r="Q67" s="8" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="68" spans="2:17">
       <c r="B68" s="7" t="s">
-        <v>111</v>
+        <v>80</v>
       </c>
       <c r="C68" s="8">
         <v>440</v>
@@ -7195,24 +9211,40 @@
         <v>480</v>
       </c>
       <c r="I68" s="8">
+        <v>470</v>
+      </c>
+      <c r="J68" s="8">
+        <v>460</v>
+      </c>
+      <c r="K68" s="8">
+        <v>470</v>
+      </c>
+      <c r="L68" s="8">
+        <f>K68+20</f>
+        <v>490</v>
+      </c>
+      <c r="M68" s="8">
+        <f>L68+10</f>
         <v>500</v>
       </c>
-      <c r="J68" s="8">
+      <c r="N68" s="8">
+        <f>M68+20</f>
         <v>520</v>
       </c>
-      <c r="K68" s="8">
+      <c r="O68" s="8">
         <v>540</v>
       </c>
-      <c r="L68" s="8">
+      <c r="P68" s="8">
+        <f>O68-10</f>
         <v>530</v>
       </c>
-      <c r="M68" s="8" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="69" spans="2:13">
+      <c r="Q68" s="8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17">
       <c r="B69" s="7" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="C69" s="8">
         <v>430</v>
@@ -7233,24 +9265,40 @@
         <v>480</v>
       </c>
       <c r="I69" s="8">
+        <v>470</v>
+      </c>
+      <c r="J69" s="8">
+        <v>460</v>
+      </c>
+      <c r="K69" s="8">
+        <v>480</v>
+      </c>
+      <c r="L69" s="8">
+        <f>K69+20</f>
+        <v>500</v>
+      </c>
+      <c r="M69" s="8">
+        <f>L69+10</f>
         <v>510</v>
       </c>
-      <c r="J69" s="8">
+      <c r="N69" s="8">
+        <f>M69+20</f>
         <v>530</v>
       </c>
-      <c r="K69" s="8">
+      <c r="O69" s="8">
         <v>550</v>
       </c>
-      <c r="L69" s="8">
+      <c r="P69" s="8">
+        <f>O69-10</f>
         <v>540</v>
       </c>
-      <c r="M69" s="8" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="70" spans="2:13">
+      <c r="Q69" s="8" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17">
       <c r="B70" s="7" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="E70" s="8">
         <v>490</v>
@@ -7265,22 +9313,38 @@
         <v>490</v>
       </c>
       <c r="I70" s="8">
+        <v>480</v>
+      </c>
+      <c r="J70" s="8">
+        <v>470</v>
+      </c>
+      <c r="K70" s="8">
+        <v>480</v>
+      </c>
+      <c r="L70" s="8">
+        <f>K70+20</f>
+        <v>500</v>
+      </c>
+      <c r="M70" s="8">
+        <f>L70+10</f>
         <v>510</v>
       </c>
-      <c r="J70" s="8">
+      <c r="N70" s="8">
+        <f>M70+20</f>
         <v>530</v>
       </c>
-      <c r="K70" s="8">
+      <c r="O70" s="8">
         <v>550</v>
       </c>
-      <c r="L70" s="8">
+      <c r="P70" s="8">
+        <f>O70-10</f>
         <v>540</v>
       </c>
-      <c r="M70" s="8" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="71" spans="2:13">
+      <c r="Q70" s="8" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17">
       <c r="B71" s="7" t="s">
         <v>85</v>
       </c>
@@ -7297,68 +9361,110 @@
         <v>480</v>
       </c>
       <c r="I71" s="8">
+        <v>460</v>
+      </c>
+      <c r="J71" s="8">
+        <v>440</v>
+      </c>
+      <c r="K71" s="8">
+        <v>450</v>
+      </c>
+      <c r="L71" s="8">
+        <f>K71+20</f>
+        <v>470</v>
+      </c>
+      <c r="M71" s="8">
+        <f>L71+10</f>
         <v>480</v>
       </c>
-      <c r="J71" s="8">
+      <c r="N71" s="8">
+        <f>M71+20</f>
         <v>500</v>
       </c>
-      <c r="K71" s="8">
+      <c r="O71" s="8">
         <v>520</v>
       </c>
-      <c r="L71" s="8">
+      <c r="P71" s="8">
+        <f>O71-10</f>
         <v>510</v>
       </c>
-      <c r="M71" s="8" t="s">
+      <c r="Q71" s="8" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="72" spans="2:13">
+    <row r="72" spans="2:17">
       <c r="B72" s="7" t="s">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="F72" s="8" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="I72" s="8">
+        <v>470</v>
+      </c>
+      <c r="J72" s="8">
+        <v>460</v>
+      </c>
+      <c r="K72" s="8">
+        <v>470</v>
+      </c>
+      <c r="L72" s="8">
+        <f>K72+20</f>
+        <v>490</v>
+      </c>
+      <c r="M72" s="8">
+        <f>L72+10</f>
         <v>500</v>
       </c>
-      <c r="J72" s="8">
+      <c r="N72" s="8">
+        <f>M72+20</f>
         <v>520</v>
       </c>
-      <c r="K72" s="8">
+      <c r="O72" s="8">
         <v>540</v>
       </c>
-      <c r="L72" s="8">
+      <c r="P72" s="8">
+        <f>O72-10</f>
         <v>530</v>
       </c>
-      <c r="M72" s="8" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="73" spans="2:13">
-      <c r="I73" s="8">
+      <c r="Q72" s="8" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="73" spans="2:17">
+      <c r="K73" s="8">
+        <v>460</v>
+      </c>
+      <c r="L73" s="8">
+        <f>K73+20</f>
+        <v>480</v>
+      </c>
+      <c r="M73" s="8">
+        <f>L73+10</f>
         <v>490</v>
       </c>
-      <c r="J73" s="8">
+      <c r="N73" s="8">
+        <f>M73+20</f>
         <v>510</v>
       </c>
-      <c r="K73" s="8">
+      <c r="O73" s="8">
         <v>530</v>
       </c>
-      <c r="L73" s="8">
+      <c r="P73" s="8">
+        <f>O73-10</f>
         <v>520</v>
       </c>
-      <c r="M73" s="8" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="74" spans="2:13">
-      <c r="M74" s="8" t="s">
-        <v>156</v>
+      <c r="Q73" s="8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17">
+      <c r="Q74" s="8" t="s">
+        <v>76</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:O74" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:S74" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/11.xlsx
+++ b/11.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255" firstSheet="2" activeTab="2"/>
+    <workbookView windowWidth="28800" windowHeight="11655" firstSheet="2" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -346,7 +346,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="166">
   <si>
     <t>客户名称</t>
   </si>
@@ -857,10 +857,10 @@
     <t>HMI</t>
   </si>
   <si>
+    <t>APW</t>
+  </si>
+  <si>
     <t>原价</t>
-  </si>
-  <si>
-    <t>APW</t>
   </si>
 </sst>
 </file>
@@ -1106,7 +1106,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="42">
+  <fills count="40">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1146,18 +1146,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE6E4E4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE2EFDA"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1501,7 +1489,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="2">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
@@ -1525,16 +1513,16 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="5">
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="6">
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="6">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="5">
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="7">
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="7">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="8">
@@ -1543,89 +1531,89 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="9">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0">
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="0">
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="17" borderId="0">
+    <xf numFmtId="0" fontId="27" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="0">
+    <xf numFmtId="0" fontId="28" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="19" borderId="0">
+    <xf numFmtId="0" fontId="29" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="20" borderId="0">
+    <xf numFmtId="0" fontId="29" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="21" borderId="0">
+    <xf numFmtId="0" fontId="28" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="22" borderId="0">
+    <xf numFmtId="0" fontId="28" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="23" borderId="0">
+    <xf numFmtId="0" fontId="29" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="24" borderId="0">
+    <xf numFmtId="0" fontId="29" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="25" borderId="0">
+    <xf numFmtId="0" fontId="28" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="26" borderId="0">
+    <xf numFmtId="0" fontId="28" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="27" borderId="0">
+    <xf numFmtId="0" fontId="29" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="28" borderId="0">
+    <xf numFmtId="0" fontId="29" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="29" borderId="0">
+    <xf numFmtId="0" fontId="28" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="30" borderId="0">
+    <xf numFmtId="0" fontId="28" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="31" borderId="0">
+    <xf numFmtId="0" fontId="29" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="29" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="28" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="34" borderId="0">
+    <xf numFmtId="0" fontId="28" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="35" borderId="0">
+    <xf numFmtId="0" fontId="29" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="36" borderId="0">
+    <xf numFmtId="0" fontId="29" fillId="34" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="37" borderId="0">
+    <xf numFmtId="0" fontId="28" fillId="35" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="38" borderId="0">
+    <xf numFmtId="0" fontId="28" fillId="36" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="39" borderId="0">
+    <xf numFmtId="0" fontId="29" fillId="37" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="40" borderId="0">
+    <xf numFmtId="0" fontId="29" fillId="38" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="41" borderId="0">
+    <xf numFmtId="0" fontId="28" fillId="39" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1717,25 +1705,7 @@
     <xf numFmtId="176" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="10" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -4717,544 +4687,544 @@
       <c r="AJ44" s="25"/>
     </row>
     <row r="45" ht="16.5" spans="1:36">
-      <c r="A45" s="31" t="s">
+      <c r="A45" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="B45" s="32"/>
-      <c r="C45" s="33" t="s">
+      <c r="B45" s="6"/>
+      <c r="C45" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D45" s="32"/>
-      <c r="E45" s="32"/>
-      <c r="F45" s="34"/>
-      <c r="G45" s="35">
+      <c r="D45" s="6"/>
+      <c r="E45" s="6"/>
+      <c r="F45" s="5"/>
+      <c r="G45" s="27">
         <v>545000</v>
       </c>
-      <c r="H45" s="35">
+      <c r="H45" s="27">
         <v>246617600</v>
       </c>
-      <c r="I45" s="34"/>
-      <c r="J45" s="35"/>
-      <c r="K45" s="35"/>
-      <c r="L45" s="34"/>
-      <c r="M45" s="35"/>
-      <c r="N45" s="35"/>
-      <c r="O45" s="34"/>
-      <c r="P45" s="35"/>
-      <c r="Q45" s="35"/>
-      <c r="R45" s="34"/>
-      <c r="S45" s="35"/>
-      <c r="T45" s="35"/>
-      <c r="U45" s="34"/>
-      <c r="V45" s="35"/>
-      <c r="W45" s="35"/>
-      <c r="X45" s="34"/>
-      <c r="Y45" s="35"/>
-      <c r="Z45" s="35"/>
-      <c r="AA45" s="34"/>
-      <c r="AB45" s="35"/>
-      <c r="AC45" s="35"/>
+      <c r="I45" s="5"/>
+      <c r="J45" s="27"/>
+      <c r="K45" s="27"/>
+      <c r="L45" s="5"/>
+      <c r="M45" s="27"/>
+      <c r="N45" s="27"/>
+      <c r="O45" s="5"/>
+      <c r="P45" s="27"/>
+      <c r="Q45" s="27"/>
+      <c r="R45" s="5"/>
+      <c r="S45" s="27"/>
+      <c r="T45" s="27"/>
+      <c r="U45" s="5"/>
+      <c r="V45" s="27"/>
+      <c r="W45" s="27"/>
+      <c r="X45" s="5"/>
+      <c r="Y45" s="27"/>
+      <c r="Z45" s="27"/>
+      <c r="AA45" s="5"/>
+      <c r="AB45" s="27"/>
+      <c r="AC45" s="27"/>
     </row>
     <row r="46" ht="16.5" spans="1:36">
-      <c r="A46" s="31" t="s">
+      <c r="A46" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="B46" s="32">
+      <c r="B46" s="6">
         <v>530000</v>
       </c>
-      <c r="C46" s="33" t="s">
+      <c r="C46" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D46" s="32"/>
-      <c r="E46" s="32"/>
-      <c r="F46" s="34"/>
-      <c r="G46" s="35">
+      <c r="D46" s="6"/>
+      <c r="E46" s="6"/>
+      <c r="F46" s="5"/>
+      <c r="G46" s="27">
         <v>530000</v>
       </c>
-      <c r="H46" s="35">
-        <v>0</v>
-      </c>
-      <c r="I46" s="34"/>
-      <c r="J46" s="35"/>
-      <c r="K46" s="35"/>
-      <c r="L46" s="34"/>
-      <c r="M46" s="35"/>
-      <c r="N46" s="35"/>
-      <c r="O46" s="34"/>
-      <c r="P46" s="35"/>
-      <c r="Q46" s="35"/>
-      <c r="R46" s="34"/>
-      <c r="S46" s="35"/>
-      <c r="T46" s="35"/>
-      <c r="U46" s="34"/>
-      <c r="V46" s="35"/>
-      <c r="W46" s="35"/>
-      <c r="X46" s="34"/>
-      <c r="Y46" s="35"/>
-      <c r="Z46" s="35"/>
-      <c r="AA46" s="34"/>
-      <c r="AB46" s="35"/>
-      <c r="AC46" s="35"/>
+      <c r="H46" s="27">
+        <v>0</v>
+      </c>
+      <c r="I46" s="5"/>
+      <c r="J46" s="27"/>
+      <c r="K46" s="27"/>
+      <c r="L46" s="5"/>
+      <c r="M46" s="27"/>
+      <c r="N46" s="27"/>
+      <c r="O46" s="5"/>
+      <c r="P46" s="27"/>
+      <c r="Q46" s="27"/>
+      <c r="R46" s="5"/>
+      <c r="S46" s="27"/>
+      <c r="T46" s="27"/>
+      <c r="U46" s="5"/>
+      <c r="V46" s="27"/>
+      <c r="W46" s="27"/>
+      <c r="X46" s="5"/>
+      <c r="Y46" s="27"/>
+      <c r="Z46" s="27"/>
+      <c r="AA46" s="5"/>
+      <c r="AB46" s="27"/>
+      <c r="AC46" s="27"/>
     </row>
     <row r="47" ht="16.5" spans="1:36">
-      <c r="A47" s="31" t="s">
+      <c r="A47" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="B47" s="32"/>
-      <c r="C47" s="33" t="s">
+      <c r="B47" s="6"/>
+      <c r="C47" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D47" s="32"/>
-      <c r="E47" s="32"/>
-      <c r="F47" s="34"/>
-      <c r="G47" s="35">
+      <c r="D47" s="6"/>
+      <c r="E47" s="6"/>
+      <c r="F47" s="5"/>
+      <c r="G47" s="27">
         <v>500000</v>
       </c>
-      <c r="H47" s="35">
-        <v>0</v>
-      </c>
-      <c r="I47" s="34"/>
-      <c r="J47" s="35">
+      <c r="H47" s="27">
+        <v>0</v>
+      </c>
+      <c r="I47" s="5"/>
+      <c r="J47" s="27">
         <v>520000</v>
       </c>
-      <c r="K47" s="35">
-        <v>0</v>
-      </c>
-      <c r="L47" s="34"/>
-      <c r="M47" s="35"/>
-      <c r="N47" s="35"/>
-      <c r="O47" s="34"/>
-      <c r="P47" s="35"/>
-      <c r="Q47" s="35"/>
-      <c r="R47" s="34"/>
-      <c r="S47" s="35"/>
-      <c r="T47" s="35"/>
-      <c r="U47" s="34"/>
-      <c r="V47" s="35"/>
-      <c r="W47" s="35"/>
-      <c r="X47" s="34"/>
-      <c r="Y47" s="35"/>
-      <c r="Z47" s="35"/>
-      <c r="AA47" s="34"/>
-      <c r="AB47" s="35"/>
-      <c r="AC47" s="35"/>
+      <c r="K47" s="27">
+        <v>0</v>
+      </c>
+      <c r="L47" s="5"/>
+      <c r="M47" s="27"/>
+      <c r="N47" s="27"/>
+      <c r="O47" s="5"/>
+      <c r="P47" s="27"/>
+      <c r="Q47" s="27"/>
+      <c r="R47" s="5"/>
+      <c r="S47" s="27"/>
+      <c r="T47" s="27"/>
+      <c r="U47" s="5"/>
+      <c r="V47" s="27"/>
+      <c r="W47" s="27"/>
+      <c r="X47" s="5"/>
+      <c r="Y47" s="27"/>
+      <c r="Z47" s="27"/>
+      <c r="AA47" s="5"/>
+      <c r="AB47" s="27"/>
+      <c r="AC47" s="27"/>
     </row>
     <row r="48" ht="16.5" spans="1:36">
-      <c r="A48" s="31" t="s">
+      <c r="A48" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B48" s="32">
+      <c r="B48" s="6">
         <v>520000</v>
       </c>
-      <c r="C48" s="33" t="s">
+      <c r="C48" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D48" s="32"/>
-      <c r="E48" s="32"/>
-      <c r="F48" s="34"/>
-      <c r="G48" s="35">
+      <c r="D48" s="6"/>
+      <c r="E48" s="6"/>
+      <c r="F48" s="5"/>
+      <c r="G48" s="27">
         <v>480000</v>
       </c>
-      <c r="H48" s="35">
-        <v>0</v>
-      </c>
-      <c r="I48" s="34"/>
-      <c r="J48" s="35">
+      <c r="H48" s="27">
+        <v>0</v>
+      </c>
+      <c r="I48" s="5"/>
+      <c r="J48" s="27">
         <v>510000</v>
       </c>
-      <c r="K48" s="35">
-        <v>0</v>
-      </c>
-      <c r="L48" s="34"/>
-      <c r="M48" s="35">
+      <c r="K48" s="27">
+        <v>0</v>
+      </c>
+      <c r="L48" s="5"/>
+      <c r="M48" s="27">
         <v>530000</v>
       </c>
-      <c r="N48" s="35">
-        <v>0</v>
-      </c>
-      <c r="O48" s="34"/>
-      <c r="P48" s="35">
+      <c r="N48" s="27">
+        <v>0</v>
+      </c>
+      <c r="O48" s="5"/>
+      <c r="P48" s="27">
         <v>520000</v>
       </c>
-      <c r="Q48" s="35">
+      <c r="Q48" s="27">
         <v>196166780</v>
       </c>
-      <c r="R48" s="34"/>
-      <c r="S48" s="35"/>
-      <c r="T48" s="35"/>
-      <c r="U48" s="34"/>
-      <c r="V48" s="35"/>
-      <c r="W48" s="35"/>
-      <c r="X48" s="34"/>
-      <c r="Y48" s="35"/>
-      <c r="Z48" s="35"/>
-      <c r="AA48" s="34"/>
-      <c r="AB48" s="35"/>
-      <c r="AC48" s="35"/>
+      <c r="R48" s="5"/>
+      <c r="S48" s="27"/>
+      <c r="T48" s="27"/>
+      <c r="U48" s="5"/>
+      <c r="V48" s="27"/>
+      <c r="W48" s="27"/>
+      <c r="X48" s="5"/>
+      <c r="Y48" s="27"/>
+      <c r="Z48" s="27"/>
+      <c r="AA48" s="5"/>
+      <c r="AB48" s="27"/>
+      <c r="AC48" s="27"/>
     </row>
     <row r="49" ht="16.5" spans="1:29">
-      <c r="A49" s="31" t="s">
+      <c r="A49" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="B49" s="32"/>
-      <c r="C49" s="36" t="s">
+      <c r="B49" s="6"/>
+      <c r="C49" s="31" t="s">
         <v>70</v>
       </c>
-      <c r="D49" s="32"/>
-      <c r="E49" s="32"/>
-      <c r="F49" s="34"/>
-      <c r="G49" s="35">
+      <c r="D49" s="6"/>
+      <c r="E49" s="6"/>
+      <c r="F49" s="5"/>
+      <c r="G49" s="27">
         <v>565000</v>
       </c>
-      <c r="H49" s="35">
-        <v>0</v>
-      </c>
-      <c r="I49" s="34"/>
-      <c r="J49" s="35">
+      <c r="H49" s="27">
+        <v>0</v>
+      </c>
+      <c r="I49" s="5"/>
+      <c r="J49" s="27">
         <v>585000</v>
       </c>
-      <c r="K49" s="37">
+      <c r="K49" s="28">
         <v>-88720000</v>
       </c>
-      <c r="L49" s="34"/>
-      <c r="M49" s="35"/>
-      <c r="N49" s="35"/>
-      <c r="O49" s="34"/>
-      <c r="P49" s="35"/>
-      <c r="Q49" s="35"/>
-      <c r="R49" s="34"/>
-      <c r="S49" s="35"/>
-      <c r="T49" s="35"/>
-      <c r="U49" s="34"/>
-      <c r="V49" s="35"/>
-      <c r="W49" s="35"/>
-      <c r="X49" s="34"/>
-      <c r="Y49" s="35"/>
-      <c r="Z49" s="35"/>
-      <c r="AA49" s="34"/>
-      <c r="AB49" s="35"/>
-      <c r="AC49" s="35"/>
+      <c r="L49" s="5"/>
+      <c r="M49" s="27"/>
+      <c r="N49" s="27"/>
+      <c r="O49" s="5"/>
+      <c r="P49" s="27"/>
+      <c r="Q49" s="27"/>
+      <c r="R49" s="5"/>
+      <c r="S49" s="27"/>
+      <c r="T49" s="27"/>
+      <c r="U49" s="5"/>
+      <c r="V49" s="27"/>
+      <c r="W49" s="27"/>
+      <c r="X49" s="5"/>
+      <c r="Y49" s="27"/>
+      <c r="Z49" s="27"/>
+      <c r="AA49" s="5"/>
+      <c r="AB49" s="27"/>
+      <c r="AC49" s="27"/>
     </row>
     <row r="50" ht="16.5" spans="1:29">
-      <c r="A50" s="31" t="s">
+      <c r="A50" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="B50" s="32"/>
-      <c r="C50" s="36" t="s">
+      <c r="B50" s="6"/>
+      <c r="C50" s="31" t="s">
         <v>70</v>
       </c>
-      <c r="D50" s="32"/>
-      <c r="E50" s="32"/>
-      <c r="F50" s="34"/>
-      <c r="G50" s="35">
+      <c r="D50" s="6"/>
+      <c r="E50" s="6"/>
+      <c r="F50" s="5"/>
+      <c r="G50" s="27">
         <v>440</v>
       </c>
-      <c r="H50" s="35">
-        <v>0</v>
-      </c>
-      <c r="I50" s="34"/>
-      <c r="J50" s="35">
+      <c r="H50" s="27">
+        <v>0</v>
+      </c>
+      <c r="I50" s="5"/>
+      <c r="J50" s="27">
         <v>-22952160</v>
       </c>
-      <c r="K50" s="35">
-        <v>0</v>
-      </c>
-      <c r="L50" s="34"/>
-      <c r="M50" s="35">
+      <c r="K50" s="27">
+        <v>0</v>
+      </c>
+      <c r="L50" s="5"/>
+      <c r="M50" s="27">
         <v>460</v>
       </c>
-      <c r="N50" s="35">
-        <v>0</v>
-      </c>
-      <c r="O50" s="34"/>
-      <c r="P50" s="35">
+      <c r="N50" s="27">
+        <v>0</v>
+      </c>
+      <c r="O50" s="5"/>
+      <c r="P50" s="27">
         <v>470000</v>
       </c>
-      <c r="Q50" s="37">
+      <c r="Q50" s="28">
         <v>-84390960</v>
       </c>
-      <c r="R50" s="34"/>
-      <c r="S50" s="35"/>
-      <c r="T50" s="35"/>
-      <c r="U50" s="34"/>
-      <c r="V50" s="35"/>
-      <c r="W50" s="35"/>
-      <c r="X50" s="34"/>
-      <c r="Y50" s="35"/>
-      <c r="Z50" s="35"/>
-      <c r="AA50" s="34"/>
-      <c r="AB50" s="35"/>
-      <c r="AC50" s="35"/>
+      <c r="R50" s="5"/>
+      <c r="S50" s="27"/>
+      <c r="T50" s="27"/>
+      <c r="U50" s="5"/>
+      <c r="V50" s="27"/>
+      <c r="W50" s="27"/>
+      <c r="X50" s="5"/>
+      <c r="Y50" s="27"/>
+      <c r="Z50" s="27"/>
+      <c r="AA50" s="5"/>
+      <c r="AB50" s="27"/>
+      <c r="AC50" s="27"/>
     </row>
     <row r="51" ht="16.5" spans="1:29">
-      <c r="A51" s="31" t="s">
+      <c r="A51" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="B51" s="32"/>
-      <c r="C51" s="36" t="s">
+      <c r="B51" s="6"/>
+      <c r="C51" s="31" t="s">
         <v>70</v>
       </c>
-      <c r="D51" s="32"/>
-      <c r="E51" s="32"/>
-      <c r="F51" s="34"/>
-      <c r="G51" s="35">
+      <c r="D51" s="6"/>
+      <c r="E51" s="6"/>
+      <c r="F51" s="5"/>
+      <c r="G51" s="27">
         <v>420000</v>
       </c>
-      <c r="H51" s="35">
-        <v>0</v>
-      </c>
-      <c r="I51" s="34"/>
-      <c r="J51" s="35">
+      <c r="H51" s="27">
+        <v>0</v>
+      </c>
+      <c r="I51" s="5"/>
+      <c r="J51" s="27">
         <v>460000</v>
       </c>
-      <c r="K51" s="37">
+      <c r="K51" s="28">
         <v>-428768000</v>
       </c>
-      <c r="L51" s="34"/>
-      <c r="M51" s="35"/>
-      <c r="N51" s="35"/>
-      <c r="O51" s="34"/>
-      <c r="P51" s="35"/>
-      <c r="Q51" s="35"/>
-      <c r="R51" s="34"/>
-      <c r="S51" s="35"/>
-      <c r="T51" s="35"/>
-      <c r="U51" s="34"/>
-      <c r="V51" s="35"/>
-      <c r="W51" s="35"/>
-      <c r="X51" s="34"/>
-      <c r="Y51" s="35"/>
-      <c r="Z51" s="35"/>
-      <c r="AA51" s="34"/>
-      <c r="AB51" s="35"/>
-      <c r="AC51" s="35"/>
+      <c r="L51" s="5"/>
+      <c r="M51" s="27"/>
+      <c r="N51" s="27"/>
+      <c r="O51" s="5"/>
+      <c r="P51" s="27"/>
+      <c r="Q51" s="27"/>
+      <c r="R51" s="5"/>
+      <c r="S51" s="27"/>
+      <c r="T51" s="27"/>
+      <c r="U51" s="5"/>
+      <c r="V51" s="27"/>
+      <c r="W51" s="27"/>
+      <c r="X51" s="5"/>
+      <c r="Y51" s="27"/>
+      <c r="Z51" s="27"/>
+      <c r="AA51" s="5"/>
+      <c r="AB51" s="27"/>
+      <c r="AC51" s="27"/>
     </row>
     <row r="52" ht="16.5" spans="1:29">
-      <c r="A52" s="31" t="s">
+      <c r="A52" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="B52" s="32"/>
-      <c r="C52" s="36" t="s">
+      <c r="B52" s="6"/>
+      <c r="C52" s="31" t="s">
         <v>70</v>
       </c>
-      <c r="D52" s="32"/>
-      <c r="E52" s="32"/>
-      <c r="F52" s="34"/>
-      <c r="G52" s="35">
+      <c r="D52" s="6"/>
+      <c r="E52" s="6"/>
+      <c r="F52" s="5"/>
+      <c r="G52" s="27">
         <v>495000</v>
       </c>
-      <c r="H52" s="35">
-        <v>0</v>
-      </c>
-      <c r="I52" s="34"/>
-      <c r="J52" s="35"/>
-      <c r="K52" s="35"/>
-      <c r="L52" s="34"/>
-      <c r="M52" s="35"/>
-      <c r="N52" s="35"/>
-      <c r="O52" s="34"/>
-      <c r="P52" s="35"/>
-      <c r="Q52" s="35"/>
-      <c r="R52" s="34"/>
-      <c r="S52" s="35"/>
-      <c r="T52" s="35"/>
-      <c r="U52" s="34"/>
-      <c r="V52" s="35"/>
-      <c r="W52" s="35"/>
-      <c r="X52" s="34"/>
-      <c r="Y52" s="35"/>
-      <c r="Z52" s="35"/>
-      <c r="AA52" s="34"/>
-      <c r="AB52" s="35"/>
-      <c r="AC52" s="35"/>
+      <c r="H52" s="27">
+        <v>0</v>
+      </c>
+      <c r="I52" s="5"/>
+      <c r="J52" s="27"/>
+      <c r="K52" s="27"/>
+      <c r="L52" s="5"/>
+      <c r="M52" s="27"/>
+      <c r="N52" s="27"/>
+      <c r="O52" s="5"/>
+      <c r="P52" s="27"/>
+      <c r="Q52" s="27"/>
+      <c r="R52" s="5"/>
+      <c r="S52" s="27"/>
+      <c r="T52" s="27"/>
+      <c r="U52" s="5"/>
+      <c r="V52" s="27"/>
+      <c r="W52" s="27"/>
+      <c r="X52" s="5"/>
+      <c r="Y52" s="27"/>
+      <c r="Z52" s="27"/>
+      <c r="AA52" s="5"/>
+      <c r="AB52" s="27"/>
+      <c r="AC52" s="27"/>
     </row>
     <row r="53" ht="16.5" spans="1:29">
-      <c r="A53" s="31" t="s">
+      <c r="A53" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="B53" s="32"/>
-      <c r="C53" s="36" t="s">
+      <c r="B53" s="6"/>
+      <c r="C53" s="31" t="s">
         <v>70</v>
       </c>
-      <c r="D53" s="32"/>
-      <c r="E53" s="32"/>
-      <c r="F53" s="34"/>
-      <c r="G53" s="35">
+      <c r="D53" s="6"/>
+      <c r="E53" s="6"/>
+      <c r="F53" s="5"/>
+      <c r="G53" s="27">
         <v>590</v>
       </c>
-      <c r="H53" s="37">
+      <c r="H53" s="28">
         <v>-7434000</v>
       </c>
-      <c r="I53" s="34"/>
-      <c r="J53" s="35"/>
-      <c r="K53" s="35"/>
-      <c r="L53" s="34"/>
-      <c r="M53" s="35"/>
-      <c r="N53" s="35"/>
-      <c r="O53" s="34"/>
-      <c r="P53" s="35"/>
-      <c r="Q53" s="35"/>
-      <c r="R53" s="34"/>
-      <c r="S53" s="35"/>
-      <c r="T53" s="35"/>
-      <c r="U53" s="34"/>
-      <c r="V53" s="35"/>
-      <c r="W53" s="35"/>
-      <c r="X53" s="34"/>
-      <c r="Y53" s="35"/>
-      <c r="Z53" s="35"/>
-      <c r="AA53" s="34"/>
-      <c r="AB53" s="35"/>
-      <c r="AC53" s="35"/>
+      <c r="I53" s="5"/>
+      <c r="J53" s="27"/>
+      <c r="K53" s="27"/>
+      <c r="L53" s="5"/>
+      <c r="M53" s="27"/>
+      <c r="N53" s="27"/>
+      <c r="O53" s="5"/>
+      <c r="P53" s="27"/>
+      <c r="Q53" s="27"/>
+      <c r="R53" s="5"/>
+      <c r="S53" s="27"/>
+      <c r="T53" s="27"/>
+      <c r="U53" s="5"/>
+      <c r="V53" s="27"/>
+      <c r="W53" s="27"/>
+      <c r="X53" s="5"/>
+      <c r="Y53" s="27"/>
+      <c r="Z53" s="27"/>
+      <c r="AA53" s="5"/>
+      <c r="AB53" s="27"/>
+      <c r="AC53" s="27"/>
     </row>
     <row r="54" ht="16.5" spans="1:29">
-      <c r="A54" s="31" t="s">
+      <c r="A54" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="B54" s="32">
+      <c r="B54" s="6">
         <v>530000</v>
       </c>
-      <c r="C54" s="33" t="s">
+      <c r="C54" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D54" s="32"/>
-      <c r="E54" s="32"/>
-      <c r="F54" s="34"/>
-      <c r="G54" s="35">
+      <c r="D54" s="6"/>
+      <c r="E54" s="6"/>
+      <c r="F54" s="5"/>
+      <c r="G54" s="27">
         <v>460000</v>
       </c>
-      <c r="H54" s="35">
-        <v>0</v>
-      </c>
-      <c r="I54" s="34"/>
-      <c r="J54" s="35">
+      <c r="H54" s="27">
+        <v>0</v>
+      </c>
+      <c r="I54" s="5"/>
+      <c r="J54" s="27">
         <v>520000</v>
       </c>
-      <c r="K54" s="35">
+      <c r="K54" s="27">
         <v>36005758</v>
       </c>
-      <c r="L54" s="34"/>
-      <c r="M54" s="35">
+      <c r="L54" s="5"/>
+      <c r="M54" s="27">
         <v>540000</v>
       </c>
-      <c r="N54" s="35">
+      <c r="N54" s="27">
         <v>50000000</v>
       </c>
-      <c r="O54" s="34"/>
-      <c r="P54" s="35"/>
-      <c r="Q54" s="35"/>
-      <c r="R54" s="34"/>
-      <c r="S54" s="35"/>
-      <c r="T54" s="35"/>
-      <c r="U54" s="34"/>
-      <c r="V54" s="35"/>
-      <c r="W54" s="35"/>
-      <c r="X54" s="34"/>
-      <c r="Y54" s="35"/>
-      <c r="Z54" s="35"/>
-      <c r="AA54" s="34"/>
-      <c r="AB54" s="35"/>
-      <c r="AC54" s="35"/>
+      <c r="O54" s="5"/>
+      <c r="P54" s="27"/>
+      <c r="Q54" s="27"/>
+      <c r="R54" s="5"/>
+      <c r="S54" s="27"/>
+      <c r="T54" s="27"/>
+      <c r="U54" s="5"/>
+      <c r="V54" s="27"/>
+      <c r="W54" s="27"/>
+      <c r="X54" s="5"/>
+      <c r="Y54" s="27"/>
+      <c r="Z54" s="27"/>
+      <c r="AA54" s="5"/>
+      <c r="AB54" s="27"/>
+      <c r="AC54" s="27"/>
     </row>
     <row r="55" ht="16.5" spans="1:29">
-      <c r="A55" s="31" t="s">
+      <c r="A55" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B55" s="32">
+      <c r="B55" s="6">
         <v>510000</v>
       </c>
-      <c r="C55" s="33" t="s">
+      <c r="C55" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D55" s="32"/>
-      <c r="E55" s="32"/>
-      <c r="F55" s="34"/>
-      <c r="G55" s="35">
+      <c r="D55" s="6"/>
+      <c r="E55" s="6"/>
+      <c r="F55" s="5"/>
+      <c r="G55" s="27">
         <v>450000</v>
       </c>
-      <c r="H55" s="35">
-        <v>0</v>
-      </c>
-      <c r="I55" s="34"/>
-      <c r="J55" s="35">
+      <c r="H55" s="27">
+        <v>0</v>
+      </c>
+      <c r="I55" s="5"/>
+      <c r="J55" s="27">
         <v>470000</v>
       </c>
-      <c r="K55" s="35">
-        <v>0</v>
-      </c>
-      <c r="L55" s="34"/>
-      <c r="M55" s="35">
+      <c r="K55" s="27">
+        <v>0</v>
+      </c>
+      <c r="L55" s="5"/>
+      <c r="M55" s="27">
         <v>480000</v>
       </c>
-      <c r="N55" s="35">
-        <v>0</v>
-      </c>
-      <c r="O55" s="34"/>
-      <c r="P55" s="35">
+      <c r="N55" s="27">
+        <v>0</v>
+      </c>
+      <c r="O55" s="5"/>
+      <c r="P55" s="27">
         <v>490000</v>
       </c>
-      <c r="Q55" s="35">
-        <v>0</v>
-      </c>
-      <c r="R55" s="34"/>
-      <c r="S55" s="35">
+      <c r="Q55" s="27">
+        <v>0</v>
+      </c>
+      <c r="R55" s="5"/>
+      <c r="S55" s="27">
         <v>500000</v>
       </c>
-      <c r="T55" s="35">
-        <v>0</v>
-      </c>
-      <c r="U55" s="34"/>
-      <c r="V55" s="35">
+      <c r="T55" s="27">
+        <v>0</v>
+      </c>
+      <c r="U55" s="5"/>
+      <c r="V55" s="27">
         <v>520000</v>
       </c>
-      <c r="W55" s="35">
+      <c r="W55" s="27">
         <v>101780710</v>
       </c>
-      <c r="X55" s="34"/>
-      <c r="Y55" s="35"/>
-      <c r="Z55" s="35"/>
-      <c r="AA55" s="34"/>
-      <c r="AB55" s="35"/>
-      <c r="AC55" s="35"/>
+      <c r="X55" s="5"/>
+      <c r="Y55" s="27"/>
+      <c r="Z55" s="27"/>
+      <c r="AA55" s="5"/>
+      <c r="AB55" s="27"/>
+      <c r="AC55" s="27"/>
     </row>
     <row r="56" ht="16.5" spans="1:29">
-      <c r="A56" s="31" t="s">
+      <c r="A56" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="B56" s="32"/>
-      <c r="C56" s="36" t="s">
+      <c r="B56" s="6"/>
+      <c r="C56" s="31" t="s">
         <v>70</v>
       </c>
-      <c r="D56" s="32"/>
-      <c r="E56" s="32"/>
-      <c r="F56" s="34"/>
-      <c r="G56" s="35">
+      <c r="D56" s="6"/>
+      <c r="E56" s="6"/>
+      <c r="F56" s="5"/>
+      <c r="G56" s="27">
         <v>540</v>
       </c>
-      <c r="H56" s="35">
-        <v>0</v>
-      </c>
-      <c r="I56" s="34"/>
-      <c r="J56" s="35"/>
-      <c r="K56" s="35"/>
-      <c r="L56" s="34"/>
-      <c r="M56" s="35"/>
-      <c r="N56" s="35"/>
-      <c r="O56" s="34"/>
-      <c r="P56" s="35"/>
-      <c r="Q56" s="35"/>
-      <c r="R56" s="34"/>
-      <c r="S56" s="35"/>
-      <c r="T56" s="35"/>
-      <c r="U56" s="34"/>
-      <c r="V56" s="35"/>
-      <c r="W56" s="35"/>
-      <c r="X56" s="34"/>
-      <c r="Y56" s="35"/>
-      <c r="Z56" s="35"/>
-      <c r="AA56" s="34"/>
-      <c r="AB56" s="35"/>
-      <c r="AC56" s="35"/>
+      <c r="H56" s="27">
+        <v>0</v>
+      </c>
+      <c r="I56" s="5"/>
+      <c r="J56" s="27"/>
+      <c r="K56" s="27"/>
+      <c r="L56" s="5"/>
+      <c r="M56" s="27"/>
+      <c r="N56" s="27"/>
+      <c r="O56" s="5"/>
+      <c r="P56" s="27"/>
+      <c r="Q56" s="27"/>
+      <c r="R56" s="5"/>
+      <c r="S56" s="27"/>
+      <c r="T56" s="27"/>
+      <c r="U56" s="5"/>
+      <c r="V56" s="27"/>
+      <c r="W56" s="27"/>
+      <c r="X56" s="5"/>
+      <c r="Y56" s="27"/>
+      <c r="Z56" s="27"/>
+      <c r="AA56" s="5"/>
+      <c r="AB56" s="27"/>
+      <c r="AC56" s="27"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5643,8 +5613,8 @@
       <c r="B2" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="C2" s="8">
-        <v>430</v>
+      <c r="C2" s="8" t="s">
+        <v>133</v>
       </c>
       <c r="D2" s="8">
         <v>450</v>
@@ -5653,7 +5623,7 @@
         <v>470</v>
       </c>
       <c r="F2" s="8">
-        <f>E2+20</f>
+        <f t="shared" ref="F2:F10" si="0">E2+20</f>
         <v>490</v>
       </c>
       <c r="G2" s="8">
@@ -5664,11 +5634,11 @@
         <v>470</v>
       </c>
       <c r="I2" s="8">
-        <f>H2-10</f>
+        <f t="shared" ref="I2:I10" si="1">H2-10</f>
         <v>460</v>
       </c>
       <c r="J2" s="8">
-        <f>I2-10</f>
+        <f t="shared" ref="J2:J10" si="2">I2-10</f>
         <v>450</v>
       </c>
       <c r="K2" s="8">
@@ -5702,8 +5672,8 @@
       <c r="B3" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="C3" s="8">
-        <v>430</v>
+      <c r="C3" s="8" t="s">
+        <v>134</v>
       </c>
       <c r="D3" s="8">
         <v>450</v>
@@ -5712,7 +5682,7 @@
         <v>470</v>
       </c>
       <c r="F3" s="8">
-        <f>E3+20</f>
+        <f t="shared" si="0"/>
         <v>490</v>
       </c>
       <c r="G3" s="8">
@@ -5723,11 +5693,11 @@
         <v>470</v>
       </c>
       <c r="I3" s="8">
-        <f>H3-10</f>
+        <f t="shared" si="1"/>
         <v>460</v>
       </c>
       <c r="J3" s="8">
-        <f>I3-10</f>
+        <f t="shared" si="2"/>
         <v>450</v>
       </c>
       <c r="K3" s="8">
@@ -5761,8 +5731,8 @@
       <c r="B4" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="C4" s="8">
-        <v>420</v>
+      <c r="C4" s="8" t="s">
+        <v>62</v>
       </c>
       <c r="D4" s="8">
         <v>440</v>
@@ -5771,7 +5741,7 @@
         <v>460</v>
       </c>
       <c r="F4" s="8">
-        <f>E4+20</f>
+        <f t="shared" si="0"/>
         <v>480</v>
       </c>
       <c r="G4" s="8">
@@ -5782,11 +5752,11 @@
         <v>460</v>
       </c>
       <c r="I4" s="8">
-        <f>H4-10</f>
+        <f t="shared" si="1"/>
         <v>450</v>
       </c>
       <c r="J4" s="8">
-        <f>I4-10</f>
+        <f t="shared" si="2"/>
         <v>440</v>
       </c>
       <c r="K4" s="8">
@@ -5821,8 +5791,8 @@
       <c r="B5" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="C5" s="8">
-        <v>420</v>
+      <c r="C5" s="8" t="s">
+        <v>135</v>
       </c>
       <c r="D5" s="8">
         <v>440</v>
@@ -5831,7 +5801,7 @@
         <v>460</v>
       </c>
       <c r="F5" s="8">
-        <f>E5+20</f>
+        <f t="shared" si="0"/>
         <v>480</v>
       </c>
       <c r="G5" s="11">
@@ -5841,11 +5811,11 @@
         <v>460</v>
       </c>
       <c r="I5" s="8">
-        <f>H5-10</f>
+        <f t="shared" si="1"/>
         <v>450</v>
       </c>
       <c r="J5" s="8">
-        <f>I5-10</f>
+        <f t="shared" si="2"/>
         <v>440</v>
       </c>
       <c r="Q5" s="8" t="s">
@@ -5857,8 +5827,8 @@
       <c r="B6" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="C6" s="8">
-        <v>435</v>
+      <c r="C6" s="8" t="s">
+        <v>136</v>
       </c>
       <c r="D6" s="8">
         <v>455</v>
@@ -5867,7 +5837,7 @@
         <v>475</v>
       </c>
       <c r="F6" s="8">
-        <f>E6+20</f>
+        <f t="shared" si="0"/>
         <v>495</v>
       </c>
       <c r="G6" s="8">
@@ -5878,33 +5848,33 @@
         <v>475</v>
       </c>
       <c r="I6" s="8">
-        <f>H6-10</f>
+        <f t="shared" si="1"/>
         <v>465</v>
       </c>
       <c r="J6" s="8">
-        <f>I6-10</f>
+        <f t="shared" si="2"/>
         <v>455</v>
       </c>
       <c r="K6" s="8">
         <v>465</v>
       </c>
       <c r="L6" s="8">
-        <f>K6+20</f>
+        <f t="shared" ref="L6:L22" si="3">K6+20</f>
         <v>485</v>
       </c>
       <c r="M6" s="8">
-        <f>L6+10</f>
+        <f t="shared" ref="M6:M22" si="4">L6+10</f>
         <v>495</v>
       </c>
       <c r="N6" s="8">
-        <f>M6+20</f>
+        <f t="shared" ref="N6:N17" si="5">M6+20</f>
         <v>515</v>
       </c>
       <c r="O6" s="8">
         <v>535</v>
       </c>
       <c r="P6" s="8">
-        <f>O6-10</f>
+        <f t="shared" ref="P6:P29" si="6">O6-10</f>
         <v>525</v>
       </c>
       <c r="Q6" s="8" t="s">
@@ -5915,8 +5885,8 @@
       <c r="B7" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="C7" s="8">
-        <v>420</v>
+      <c r="C7" s="8" t="s">
+        <v>61</v>
       </c>
       <c r="D7" s="8">
         <v>440</v>
@@ -5925,7 +5895,7 @@
         <v>460</v>
       </c>
       <c r="F7" s="8">
-        <f>E7+20</f>
+        <f t="shared" si="0"/>
         <v>480</v>
       </c>
       <c r="G7" s="8">
@@ -5936,33 +5906,33 @@
         <v>460</v>
       </c>
       <c r="I7" s="8">
-        <f>H7-10</f>
+        <f t="shared" si="1"/>
         <v>450</v>
       </c>
       <c r="J7" s="8">
-        <f>I7-10</f>
+        <f t="shared" si="2"/>
         <v>440</v>
       </c>
       <c r="K7" s="8">
         <v>450</v>
       </c>
       <c r="L7" s="8">
-        <f>K7+20</f>
+        <f t="shared" si="3"/>
         <v>470</v>
       </c>
       <c r="M7" s="8">
-        <f>L7+10</f>
+        <f t="shared" si="4"/>
         <v>480</v>
       </c>
       <c r="N7" s="8">
-        <f>M7+20</f>
+        <f t="shared" si="5"/>
         <v>500</v>
       </c>
       <c r="O7" s="8">
         <v>520</v>
       </c>
       <c r="P7" s="8">
-        <f>O7-10</f>
+        <f t="shared" si="6"/>
         <v>510</v>
       </c>
       <c r="Q7" s="8" t="s">
@@ -5973,8 +5943,8 @@
       <c r="B8" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="C8" s="8">
-        <v>435</v>
+      <c r="C8" s="8" t="s">
+        <v>60</v>
       </c>
       <c r="D8" s="8">
         <v>455</v>
@@ -5983,7 +5953,7 @@
         <v>475</v>
       </c>
       <c r="F8" s="8">
-        <f>E8+20</f>
+        <f t="shared" si="0"/>
         <v>495</v>
       </c>
       <c r="G8" s="8">
@@ -5994,33 +5964,33 @@
         <v>480</v>
       </c>
       <c r="I8" s="8">
-        <f>H8-10</f>
+        <f t="shared" si="1"/>
         <v>470</v>
       </c>
       <c r="J8" s="8">
-        <f>I8-10</f>
+        <f t="shared" si="2"/>
         <v>460</v>
       </c>
       <c r="K8" s="8">
         <v>470</v>
       </c>
       <c r="L8" s="8">
-        <f>K8+20</f>
+        <f t="shared" si="3"/>
         <v>490</v>
       </c>
       <c r="M8" s="8">
-        <f>L8+10</f>
+        <f t="shared" si="4"/>
         <v>500</v>
       </c>
       <c r="N8" s="8">
-        <f>M8+20</f>
+        <f t="shared" si="5"/>
         <v>520</v>
       </c>
       <c r="O8" s="8">
         <v>540</v>
       </c>
       <c r="P8" s="8">
-        <f>O8-10</f>
+        <f t="shared" si="6"/>
         <v>530</v>
       </c>
       <c r="Q8" s="8" t="s">
@@ -6031,8 +6001,8 @@
       <c r="B9" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="C9" s="8">
-        <v>430</v>
+      <c r="C9" s="8" t="s">
+        <v>73</v>
       </c>
       <c r="D9" s="8">
         <v>450</v>
@@ -6041,7 +6011,7 @@
         <v>470</v>
       </c>
       <c r="F9" s="8">
-        <f>E9+20</f>
+        <f t="shared" si="0"/>
         <v>490</v>
       </c>
       <c r="G9" s="8">
@@ -6052,33 +6022,33 @@
         <v>470</v>
       </c>
       <c r="I9" s="8">
-        <f>H9-10</f>
+        <f t="shared" si="1"/>
         <v>460</v>
       </c>
       <c r="J9" s="8">
-        <f>I9-10</f>
+        <f t="shared" si="2"/>
         <v>450</v>
       </c>
       <c r="K9" s="8">
         <v>460</v>
       </c>
       <c r="L9" s="8">
-        <f>K9+20</f>
+        <f t="shared" si="3"/>
         <v>480</v>
       </c>
       <c r="M9" s="8">
-        <f>L9+10</f>
+        <f t="shared" si="4"/>
         <v>490</v>
       </c>
       <c r="N9" s="8">
-        <f>M9+20</f>
+        <f t="shared" si="5"/>
         <v>510</v>
       </c>
       <c r="O9" s="8">
         <v>530</v>
       </c>
       <c r="P9" s="8">
-        <f>O9-10</f>
+        <f t="shared" si="6"/>
         <v>520</v>
       </c>
       <c r="Q9" s="8" t="s">
@@ -6089,8 +6059,8 @@
       <c r="B10" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="C10" s="8">
-        <v>420</v>
+      <c r="C10" s="8" t="s">
+        <v>59</v>
       </c>
       <c r="D10" s="8">
         <v>440</v>
@@ -6099,7 +6069,7 @@
         <v>460</v>
       </c>
       <c r="F10" s="8">
-        <f>E10+20</f>
+        <f t="shared" si="0"/>
         <v>480</v>
       </c>
       <c r="G10" s="8">
@@ -6110,33 +6080,33 @@
         <v>460</v>
       </c>
       <c r="I10" s="8">
-        <f>H10-10</f>
+        <f t="shared" si="1"/>
         <v>450</v>
       </c>
       <c r="J10" s="8">
-        <f>I10-10</f>
+        <f t="shared" si="2"/>
         <v>440</v>
       </c>
       <c r="K10" s="8">
         <v>450</v>
       </c>
       <c r="L10" s="8">
-        <f>K10+20</f>
+        <f t="shared" si="3"/>
         <v>470</v>
       </c>
       <c r="M10" s="8">
-        <f>L10+10</f>
+        <f t="shared" si="4"/>
         <v>480</v>
       </c>
       <c r="N10" s="8">
-        <f>M10+20</f>
+        <f t="shared" si="5"/>
         <v>500</v>
       </c>
       <c r="O10" s="8">
         <v>520</v>
       </c>
       <c r="P10" s="8">
-        <f>O10-10</f>
+        <f t="shared" si="6"/>
         <v>510</v>
       </c>
       <c r="Q10" s="8" t="s">
@@ -6147,6 +6117,9 @@
       <c r="B11" s="7" t="s">
         <v>57</v>
       </c>
+      <c r="C11" s="8" t="s">
+        <v>96</v>
+      </c>
       <c r="G11" s="11">
         <v>480</v>
       </c>
@@ -6163,22 +6136,22 @@
         <v>450</v>
       </c>
       <c r="L11" s="8">
-        <f>K11+20</f>
+        <f t="shared" si="3"/>
         <v>470</v>
       </c>
       <c r="M11" s="8">
-        <f>L11+10</f>
+        <f t="shared" si="4"/>
         <v>480</v>
       </c>
       <c r="N11" s="8">
-        <f>M11+20</f>
+        <f t="shared" si="5"/>
         <v>500</v>
       </c>
       <c r="O11" s="8">
         <v>520</v>
       </c>
       <c r="P11" s="8">
-        <f>O11-10</f>
+        <f t="shared" si="6"/>
         <v>510</v>
       </c>
       <c r="Q11" s="8" t="s">
@@ -6189,8 +6162,8 @@
       <c r="B12" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="C12" s="8">
-        <v>440</v>
+      <c r="C12" s="8" t="s">
+        <v>56</v>
       </c>
       <c r="D12" s="8">
         <v>460</v>
@@ -6199,44 +6172,44 @@
         <v>480</v>
       </c>
       <c r="F12" s="8">
-        <f>E12+20</f>
+        <f t="shared" ref="F12:F33" si="7">E12+20</f>
         <v>500</v>
       </c>
       <c r="G12" s="8">
-        <f>F12+20</f>
+        <f t="shared" ref="G12:G22" si="8">F12+20</f>
         <v>520</v>
       </c>
       <c r="H12" s="8">
         <v>480</v>
       </c>
       <c r="I12" s="8">
-        <f>H12-10</f>
+        <f t="shared" ref="I12:I33" si="9">H12-10</f>
         <v>470</v>
       </c>
       <c r="J12" s="8">
-        <f>I12-10</f>
+        <f t="shared" ref="J12:J23" si="10">I12-10</f>
         <v>460</v>
       </c>
       <c r="K12" s="8">
         <v>470</v>
       </c>
       <c r="L12" s="8">
-        <f>K12+20</f>
+        <f t="shared" si="3"/>
         <v>490</v>
       </c>
       <c r="M12" s="8">
-        <f>L12+10</f>
+        <f t="shared" si="4"/>
         <v>500</v>
       </c>
       <c r="N12" s="8">
-        <f>M12+20</f>
+        <f t="shared" si="5"/>
         <v>520</v>
       </c>
       <c r="O12" s="8">
         <v>540</v>
       </c>
       <c r="P12" s="8">
-        <f>O12-10</f>
+        <f t="shared" si="6"/>
         <v>530</v>
       </c>
       <c r="Q12" s="8" t="s">
@@ -6247,8 +6220,8 @@
       <c r="B13" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="C13" s="8">
-        <v>425</v>
+      <c r="C13" s="8" t="s">
+        <v>137</v>
       </c>
       <c r="D13" s="8">
         <v>445</v>
@@ -6257,44 +6230,44 @@
         <v>465</v>
       </c>
       <c r="F13" s="8">
-        <f>E13+20</f>
+        <f t="shared" si="7"/>
         <v>485</v>
       </c>
       <c r="G13" s="8">
-        <f>F13+20</f>
+        <f t="shared" si="8"/>
         <v>505</v>
       </c>
       <c r="H13" s="8">
         <v>465</v>
       </c>
       <c r="I13" s="8">
-        <f>H13-10</f>
+        <f t="shared" si="9"/>
         <v>455</v>
       </c>
       <c r="J13" s="8">
-        <f>I13-10</f>
+        <f t="shared" si="10"/>
         <v>445</v>
       </c>
       <c r="K13" s="8">
         <v>455</v>
       </c>
       <c r="L13" s="8">
-        <f>K13+20</f>
+        <f t="shared" si="3"/>
         <v>475</v>
       </c>
       <c r="M13" s="8">
-        <f>L13+10</f>
+        <f t="shared" si="4"/>
         <v>485</v>
       </c>
       <c r="N13" s="8">
-        <f>M13+20</f>
+        <f t="shared" si="5"/>
         <v>505</v>
       </c>
       <c r="O13" s="8">
         <v>525</v>
       </c>
       <c r="P13" s="8">
-        <f>O13-10</f>
+        <f t="shared" si="6"/>
         <v>515</v>
       </c>
       <c r="Q13" s="8" t="s">
@@ -6305,8 +6278,8 @@
       <c r="B14" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="C14" s="8">
-        <v>435</v>
+      <c r="C14" s="8" t="s">
+        <v>138</v>
       </c>
       <c r="D14" s="8">
         <v>455</v>
@@ -6315,44 +6288,44 @@
         <v>475</v>
       </c>
       <c r="F14" s="8">
-        <f>E14+20</f>
+        <f t="shared" si="7"/>
         <v>495</v>
       </c>
       <c r="G14" s="8">
-        <f>F14+20</f>
+        <f t="shared" si="8"/>
         <v>515</v>
       </c>
       <c r="H14" s="8">
         <v>475</v>
       </c>
       <c r="I14" s="8">
-        <f>H14-10</f>
+        <f t="shared" si="9"/>
         <v>465</v>
       </c>
       <c r="J14" s="8">
-        <f>I14-10</f>
+        <f t="shared" si="10"/>
         <v>455</v>
       </c>
       <c r="K14" s="8">
         <v>465</v>
       </c>
       <c r="L14" s="8">
-        <f>K14+20</f>
+        <f t="shared" si="3"/>
         <v>485</v>
       </c>
       <c r="M14" s="8">
-        <f>L14+10</f>
+        <f t="shared" si="4"/>
         <v>495</v>
       </c>
       <c r="N14" s="8">
-        <f>M14+20</f>
+        <f t="shared" si="5"/>
         <v>515</v>
       </c>
       <c r="O14" s="8">
         <v>535</v>
       </c>
       <c r="P14" s="8">
-        <f>O14-10</f>
+        <f t="shared" si="6"/>
         <v>525</v>
       </c>
       <c r="Q14" s="8" t="s">
@@ -6363,8 +6336,8 @@
       <c r="B15" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="C15" s="8">
-        <v>420</v>
+      <c r="C15" s="8" t="s">
+        <v>139</v>
       </c>
       <c r="D15" s="8">
         <v>440</v>
@@ -6373,44 +6346,44 @@
         <v>460</v>
       </c>
       <c r="F15" s="8">
-        <f>E15+20</f>
+        <f t="shared" si="7"/>
         <v>480</v>
       </c>
       <c r="G15" s="8">
-        <f>F15+20</f>
+        <f t="shared" si="8"/>
         <v>500</v>
       </c>
       <c r="H15" s="8">
         <v>460</v>
       </c>
       <c r="I15" s="8">
-        <f>H15-10</f>
+        <f t="shared" si="9"/>
         <v>450</v>
       </c>
       <c r="J15" s="8">
-        <f>I15-10</f>
+        <f t="shared" si="10"/>
         <v>440</v>
       </c>
       <c r="K15" s="8">
         <v>450</v>
       </c>
       <c r="L15" s="8">
-        <f>K15+20</f>
+        <f t="shared" si="3"/>
         <v>470</v>
       </c>
       <c r="M15" s="8">
-        <f>L15+10</f>
+        <f t="shared" si="4"/>
         <v>480</v>
       </c>
       <c r="N15" s="8">
-        <f>M15+20</f>
+        <f t="shared" si="5"/>
         <v>500</v>
       </c>
       <c r="O15" s="8">
         <v>520</v>
       </c>
       <c r="P15" s="8">
-        <f>O15-10</f>
+        <f t="shared" si="6"/>
         <v>510</v>
       </c>
       <c r="Q15" s="8" t="s">
@@ -6421,8 +6394,8 @@
       <c r="B16" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="C16" s="8">
-        <v>430</v>
+      <c r="C16" s="8" t="s">
+        <v>55</v>
       </c>
       <c r="D16" s="8">
         <v>450</v>
@@ -6431,44 +6404,44 @@
         <v>470</v>
       </c>
       <c r="F16" s="8">
-        <f>E16+20</f>
+        <f t="shared" si="7"/>
         <v>490</v>
       </c>
       <c r="G16" s="8">
-        <f>F16+20</f>
+        <f t="shared" si="8"/>
         <v>510</v>
       </c>
       <c r="H16" s="8">
         <v>470</v>
       </c>
       <c r="I16" s="8">
-        <f>H16-10</f>
+        <f t="shared" si="9"/>
         <v>460</v>
       </c>
       <c r="J16" s="8">
-        <f>I16-10</f>
+        <f t="shared" si="10"/>
         <v>450</v>
       </c>
       <c r="K16" s="8">
         <v>460</v>
       </c>
       <c r="L16" s="8">
-        <f>K16+20</f>
+        <f t="shared" si="3"/>
         <v>480</v>
       </c>
       <c r="M16" s="8">
-        <f>L16+10</f>
+        <f t="shared" si="4"/>
         <v>490</v>
       </c>
       <c r="N16" s="8">
-        <f>M16+20</f>
+        <f t="shared" si="5"/>
         <v>510</v>
       </c>
       <c r="O16" s="8">
         <v>530</v>
       </c>
       <c r="P16" s="8">
-        <f>O16-10</f>
+        <f t="shared" si="6"/>
         <v>520</v>
       </c>
       <c r="Q16" s="8" t="s">
@@ -6479,8 +6452,8 @@
       <c r="B17" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="C17" s="8">
-        <v>410</v>
+      <c r="C17" s="8" t="s">
+        <v>54</v>
       </c>
       <c r="D17" s="8">
         <v>430</v>
@@ -6489,44 +6462,44 @@
         <v>450</v>
       </c>
       <c r="F17" s="8">
-        <f>E17+20</f>
+        <f t="shared" si="7"/>
         <v>470</v>
       </c>
       <c r="G17" s="8">
-        <f>F17+20</f>
+        <f t="shared" si="8"/>
         <v>490</v>
       </c>
       <c r="H17" s="8">
         <v>450</v>
       </c>
       <c r="I17" s="8">
-        <f>H17-10</f>
+        <f t="shared" si="9"/>
         <v>440</v>
       </c>
       <c r="J17" s="8">
-        <f>I17-10</f>
+        <f t="shared" si="10"/>
         <v>430</v>
       </c>
       <c r="K17" s="14">
         <v>440</v>
       </c>
       <c r="L17" s="14">
-        <f>K17+20</f>
+        <f t="shared" si="3"/>
         <v>460</v>
       </c>
       <c r="M17" s="8">
-        <f>L17+10</f>
+        <f t="shared" si="4"/>
         <v>470</v>
       </c>
       <c r="N17" s="8">
-        <f>M17+20</f>
+        <f t="shared" si="5"/>
         <v>490</v>
       </c>
       <c r="O17" s="8">
         <v>510</v>
       </c>
       <c r="P17" s="8">
-        <f>O17-10</f>
+        <f t="shared" si="6"/>
         <v>500</v>
       </c>
       <c r="Q17" s="15" t="s">
@@ -6539,8 +6512,8 @@
       <c r="B18" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="C18" s="8">
-        <v>435</v>
+      <c r="C18" s="8" t="s">
+        <v>140</v>
       </c>
       <c r="D18" s="8">
         <v>455</v>
@@ -6549,33 +6522,33 @@
         <v>475</v>
       </c>
       <c r="F18" s="8">
-        <f>E18+20</f>
+        <f t="shared" si="7"/>
         <v>495</v>
       </c>
       <c r="G18" s="8">
-        <f>F18+20</f>
+        <f t="shared" si="8"/>
         <v>515</v>
       </c>
       <c r="H18" s="8">
         <v>475</v>
       </c>
       <c r="I18" s="8">
-        <f>H18-10</f>
+        <f t="shared" si="9"/>
         <v>465</v>
       </c>
       <c r="J18" s="8">
-        <f>I18-10</f>
+        <f t="shared" si="10"/>
         <v>455</v>
       </c>
       <c r="K18" s="8">
         <v>470</v>
       </c>
       <c r="L18" s="8">
-        <f>K18+20</f>
+        <f t="shared" si="3"/>
         <v>490</v>
       </c>
       <c r="M18" s="8">
-        <f>L18+10</f>
+        <f t="shared" si="4"/>
         <v>500</v>
       </c>
       <c r="N18" s="8">
@@ -6585,7 +6558,7 @@
         <v>535</v>
       </c>
       <c r="P18" s="8">
-        <f>O18-10</f>
+        <f t="shared" si="6"/>
         <v>525</v>
       </c>
       <c r="Q18" s="8" t="s">
@@ -6598,8 +6571,8 @@
       <c r="B19" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="C19" s="8">
-        <v>440</v>
+      <c r="C19" s="8" t="s">
+        <v>72</v>
       </c>
       <c r="D19" s="8">
         <v>460</v>
@@ -6608,33 +6581,33 @@
         <v>480</v>
       </c>
       <c r="F19" s="8">
-        <f>E19+20</f>
+        <f t="shared" si="7"/>
         <v>500</v>
       </c>
       <c r="G19" s="8">
-        <f>F19+20</f>
+        <f t="shared" si="8"/>
         <v>520</v>
       </c>
       <c r="H19" s="8">
         <v>490</v>
       </c>
       <c r="I19" s="8">
-        <f>H19-10</f>
+        <f t="shared" si="9"/>
         <v>480</v>
       </c>
       <c r="J19" s="8">
-        <f>I19-10</f>
+        <f t="shared" si="10"/>
         <v>470</v>
       </c>
       <c r="K19" s="8">
         <v>480</v>
       </c>
       <c r="L19" s="8">
-        <f>K19+20</f>
+        <f t="shared" si="3"/>
         <v>500</v>
       </c>
       <c r="M19" s="8">
-        <f>L19+10</f>
+        <f t="shared" si="4"/>
         <v>510</v>
       </c>
       <c r="N19" s="8">
@@ -6645,7 +6618,7 @@
         <v>540</v>
       </c>
       <c r="P19" s="8">
-        <f>O19-10</f>
+        <f t="shared" si="6"/>
         <v>530</v>
       </c>
       <c r="Q19" s="8" t="s">
@@ -6658,8 +6631,8 @@
       <c r="B20" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="C20" s="8">
-        <v>430</v>
+      <c r="C20" s="8" t="s">
+        <v>53</v>
       </c>
       <c r="D20" s="8">
         <v>450</v>
@@ -6668,33 +6641,33 @@
         <v>470</v>
       </c>
       <c r="F20" s="8">
-        <f>E20+20</f>
+        <f t="shared" si="7"/>
         <v>490</v>
       </c>
       <c r="G20" s="8">
-        <f>F20+20</f>
+        <f t="shared" si="8"/>
         <v>510</v>
       </c>
       <c r="H20" s="8">
         <v>475</v>
       </c>
       <c r="I20" s="8">
-        <f>H20-10</f>
+        <f t="shared" si="9"/>
         <v>465</v>
       </c>
       <c r="J20" s="8">
-        <f>I20-10</f>
+        <f t="shared" si="10"/>
         <v>455</v>
       </c>
       <c r="K20" s="8">
         <v>465</v>
       </c>
       <c r="L20" s="8">
-        <f>K20+20</f>
+        <f t="shared" si="3"/>
         <v>485</v>
       </c>
       <c r="M20" s="8">
-        <f>L20+10</f>
+        <f t="shared" si="4"/>
         <v>495</v>
       </c>
       <c r="N20" s="8">
@@ -6705,7 +6678,7 @@
         <v>535</v>
       </c>
       <c r="P20" s="8">
-        <f>O20-10</f>
+        <f t="shared" si="6"/>
         <v>525</v>
       </c>
       <c r="Q20" s="8" t="s">
@@ -6718,8 +6691,8 @@
       <c r="B21" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="C21" s="8">
-        <v>430</v>
+      <c r="C21" s="8" t="s">
+        <v>141</v>
       </c>
       <c r="D21" s="8">
         <v>450</v>
@@ -6728,33 +6701,33 @@
         <v>470</v>
       </c>
       <c r="F21" s="8">
-        <f>E21+20</f>
+        <f t="shared" si="7"/>
         <v>490</v>
       </c>
       <c r="G21" s="8">
-        <f>F21+20</f>
+        <f t="shared" si="8"/>
         <v>510</v>
       </c>
       <c r="H21" s="8">
         <v>485</v>
       </c>
       <c r="I21" s="8">
-        <f>H21-10</f>
+        <f t="shared" si="9"/>
         <v>475</v>
       </c>
       <c r="J21" s="8">
-        <f>I21-10</f>
+        <f t="shared" si="10"/>
         <v>465</v>
       </c>
       <c r="K21" s="8">
         <v>475</v>
       </c>
       <c r="L21" s="8">
-        <f>K21+20</f>
+        <f t="shared" si="3"/>
         <v>495</v>
       </c>
       <c r="M21" s="8">
-        <f>L21+10</f>
+        <f t="shared" si="4"/>
         <v>505</v>
       </c>
       <c r="N21" s="8">
@@ -6765,7 +6738,7 @@
         <v>545</v>
       </c>
       <c r="P21" s="8">
-        <f>O21-10</f>
+        <f t="shared" si="6"/>
         <v>535</v>
       </c>
       <c r="Q21" s="8" t="s">
@@ -6778,8 +6751,8 @@
       <c r="B22" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="C22" s="8">
-        <v>160</v>
+      <c r="C22" s="8" t="s">
+        <v>142</v>
       </c>
       <c r="D22" s="8">
         <v>160</v>
@@ -6788,33 +6761,33 @@
         <v>460</v>
       </c>
       <c r="F22" s="8">
-        <f>E22+20</f>
+        <f t="shared" si="7"/>
         <v>480</v>
       </c>
       <c r="G22" s="8">
-        <f>F22+20</f>
+        <f t="shared" si="8"/>
         <v>500</v>
       </c>
       <c r="H22" s="8">
         <v>490</v>
       </c>
       <c r="I22" s="8">
-        <f>H22-10</f>
+        <f t="shared" si="9"/>
         <v>480</v>
       </c>
       <c r="J22" s="8">
-        <f>I22-10</f>
+        <f t="shared" si="10"/>
         <v>470</v>
       </c>
       <c r="K22" s="8">
         <v>480</v>
       </c>
       <c r="L22" s="8">
-        <f>K22+20</f>
+        <f t="shared" si="3"/>
         <v>500</v>
       </c>
       <c r="M22" s="8">
-        <f>L22+10</f>
+        <f t="shared" si="4"/>
         <v>510</v>
       </c>
       <c r="N22" s="8">
@@ -6825,7 +6798,7 @@
         <v>550</v>
       </c>
       <c r="P22" s="8">
-        <f>O22-10</f>
+        <f t="shared" si="6"/>
         <v>540</v>
       </c>
       <c r="Q22" s="8" t="s">
@@ -6838,9 +6811,7 @@
       <c r="B23" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="C23" s="8">
-        <v>420</v>
-      </c>
+      <c r="C23" s="8"/>
       <c r="D23" s="8">
         <v>440</v>
       </c>
@@ -6848,7 +6819,7 @@
         <v>460</v>
       </c>
       <c r="F23" s="8">
-        <f>E23+20</f>
+        <f t="shared" si="7"/>
         <v>480</v>
       </c>
       <c r="G23" s="11">
@@ -6858,15 +6829,15 @@
         <v>460</v>
       </c>
       <c r="I23" s="8">
-        <f>H23-10</f>
+        <f t="shared" si="9"/>
         <v>450</v>
       </c>
       <c r="J23" s="8">
-        <f>I23-10</f>
+        <f t="shared" si="10"/>
         <v>440</v>
       </c>
       <c r="P23" s="8">
-        <f>O23-10</f>
+        <f t="shared" si="6"/>
         <v>-10</v>
       </c>
       <c r="R23" s="16"/>
@@ -6876,8 +6847,8 @@
       <c r="B24" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="C24" s="8">
-        <v>430</v>
+      <c r="C24" s="8" t="s">
+        <v>52</v>
       </c>
       <c r="D24" s="8">
         <v>450</v>
@@ -6886,18 +6857,18 @@
         <v>470</v>
       </c>
       <c r="F24" s="8">
-        <f>E24+20</f>
+        <f t="shared" si="7"/>
         <v>490</v>
       </c>
       <c r="G24" s="8">
-        <f>F24+20</f>
+        <f t="shared" ref="G24:G33" si="11">F24+20</f>
         <v>510</v>
       </c>
       <c r="H24" s="8">
         <v>485</v>
       </c>
       <c r="I24" s="8">
-        <f>H24-10</f>
+        <f t="shared" si="9"/>
         <v>475</v>
       </c>
       <c r="J24" s="8">
@@ -6907,23 +6878,23 @@
         <v>470</v>
       </c>
       <c r="L24" s="8">
-        <f>K24+20</f>
+        <f t="shared" ref="L24:L29" si="12">K24+20</f>
         <v>490</v>
       </c>
       <c r="M24" s="8">
-        <f>L24+10</f>
+        <f t="shared" ref="M24:M29" si="13">L24+10</f>
         <v>500</v>
       </c>
       <c r="N24" s="8">
-        <f>M24+20</f>
+        <f t="shared" ref="N24:N36" si="14">M24+20</f>
         <v>520</v>
       </c>
       <c r="O24" s="8">
-        <f>N24+20</f>
+        <f t="shared" ref="O24:O29" si="15">N24+20</f>
         <v>540</v>
       </c>
       <c r="P24" s="8">
-        <f>O24-10</f>
+        <f t="shared" si="6"/>
         <v>530</v>
       </c>
       <c r="Q24" s="8" t="s">
@@ -6936,8 +6907,8 @@
       <c r="B25" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="C25" s="8">
-        <v>410</v>
+      <c r="C25" s="8" t="s">
+        <v>71</v>
       </c>
       <c r="D25" s="8">
         <v>430</v>
@@ -6946,45 +6917,45 @@
         <v>450</v>
       </c>
       <c r="F25" s="8">
-        <f>E25+20</f>
+        <f t="shared" si="7"/>
         <v>470</v>
       </c>
       <c r="G25" s="8">
-        <f>F25+20</f>
+        <f t="shared" si="11"/>
         <v>490</v>
       </c>
       <c r="H25" s="8">
         <v>450</v>
       </c>
       <c r="I25" s="8">
-        <f>H25-10</f>
+        <f t="shared" si="9"/>
         <v>440</v>
       </c>
       <c r="J25" s="8">
-        <f>I25-10</f>
+        <f t="shared" ref="J25:J33" si="16">I25-10</f>
         <v>430</v>
       </c>
       <c r="K25" s="15">
         <v>440</v>
       </c>
       <c r="L25" s="14">
-        <f>K25+20</f>
+        <f t="shared" si="12"/>
         <v>460</v>
       </c>
       <c r="M25" s="8">
-        <f>L25+10</f>
+        <f t="shared" si="13"/>
         <v>470</v>
       </c>
       <c r="N25" s="8">
-        <f>M25+20</f>
+        <f t="shared" si="14"/>
         <v>490</v>
       </c>
       <c r="O25" s="8">
-        <f>N25+20</f>
+        <f t="shared" si="15"/>
         <v>510</v>
       </c>
       <c r="P25" s="8">
-        <f>O25-10</f>
+        <f t="shared" si="6"/>
         <v>500</v>
       </c>
       <c r="Q25" s="15" t="s">
@@ -6997,8 +6968,8 @@
       <c r="B26" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="C26" s="8">
-        <v>440</v>
+      <c r="C26" s="8" t="s">
+        <v>144</v>
       </c>
       <c r="D26" s="8">
         <v>460</v>
@@ -7007,45 +6978,45 @@
         <v>480</v>
       </c>
       <c r="F26" s="8">
-        <f>E26+20</f>
+        <f t="shared" si="7"/>
         <v>500</v>
       </c>
       <c r="G26" s="8">
-        <f>F26+20</f>
+        <f t="shared" si="11"/>
         <v>520</v>
       </c>
       <c r="H26" s="8">
         <v>480</v>
       </c>
       <c r="I26" s="8">
-        <f>H26-10</f>
+        <f t="shared" si="9"/>
         <v>470</v>
       </c>
       <c r="J26" s="8">
-        <f>I26-10</f>
+        <f t="shared" si="16"/>
         <v>460</v>
       </c>
       <c r="K26" s="8">
         <v>470</v>
       </c>
       <c r="L26" s="8">
-        <f>K26+20</f>
+        <f t="shared" si="12"/>
         <v>490</v>
       </c>
       <c r="M26" s="8">
-        <f>L26+10</f>
+        <f t="shared" si="13"/>
         <v>500</v>
       </c>
       <c r="N26" s="8">
-        <f>M26+20</f>
+        <f t="shared" si="14"/>
         <v>520</v>
       </c>
       <c r="O26" s="8">
-        <f>N26+20</f>
+        <f t="shared" si="15"/>
         <v>540</v>
       </c>
       <c r="P26" s="8">
-        <f>O26-10</f>
+        <f t="shared" si="6"/>
         <v>530</v>
       </c>
       <c r="Q26" s="8" t="s">
@@ -7058,8 +7029,8 @@
       <c r="B27" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="C27" s="8">
-        <v>430</v>
+      <c r="C27" s="8" t="s">
+        <v>145</v>
       </c>
       <c r="D27" s="8">
         <v>450</v>
@@ -7068,45 +7039,45 @@
         <v>470</v>
       </c>
       <c r="F27" s="8">
-        <f>E27+20</f>
+        <f t="shared" si="7"/>
         <v>490</v>
       </c>
       <c r="G27" s="8">
-        <f>F27+20</f>
+        <f t="shared" si="11"/>
         <v>510</v>
       </c>
       <c r="H27" s="8">
         <v>470</v>
       </c>
       <c r="I27" s="8">
-        <f>H27-10</f>
+        <f t="shared" si="9"/>
         <v>460</v>
       </c>
       <c r="J27" s="8">
-        <f>I27-10</f>
+        <f t="shared" si="16"/>
         <v>450</v>
       </c>
       <c r="K27" s="8">
         <v>470</v>
       </c>
       <c r="L27" s="8">
-        <f>K27+20</f>
+        <f t="shared" si="12"/>
         <v>490</v>
       </c>
       <c r="M27" s="8">
-        <f>L27+10</f>
+        <f t="shared" si="13"/>
         <v>500</v>
       </c>
       <c r="N27" s="8">
-        <f>M27+20</f>
+        <f t="shared" si="14"/>
         <v>520</v>
       </c>
       <c r="O27" s="8">
-        <f>N27+20</f>
+        <f t="shared" si="15"/>
         <v>540</v>
       </c>
       <c r="P27" s="8">
-        <f>O27-10</f>
+        <f t="shared" si="6"/>
         <v>530</v>
       </c>
       <c r="Q27" s="8" t="s">
@@ -7117,8 +7088,8 @@
       <c r="B28" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="C28" s="8">
-        <v>430</v>
+      <c r="C28" s="8" t="s">
+        <v>50</v>
       </c>
       <c r="D28" s="8">
         <v>450</v>
@@ -7127,45 +7098,45 @@
         <v>470</v>
       </c>
       <c r="F28" s="8">
-        <f>E28+20</f>
+        <f t="shared" si="7"/>
         <v>490</v>
       </c>
       <c r="G28" s="8">
-        <f>F28+20</f>
+        <f t="shared" si="11"/>
         <v>510</v>
       </c>
       <c r="H28" s="8">
         <v>470</v>
       </c>
       <c r="I28" s="8">
-        <f>H28-10</f>
+        <f t="shared" si="9"/>
         <v>460</v>
       </c>
       <c r="J28" s="8">
-        <f>I28-10</f>
+        <f t="shared" si="16"/>
         <v>450</v>
       </c>
       <c r="K28" s="8">
         <v>460</v>
       </c>
       <c r="L28" s="8">
-        <f>K28+20</f>
+        <f t="shared" si="12"/>
         <v>480</v>
       </c>
       <c r="M28" s="8">
-        <f>L28+10</f>
+        <f t="shared" si="13"/>
         <v>490</v>
       </c>
       <c r="N28" s="8">
-        <f>M28+20</f>
+        <f t="shared" si="14"/>
         <v>510</v>
       </c>
       <c r="O28" s="8">
-        <f>N28+20</f>
+        <f t="shared" si="15"/>
         <v>530</v>
       </c>
       <c r="P28" s="8">
-        <f>O28-10</f>
+        <f t="shared" si="6"/>
         <v>520</v>
       </c>
       <c r="Q28" s="8" t="s">
@@ -7176,8 +7147,8 @@
       <c r="B29" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="C29" s="8">
-        <v>435</v>
+      <c r="C29" s="8" t="s">
+        <v>49</v>
       </c>
       <c r="D29" s="8">
         <v>455</v>
@@ -7186,45 +7157,45 @@
         <v>475</v>
       </c>
       <c r="F29" s="8">
-        <f>E29+20</f>
+        <f t="shared" si="7"/>
         <v>495</v>
       </c>
       <c r="G29" s="8">
-        <f>F29+20</f>
+        <f t="shared" si="11"/>
         <v>515</v>
       </c>
       <c r="H29" s="8">
         <v>475</v>
       </c>
       <c r="I29" s="8">
-        <f>H29-10</f>
+        <f t="shared" si="9"/>
         <v>465</v>
       </c>
       <c r="J29" s="8">
-        <f>I29-10</f>
+        <f t="shared" si="16"/>
         <v>455</v>
       </c>
       <c r="K29" s="8">
         <v>465</v>
       </c>
       <c r="L29" s="8">
-        <f>K29+20</f>
+        <f t="shared" si="12"/>
         <v>485</v>
       </c>
       <c r="M29" s="8">
-        <f>L29+10</f>
+        <f t="shared" si="13"/>
         <v>495</v>
       </c>
       <c r="N29" s="8">
-        <f>M29+20</f>
+        <f t="shared" si="14"/>
         <v>515</v>
       </c>
       <c r="O29" s="8">
-        <f>N29+20</f>
+        <f t="shared" si="15"/>
         <v>535</v>
       </c>
       <c r="P29" s="8">
-        <f>O29-10</f>
+        <f t="shared" si="6"/>
         <v>525</v>
       </c>
       <c r="Q29" s="8" t="s">
@@ -7235,8 +7206,8 @@
       <c r="B30" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="C30" s="8">
-        <v>420</v>
+      <c r="C30" s="8" t="s">
+        <v>146</v>
       </c>
       <c r="D30" s="8">
         <v>440</v>
@@ -7245,26 +7216,26 @@
         <v>460</v>
       </c>
       <c r="F30" s="8">
-        <f>E30+20</f>
+        <f t="shared" si="7"/>
         <v>480</v>
       </c>
       <c r="G30" s="8">
-        <f>F30+20</f>
+        <f t="shared" si="11"/>
         <v>500</v>
       </c>
       <c r="H30" s="8">
         <v>460</v>
       </c>
       <c r="I30" s="8">
-        <f>H30-10</f>
+        <f t="shared" si="9"/>
         <v>450</v>
       </c>
       <c r="J30" s="8">
-        <f>I30-10</f>
+        <f t="shared" si="16"/>
         <v>440</v>
       </c>
       <c r="N30" s="8">
-        <f>M30+20</f>
+        <f t="shared" si="14"/>
         <v>20</v>
       </c>
       <c r="Q30" s="8" t="s">
@@ -7275,8 +7246,8 @@
       <c r="B31" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="C31" s="8">
-        <v>425</v>
+      <c r="C31" s="8" t="s">
+        <v>147</v>
       </c>
       <c r="D31" s="8">
         <v>445</v>
@@ -7285,45 +7256,45 @@
         <v>465</v>
       </c>
       <c r="F31" s="8">
-        <f>E31+20</f>
+        <f t="shared" si="7"/>
         <v>485</v>
       </c>
       <c r="G31" s="8">
-        <f>F31+20</f>
+        <f t="shared" si="11"/>
         <v>505</v>
       </c>
       <c r="H31" s="8">
         <v>465</v>
       </c>
       <c r="I31" s="8">
-        <f>H31-10</f>
+        <f t="shared" si="9"/>
         <v>455</v>
       </c>
       <c r="J31" s="8">
-        <f>I31-10</f>
+        <f t="shared" si="16"/>
         <v>445</v>
       </c>
       <c r="K31" s="8">
         <v>455</v>
       </c>
       <c r="L31" s="8">
-        <f>K31+20</f>
+        <f t="shared" ref="L31:L41" si="17">K31+20</f>
         <v>475</v>
       </c>
       <c r="M31" s="8">
-        <f>L31+10</f>
+        <f t="shared" ref="M31:M41" si="18">L31+10</f>
         <v>485</v>
       </c>
       <c r="N31" s="8">
-        <f>M31+20</f>
+        <f t="shared" si="14"/>
         <v>505</v>
       </c>
       <c r="O31" s="8">
-        <f>N31+20</f>
+        <f t="shared" ref="O31:O47" si="19">N31+20</f>
         <v>525</v>
       </c>
       <c r="P31" s="8">
-        <f>O31-10</f>
+        <f t="shared" ref="P31:P49" si="20">O31-10</f>
         <v>515</v>
       </c>
       <c r="Q31" s="8" t="s">
@@ -7334,8 +7305,8 @@
       <c r="B32" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C32" s="8">
-        <v>425</v>
+      <c r="C32" s="8" t="s">
+        <v>117</v>
       </c>
       <c r="D32" s="8">
         <v>445</v>
@@ -7344,45 +7315,45 @@
         <v>465</v>
       </c>
       <c r="F32" s="8">
-        <f>E32+20</f>
+        <f t="shared" si="7"/>
         <v>485</v>
       </c>
       <c r="G32" s="8">
-        <f>F32+20</f>
+        <f t="shared" si="11"/>
         <v>505</v>
       </c>
       <c r="H32" s="8">
         <v>465</v>
       </c>
       <c r="I32" s="8">
-        <f>H32-10</f>
+        <f t="shared" si="9"/>
         <v>455</v>
       </c>
       <c r="J32" s="8">
-        <f>I32-10</f>
+        <f t="shared" si="16"/>
         <v>445</v>
       </c>
       <c r="K32" s="8">
         <v>455</v>
       </c>
       <c r="L32" s="8">
-        <f>K32+20</f>
+        <f t="shared" si="17"/>
         <v>475</v>
       </c>
       <c r="M32" s="8">
-        <f>L32+10</f>
+        <f t="shared" si="18"/>
         <v>485</v>
       </c>
       <c r="N32" s="8">
-        <f>M32+20</f>
+        <f t="shared" si="14"/>
         <v>505</v>
       </c>
       <c r="O32" s="8">
-        <f>N32+20</f>
+        <f t="shared" si="19"/>
         <v>525</v>
       </c>
       <c r="P32" s="8">
-        <f>O32-10</f>
+        <f t="shared" si="20"/>
         <v>515</v>
       </c>
       <c r="Q32" s="8" t="s">
@@ -7393,8 +7364,8 @@
       <c r="B33" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="C33" s="8">
-        <v>410</v>
+      <c r="C33" s="8" t="s">
+        <v>47</v>
       </c>
       <c r="D33" s="8">
         <v>430</v>
@@ -7403,45 +7374,45 @@
         <v>450</v>
       </c>
       <c r="F33" s="8">
-        <f>E33+20</f>
+        <f t="shared" si="7"/>
         <v>470</v>
       </c>
       <c r="G33" s="8">
-        <f>F33+20</f>
+        <f t="shared" si="11"/>
         <v>490</v>
       </c>
       <c r="H33" s="8">
         <v>450</v>
       </c>
       <c r="I33" s="8">
-        <f>H33-10</f>
+        <f t="shared" si="9"/>
         <v>440</v>
       </c>
       <c r="J33" s="8">
-        <f>I33-10</f>
+        <f t="shared" si="16"/>
         <v>430</v>
       </c>
       <c r="K33" s="15">
         <v>440</v>
       </c>
       <c r="L33" s="14">
-        <f>K33+20</f>
+        <f t="shared" si="17"/>
         <v>460</v>
       </c>
       <c r="M33" s="8">
-        <f>L33+10</f>
+        <f t="shared" si="18"/>
         <v>470</v>
       </c>
       <c r="N33" s="8">
-        <f>M33+20</f>
+        <f t="shared" si="14"/>
         <v>490</v>
       </c>
       <c r="O33" s="8">
-        <f>N33+20</f>
+        <f t="shared" si="19"/>
         <v>510</v>
       </c>
       <c r="P33" s="8">
-        <f>O33-10</f>
+        <f t="shared" si="20"/>
         <v>500</v>
       </c>
       <c r="Q33" s="15" t="s">
@@ -7452,6 +7423,9 @@
       <c r="B34" s="7" t="s">
         <v>148</v>
       </c>
+      <c r="C34" s="8" t="s">
+        <v>148</v>
+      </c>
       <c r="J34" s="8">
         <v>440</v>
       </c>
@@ -7459,23 +7433,23 @@
         <v>475</v>
       </c>
       <c r="L34" s="8">
-        <f>K34+20</f>
+        <f t="shared" si="17"/>
         <v>495</v>
       </c>
       <c r="M34" s="8">
-        <f>L34+10</f>
+        <f t="shared" si="18"/>
         <v>505</v>
       </c>
       <c r="N34" s="8">
-        <f>M34+20</f>
+        <f t="shared" si="14"/>
         <v>525</v>
       </c>
       <c r="O34" s="8">
-        <f>N34+20</f>
+        <f t="shared" si="19"/>
         <v>545</v>
       </c>
       <c r="P34" s="8">
-        <f>O34-10</f>
+        <f t="shared" si="20"/>
         <v>535</v>
       </c>
       <c r="Q34" s="8" t="s">
@@ -7486,6 +7460,9 @@
       <c r="B35" s="7" t="s">
         <v>45</v>
       </c>
+      <c r="C35" s="8" t="s">
+        <v>45</v>
+      </c>
       <c r="G35" s="8">
         <v>480</v>
       </c>
@@ -7500,23 +7477,23 @@
         <v>450</v>
       </c>
       <c r="L35" s="8">
-        <f>K35+20</f>
+        <f t="shared" si="17"/>
         <v>470</v>
       </c>
       <c r="M35" s="8">
-        <f>L35+10</f>
+        <f t="shared" si="18"/>
         <v>480</v>
       </c>
       <c r="N35" s="8">
-        <f>M35+20</f>
+        <f t="shared" si="14"/>
         <v>500</v>
       </c>
       <c r="O35" s="8">
-        <f>N35+20</f>
+        <f t="shared" si="19"/>
         <v>520</v>
       </c>
       <c r="P35" s="8">
-        <f>O35-10</f>
+        <f t="shared" si="20"/>
         <v>510</v>
       </c>
       <c r="Q35" s="8" t="s">
@@ -7527,8 +7504,8 @@
       <c r="B36" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="C36" s="8">
-        <v>445</v>
+      <c r="C36" s="8" t="s">
+        <v>46</v>
       </c>
       <c r="D36" s="17">
         <v>455</v>
@@ -7558,23 +7535,23 @@
         <v>465</v>
       </c>
       <c r="L36" s="8">
-        <f>K36+20</f>
+        <f t="shared" si="17"/>
         <v>485</v>
       </c>
       <c r="M36" s="8">
-        <f>L36+10</f>
+        <f t="shared" si="18"/>
         <v>495</v>
       </c>
       <c r="N36" s="8">
-        <f>M36+20</f>
+        <f t="shared" si="14"/>
         <v>515</v>
       </c>
       <c r="O36" s="8">
-        <f>N36+20</f>
+        <f t="shared" si="19"/>
         <v>535</v>
       </c>
       <c r="P36" s="8">
-        <f>O36-10</f>
+        <f t="shared" si="20"/>
         <v>525</v>
       </c>
       <c r="Q36" s="8" t="s">
@@ -7585,26 +7562,29 @@
       <c r="B37" s="7" t="s">
         <v>44</v>
       </c>
+      <c r="C37" s="8" t="s">
+        <v>44</v>
+      </c>
       <c r="K37" s="8">
         <v>470</v>
       </c>
       <c r="L37" s="8">
-        <f>K37+20</f>
+        <f t="shared" si="17"/>
         <v>490</v>
       </c>
       <c r="M37" s="8">
-        <f>L37+10</f>
+        <f t="shared" si="18"/>
         <v>500</v>
       </c>
       <c r="N37" s="8">
         <v>530</v>
       </c>
       <c r="O37" s="8">
-        <f>N37+20</f>
+        <f t="shared" si="19"/>
         <v>550</v>
       </c>
       <c r="P37" s="8">
-        <f>O37-10</f>
+        <f t="shared" si="20"/>
         <v>540</v>
       </c>
       <c r="Q37" s="8" t="s">
@@ -7615,8 +7595,8 @@
       <c r="B38" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="C38" s="8">
-        <v>430</v>
+      <c r="C38" s="8" t="s">
+        <v>43</v>
       </c>
       <c r="D38" s="8">
         <v>450</v>
@@ -7647,23 +7627,23 @@
         <v>460</v>
       </c>
       <c r="L38" s="8">
-        <f>K38+20</f>
+        <f t="shared" si="17"/>
         <v>480</v>
       </c>
       <c r="M38" s="8">
-        <f>L38+10</f>
+        <f t="shared" si="18"/>
         <v>490</v>
       </c>
       <c r="N38" s="8">
-        <f>M38+20</f>
+        <f t="shared" ref="N38:N47" si="21">M38+20</f>
         <v>510</v>
       </c>
       <c r="O38" s="8">
-        <f>N38+20</f>
+        <f t="shared" si="19"/>
         <v>530</v>
       </c>
       <c r="P38" s="8">
-        <f>O38-10</f>
+        <f t="shared" si="20"/>
         <v>520</v>
       </c>
       <c r="Q38" s="8" t="s">
@@ -7674,8 +7654,8 @@
       <c r="B39" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="C39" s="8">
-        <v>440</v>
+      <c r="C39" s="8" t="s">
+        <v>149</v>
       </c>
       <c r="D39" s="8">
         <v>460</v>
@@ -7706,23 +7686,23 @@
         <v>470</v>
       </c>
       <c r="L39" s="8">
-        <f>K39+20</f>
+        <f t="shared" si="17"/>
         <v>490</v>
       </c>
       <c r="M39" s="8">
-        <f>L39+10</f>
+        <f t="shared" si="18"/>
         <v>500</v>
       </c>
       <c r="N39" s="8">
-        <f>M39+20</f>
+        <f t="shared" si="21"/>
         <v>520</v>
       </c>
       <c r="O39" s="8">
-        <f>N39+20</f>
+        <f t="shared" si="19"/>
         <v>540</v>
       </c>
       <c r="P39" s="8">
-        <f>O39-10</f>
+        <f t="shared" si="20"/>
         <v>530</v>
       </c>
       <c r="Q39" s="8" t="s">
@@ -7733,8 +7713,8 @@
       <c r="B40" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="C40" s="8">
-        <v>430</v>
+      <c r="C40" s="8" t="s">
+        <v>42</v>
       </c>
       <c r="D40" s="8">
         <v>450</v>
@@ -7765,23 +7745,23 @@
         <v>460</v>
       </c>
       <c r="L40" s="8">
-        <f>K40+20</f>
+        <f t="shared" si="17"/>
         <v>480</v>
       </c>
       <c r="M40" s="8">
-        <f>L40+10</f>
+        <f t="shared" si="18"/>
         <v>490</v>
       </c>
       <c r="N40" s="8">
-        <f>M40+20</f>
+        <f t="shared" si="21"/>
         <v>510</v>
       </c>
       <c r="O40" s="8">
-        <f>N40+20</f>
+        <f t="shared" si="19"/>
         <v>530</v>
       </c>
       <c r="P40" s="8">
-        <f>O40-10</f>
+        <f t="shared" si="20"/>
         <v>520</v>
       </c>
       <c r="Q40" s="8" t="s">
@@ -7792,8 +7772,8 @@
       <c r="B41" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="C41" s="8">
-        <v>430</v>
+      <c r="C41" s="8" t="s">
+        <v>41</v>
       </c>
       <c r="D41" s="8">
         <v>450</v>
@@ -7824,23 +7804,23 @@
         <v>470</v>
       </c>
       <c r="L41" s="8">
-        <f>K41+20</f>
+        <f t="shared" si="17"/>
         <v>490</v>
       </c>
       <c r="M41" s="8">
-        <f>L41+10</f>
+        <f t="shared" si="18"/>
         <v>500</v>
       </c>
       <c r="N41" s="8">
-        <f>M41+20</f>
+        <f t="shared" si="21"/>
         <v>520</v>
       </c>
       <c r="O41" s="8">
-        <f>N41+20</f>
+        <f t="shared" si="19"/>
         <v>540</v>
       </c>
       <c r="P41" s="8">
-        <f>O41-10</f>
+        <f t="shared" si="20"/>
         <v>530</v>
       </c>
       <c r="Q41" s="8" t="s">
@@ -7848,19 +7828,22 @@
       </c>
     </row>
     <row r="42" spans="2:17">
+      <c r="C42" s="8" t="s">
+        <v>40</v>
+      </c>
       <c r="M42" s="8">
         <v>480</v>
       </c>
       <c r="N42" s="8">
-        <f>M42+20</f>
+        <f t="shared" si="21"/>
         <v>500</v>
       </c>
       <c r="O42" s="8">
-        <f>N42+20</f>
+        <f t="shared" si="19"/>
         <v>520</v>
       </c>
       <c r="P42" s="8">
-        <f>O42-10</f>
+        <f t="shared" si="20"/>
         <v>510</v>
       </c>
       <c r="Q42" s="8" t="s">
@@ -7871,8 +7854,8 @@
       <c r="B43" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="C43" s="8">
-        <v>435</v>
+      <c r="C43" s="8" t="s">
+        <v>150</v>
       </c>
       <c r="D43" s="8">
         <v>455</v>
@@ -7910,15 +7893,15 @@
         <v>495</v>
       </c>
       <c r="N43" s="8">
-        <f>M43+20</f>
+        <f t="shared" si="21"/>
         <v>515</v>
       </c>
       <c r="O43" s="8">
-        <f>N43+20</f>
+        <f t="shared" si="19"/>
         <v>535</v>
       </c>
       <c r="P43" s="8">
-        <f>O43-10</f>
+        <f t="shared" si="20"/>
         <v>525</v>
       </c>
       <c r="Q43" s="8" t="s">
@@ -7929,8 +7912,8 @@
       <c r="B44" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="C44" s="8">
-        <v>410</v>
+      <c r="C44" s="8" t="s">
+        <v>39</v>
       </c>
       <c r="D44" s="8">
         <v>430</v>
@@ -7969,15 +7952,15 @@
         <v>470</v>
       </c>
       <c r="N44" s="8">
-        <f>M44+20</f>
+        <f t="shared" si="21"/>
         <v>490</v>
       </c>
       <c r="O44" s="8">
-        <f>N44+20</f>
+        <f t="shared" si="19"/>
         <v>510</v>
       </c>
       <c r="P44" s="8">
-        <f>O44-10</f>
+        <f t="shared" si="20"/>
         <v>500</v>
       </c>
       <c r="Q44" s="15" t="s">
@@ -7988,8 +7971,8 @@
       <c r="B45" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C45" s="8">
-        <v>410</v>
+      <c r="C45" s="8" t="s">
+        <v>38</v>
       </c>
       <c r="D45" s="8">
         <v>430</v>
@@ -8028,15 +8011,15 @@
         <v>470</v>
       </c>
       <c r="N45" s="8">
-        <f>M45+20</f>
+        <f t="shared" si="21"/>
         <v>490</v>
       </c>
       <c r="O45" s="8">
-        <f>N45+20</f>
+        <f t="shared" si="19"/>
         <v>510</v>
       </c>
       <c r="P45" s="8">
-        <f>O45-10</f>
+        <f t="shared" si="20"/>
         <v>500</v>
       </c>
       <c r="Q45" s="15" t="s">
@@ -8047,8 +8030,8 @@
       <c r="B46" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="C46" s="8">
-        <v>420</v>
+      <c r="C46" s="8" t="s">
+        <v>152</v>
       </c>
       <c r="D46" s="8">
         <v>440</v>
@@ -8087,15 +8070,15 @@
         <v>480</v>
       </c>
       <c r="N46" s="8">
-        <f>M46+20</f>
+        <f t="shared" si="21"/>
         <v>500</v>
       </c>
       <c r="O46" s="8">
-        <f>N46+20</f>
+        <f t="shared" si="19"/>
         <v>520</v>
       </c>
       <c r="P46" s="8">
-        <f>O46-10</f>
+        <f t="shared" si="20"/>
         <v>510</v>
       </c>
       <c r="Q46" s="8" t="s">
@@ -8106,8 +8089,8 @@
       <c r="B47" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="C47" s="8">
-        <v>430</v>
+      <c r="C47" s="8" t="s">
+        <v>153</v>
       </c>
       <c r="D47" s="8">
         <v>450</v>
@@ -8146,15 +8129,15 @@
         <v>490</v>
       </c>
       <c r="N47" s="8">
-        <f>M47+20</f>
+        <f t="shared" si="21"/>
         <v>510</v>
       </c>
       <c r="O47" s="8">
-        <f>N47+20</f>
+        <f t="shared" si="19"/>
         <v>530</v>
       </c>
       <c r="P47" s="8">
-        <f>O47-10</f>
+        <f t="shared" si="20"/>
         <v>520</v>
       </c>
       <c r="Q47" s="8" t="s">
@@ -8163,13 +8146,16 @@
     </row>
     <row r="48" spans="2:17">
       <c r="B48" s="13"/>
+      <c r="C48" s="8" t="s">
+        <v>65</v>
+      </c>
       <c r="K48" s="15"/>
       <c r="L48" s="14"/>
       <c r="O48" s="8">
         <v>520</v>
       </c>
       <c r="P48" s="8">
-        <f>O48-10</f>
+        <f t="shared" si="20"/>
         <v>510</v>
       </c>
       <c r="Q48" s="8" t="s">
@@ -8180,8 +8166,8 @@
       <c r="B49" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C49" s="8">
-        <v>410</v>
+      <c r="C49" s="8" t="s">
+        <v>36</v>
       </c>
       <c r="D49" s="8">
         <v>430</v>
@@ -8201,7 +8187,7 @@
         <v>450</v>
       </c>
       <c r="I49" s="8">
-        <f>H49-10</f>
+        <f t="shared" ref="I49:I54" si="22">H49-10</f>
         <v>440</v>
       </c>
       <c r="J49" s="8">
@@ -8228,7 +8214,7 @@
         <v>510</v>
       </c>
       <c r="P49" s="8">
-        <f>O49-10</f>
+        <f t="shared" si="20"/>
         <v>500</v>
       </c>
       <c r="Q49" s="15" t="s">
@@ -8239,8 +8225,8 @@
       <c r="B50" s="13" t="s">
         <v>154</v>
       </c>
-      <c r="C50" s="8">
-        <v>410</v>
+      <c r="C50" s="8" t="s">
+        <v>154</v>
       </c>
       <c r="D50" s="8">
         <v>430</v>
@@ -8260,7 +8246,7 @@
         <v>450</v>
       </c>
       <c r="I50" s="8">
-        <f>H50-10</f>
+        <f t="shared" si="22"/>
         <v>440</v>
       </c>
       <c r="J50" s="8">
@@ -8277,8 +8263,8 @@
       <c r="B51" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="C51" s="8">
-        <v>450</v>
+      <c r="C51" s="8" t="s">
+        <v>64</v>
       </c>
       <c r="D51" s="8">
         <v>470</v>
@@ -8298,7 +8284,7 @@
         <v>490</v>
       </c>
       <c r="I51" s="8">
-        <f>H51-10</f>
+        <f t="shared" si="22"/>
         <v>480</v>
       </c>
       <c r="J51" s="8">
@@ -8309,23 +8295,23 @@
         <v>480</v>
       </c>
       <c r="L51" s="8">
-        <f>K51+20</f>
+        <f t="shared" ref="L51:L63" si="23">K51+20</f>
         <v>500</v>
       </c>
       <c r="M51" s="8">
-        <f>L51+10</f>
+        <f t="shared" ref="M51:M63" si="24">L51+10</f>
         <v>510</v>
       </c>
       <c r="N51" s="8">
-        <f>M51+20</f>
+        <f t="shared" ref="N51:N57" si="25">M51+20</f>
         <v>530</v>
       </c>
       <c r="O51" s="8">
-        <f>N51+20</f>
+        <f t="shared" ref="O51:O63" si="26">N51+20</f>
         <v>550</v>
       </c>
       <c r="P51" s="8">
-        <f>O51-10</f>
+        <f t="shared" ref="P51:P63" si="27">O51-10</f>
         <v>540</v>
       </c>
       <c r="Q51" s="8" t="s">
@@ -8336,11 +8322,14 @@
       <c r="B52" s="7" t="s">
         <v>33</v>
       </c>
+      <c r="C52" s="8" t="s">
+        <v>33</v>
+      </c>
       <c r="G52" s="8">
         <v>480</v>
       </c>
       <c r="I52" s="8">
-        <f>H52-10</f>
+        <f t="shared" si="22"/>
         <v>-10</v>
       </c>
       <c r="J52" s="8">
@@ -8350,23 +8339,23 @@
         <v>450</v>
       </c>
       <c r="L52" s="8">
-        <f>K52+20</f>
+        <f t="shared" si="23"/>
         <v>470</v>
       </c>
       <c r="M52" s="8">
-        <f>L52+10</f>
+        <f t="shared" si="24"/>
         <v>480</v>
       </c>
       <c r="N52" s="8">
-        <f>M52+20</f>
+        <f t="shared" si="25"/>
         <v>500</v>
       </c>
       <c r="O52" s="8">
-        <f>N52+20</f>
+        <f t="shared" si="26"/>
         <v>520</v>
       </c>
       <c r="P52" s="8">
-        <f>O52-10</f>
+        <f t="shared" si="27"/>
         <v>510</v>
       </c>
       <c r="Q52" s="8" t="s">
@@ -8377,8 +8366,8 @@
       <c r="B53" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="C53" s="8">
-        <v>450</v>
+      <c r="C53" s="8" t="s">
+        <v>155</v>
       </c>
       <c r="D53" s="8">
         <v>470</v>
@@ -8387,18 +8376,18 @@
         <v>490</v>
       </c>
       <c r="F53" s="8">
-        <f>E53+20</f>
+        <f t="shared" ref="F53:F63" si="28">E53+20</f>
         <v>510</v>
       </c>
       <c r="G53" s="8">
-        <f>F53+20</f>
+        <f t="shared" ref="G53:G63" si="29">F53+20</f>
         <v>530</v>
       </c>
       <c r="H53" s="8">
         <v>490</v>
       </c>
       <c r="I53" s="8">
-        <f>H53-10</f>
+        <f t="shared" si="22"/>
         <v>480</v>
       </c>
       <c r="J53" s="8">
@@ -8409,23 +8398,23 @@
         <v>480</v>
       </c>
       <c r="L53" s="8">
-        <f>K53+20</f>
+        <f t="shared" si="23"/>
         <v>500</v>
       </c>
       <c r="M53" s="8">
-        <f>L53+10</f>
+        <f t="shared" si="24"/>
         <v>510</v>
       </c>
       <c r="N53" s="8">
-        <f>M53+20</f>
+        <f t="shared" si="25"/>
         <v>530</v>
       </c>
       <c r="O53" s="8">
-        <f>N53+20</f>
+        <f t="shared" si="26"/>
         <v>550</v>
       </c>
       <c r="P53" s="8">
-        <f>O53-10</f>
+        <f t="shared" si="27"/>
         <v>540</v>
       </c>
       <c r="Q53" s="8" t="s">
@@ -8436,8 +8425,8 @@
       <c r="B54" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="C54" s="8">
-        <v>430</v>
+      <c r="C54" s="8" t="s">
+        <v>35</v>
       </c>
       <c r="D54" s="8">
         <v>450</v>
@@ -8446,18 +8435,18 @@
         <v>470</v>
       </c>
       <c r="F54" s="8">
-        <f>E54+20</f>
+        <f t="shared" si="28"/>
         <v>490</v>
       </c>
       <c r="G54" s="8">
-        <f>F54+20</f>
+        <f t="shared" si="29"/>
         <v>510</v>
       </c>
       <c r="H54" s="8">
         <v>470</v>
       </c>
       <c r="I54" s="8">
-        <f>H54-10</f>
+        <f t="shared" si="22"/>
         <v>460</v>
       </c>
       <c r="J54" s="8">
@@ -8468,23 +8457,23 @@
         <v>460</v>
       </c>
       <c r="L54" s="8">
-        <f>K54+20</f>
+        <f t="shared" si="23"/>
         <v>480</v>
       </c>
       <c r="M54" s="8">
-        <f>L54+10</f>
+        <f t="shared" si="24"/>
         <v>490</v>
       </c>
       <c r="N54" s="8">
-        <f>M54+20</f>
+        <f t="shared" si="25"/>
         <v>510</v>
       </c>
       <c r="O54" s="8">
-        <f>N54+20</f>
+        <f t="shared" si="26"/>
         <v>530</v>
       </c>
       <c r="P54" s="8">
-        <f>O54-10</f>
+        <f t="shared" si="27"/>
         <v>520</v>
       </c>
       <c r="Q54" s="8" t="s">
@@ -8495,8 +8484,8 @@
       <c r="B55" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="C55" s="8">
-        <v>430</v>
+      <c r="C55" s="8" t="s">
+        <v>34</v>
       </c>
       <c r="D55" s="8">
         <v>450</v>
@@ -8505,11 +8494,11 @@
         <v>470</v>
       </c>
       <c r="F55" s="8">
-        <f>E55+20</f>
+        <f t="shared" si="28"/>
         <v>490</v>
       </c>
       <c r="G55" s="8">
-        <f>F55+20</f>
+        <f t="shared" si="29"/>
         <v>510</v>
       </c>
       <c r="H55" s="8">
@@ -8525,23 +8514,23 @@
         <v>460</v>
       </c>
       <c r="L55" s="8">
-        <f>K55+20</f>
+        <f t="shared" si="23"/>
         <v>480</v>
       </c>
       <c r="M55" s="8">
-        <f>L55+10</f>
+        <f t="shared" si="24"/>
         <v>490</v>
       </c>
       <c r="N55" s="8">
-        <f>M55+20</f>
+        <f t="shared" si="25"/>
         <v>510</v>
       </c>
       <c r="O55" s="8">
-        <f>N55+20</f>
+        <f t="shared" si="26"/>
         <v>530</v>
       </c>
       <c r="P55" s="8">
-        <f>O55-10</f>
+        <f t="shared" si="27"/>
         <v>520</v>
       </c>
       <c r="Q55" s="8" t="s">
@@ -8552,8 +8541,8 @@
       <c r="B56" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="C56" s="8">
-        <v>425</v>
+      <c r="C56" s="8" t="s">
+        <v>113</v>
       </c>
       <c r="D56" s="8">
         <v>445</v>
@@ -8562,45 +8551,45 @@
         <v>465</v>
       </c>
       <c r="F56" s="8">
-        <f>E56+20</f>
+        <f t="shared" si="28"/>
         <v>485</v>
       </c>
       <c r="G56" s="8">
-        <f>F56+20</f>
+        <f t="shared" si="29"/>
         <v>505</v>
       </c>
       <c r="H56" s="8">
         <v>465</v>
       </c>
       <c r="I56" s="8">
-        <f>H56-10</f>
+        <f t="shared" ref="I56:I63" si="30">H56-10</f>
         <v>455</v>
       </c>
       <c r="J56" s="8">
-        <f>I56-10</f>
+        <f t="shared" ref="J56:J63" si="31">I56-10</f>
         <v>445</v>
       </c>
       <c r="K56" s="8">
         <v>450</v>
       </c>
       <c r="L56" s="8">
-        <f>K56+20</f>
+        <f t="shared" si="23"/>
         <v>470</v>
       </c>
       <c r="M56" s="8">
-        <f>L56+10</f>
+        <f t="shared" si="24"/>
         <v>480</v>
       </c>
       <c r="N56" s="8">
-        <f>M56+20</f>
+        <f t="shared" si="25"/>
         <v>500</v>
       </c>
       <c r="O56" s="8">
-        <f>N56+20</f>
+        <f t="shared" si="26"/>
         <v>520</v>
       </c>
       <c r="P56" s="8">
-        <f>O56-10</f>
+        <f t="shared" si="27"/>
         <v>510</v>
       </c>
       <c r="Q56" s="8" t="s">
@@ -8611,8 +8600,8 @@
       <c r="B57" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="C57" s="8">
-        <v>440</v>
+      <c r="C57" s="8" t="s">
+        <v>86</v>
       </c>
       <c r="D57" s="8">
         <v>460</v>
@@ -8621,45 +8610,45 @@
         <v>480</v>
       </c>
       <c r="F57" s="8">
-        <f>E57+20</f>
+        <f t="shared" si="28"/>
         <v>500</v>
       </c>
       <c r="G57" s="8">
-        <f>F57+20</f>
+        <f t="shared" si="29"/>
         <v>520</v>
       </c>
       <c r="H57" s="8">
         <v>480</v>
       </c>
       <c r="I57" s="8">
-        <f>H57-10</f>
+        <f t="shared" si="30"/>
         <v>470</v>
       </c>
       <c r="J57" s="8">
-        <f>I57-10</f>
+        <f t="shared" si="31"/>
         <v>460</v>
       </c>
       <c r="K57" s="8">
         <v>470</v>
       </c>
       <c r="L57" s="8">
-        <f>K57+20</f>
+        <f t="shared" si="23"/>
         <v>490</v>
       </c>
       <c r="M57" s="8">
-        <f>L57+10</f>
+        <f t="shared" si="24"/>
         <v>500</v>
       </c>
       <c r="N57" s="8">
-        <f>M57+20</f>
+        <f t="shared" si="25"/>
         <v>520</v>
       </c>
       <c r="O57" s="8">
-        <f>N57+20</f>
+        <f t="shared" si="26"/>
         <v>540</v>
       </c>
       <c r="P57" s="8">
-        <f>O57-10</f>
+        <f t="shared" si="27"/>
         <v>530</v>
       </c>
       <c r="Q57" s="8" t="s">
@@ -8670,8 +8659,8 @@
       <c r="B58" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="C58" s="8">
-        <v>440</v>
+      <c r="C58" s="8" t="s">
+        <v>156</v>
       </c>
       <c r="D58" s="8">
         <v>460</v>
@@ -8680,44 +8669,44 @@
         <v>480</v>
       </c>
       <c r="F58" s="8">
-        <f>E58+20</f>
+        <f t="shared" si="28"/>
         <v>500</v>
       </c>
       <c r="G58" s="8">
-        <f>F58+20</f>
+        <f t="shared" si="29"/>
         <v>520</v>
       </c>
       <c r="H58" s="8">
         <v>480</v>
       </c>
       <c r="I58" s="8">
-        <f>H58-10</f>
+        <f t="shared" si="30"/>
         <v>470</v>
       </c>
       <c r="J58" s="8">
-        <f>I58-10</f>
+        <f t="shared" si="31"/>
         <v>460</v>
       </c>
       <c r="K58" s="8">
         <v>470</v>
       </c>
       <c r="L58" s="8">
-        <f>K58+20</f>
+        <f t="shared" si="23"/>
         <v>490</v>
       </c>
       <c r="M58" s="8">
-        <f>L58+10</f>
+        <f t="shared" si="24"/>
         <v>500</v>
       </c>
       <c r="N58" s="8">
         <v>530</v>
       </c>
       <c r="O58" s="8">
-        <f>N58+20</f>
+        <f t="shared" si="26"/>
         <v>550</v>
       </c>
       <c r="P58" s="8">
-        <f>O58-10</f>
+        <f t="shared" si="27"/>
         <v>540</v>
       </c>
       <c r="Q58" s="8" t="s">
@@ -8728,8 +8717,8 @@
       <c r="B59" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="C59" s="8">
-        <v>440</v>
+      <c r="C59" s="8" t="s">
+        <v>32</v>
       </c>
       <c r="D59" s="8">
         <v>460</v>
@@ -8738,33 +8727,33 @@
         <v>480</v>
       </c>
       <c r="F59" s="8">
-        <f>E59+20</f>
+        <f t="shared" si="28"/>
         <v>500</v>
       </c>
       <c r="G59" s="8">
-        <f>F59+20</f>
+        <f t="shared" si="29"/>
         <v>520</v>
       </c>
       <c r="H59" s="8">
         <v>480</v>
       </c>
       <c r="I59" s="8">
-        <f>H59-10</f>
+        <f t="shared" si="30"/>
         <v>470</v>
       </c>
       <c r="J59" s="8">
-        <f>I59-10</f>
+        <f t="shared" si="31"/>
         <v>460</v>
       </c>
       <c r="K59" s="8">
         <v>470</v>
       </c>
       <c r="L59" s="8">
-        <f>K59+20</f>
+        <f t="shared" si="23"/>
         <v>490</v>
       </c>
       <c r="M59" s="8">
-        <f>L59+10</f>
+        <f t="shared" si="24"/>
         <v>500</v>
       </c>
       <c r="N59" s="8">
@@ -8772,11 +8761,11 @@
         <v>520</v>
       </c>
       <c r="O59" s="8">
-        <f>N59+20</f>
+        <f t="shared" si="26"/>
         <v>540</v>
       </c>
       <c r="P59" s="8">
-        <f>O59-10</f>
+        <f t="shared" si="27"/>
         <v>530</v>
       </c>
       <c r="Q59" s="8" t="s">
@@ -8787,8 +8776,8 @@
       <c r="B60" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="C60" s="8">
-        <v>410</v>
+      <c r="C60" s="8" t="s">
+        <v>68</v>
       </c>
       <c r="D60" s="8">
         <v>430</v>
@@ -8797,33 +8786,33 @@
         <v>450</v>
       </c>
       <c r="F60" s="8">
-        <f>E60+20</f>
+        <f t="shared" si="28"/>
         <v>470</v>
       </c>
       <c r="G60" s="8">
-        <f>F60+20</f>
+        <f t="shared" si="29"/>
         <v>490</v>
       </c>
       <c r="H60" s="8">
         <v>450</v>
       </c>
       <c r="I60" s="8">
-        <f>H60-10</f>
+        <f t="shared" si="30"/>
         <v>440</v>
       </c>
       <c r="J60" s="8">
-        <f>I60-10</f>
+        <f t="shared" si="31"/>
         <v>430</v>
       </c>
       <c r="K60" s="15">
         <v>440</v>
       </c>
       <c r="L60" s="14">
-        <f>K60+20</f>
+        <f t="shared" si="23"/>
         <v>460</v>
       </c>
       <c r="M60" s="8">
-        <f>L60+10</f>
+        <f t="shared" si="24"/>
         <v>470</v>
       </c>
       <c r="N60" s="8">
@@ -8831,11 +8820,11 @@
         <v>490</v>
       </c>
       <c r="O60" s="8">
-        <f>N60+20</f>
+        <f t="shared" si="26"/>
         <v>510</v>
       </c>
       <c r="P60" s="8">
-        <f>O60-10</f>
+        <f t="shared" si="27"/>
         <v>500</v>
       </c>
       <c r="Q60" s="15" t="s">
@@ -8846,8 +8835,8 @@
       <c r="B61" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="C61" s="8">
-        <v>430</v>
+      <c r="C61" s="8" t="s">
+        <v>157</v>
       </c>
       <c r="D61" s="8">
         <v>450</v>
@@ -8856,33 +8845,33 @@
         <v>470</v>
       </c>
       <c r="F61" s="8">
-        <f>E61+20</f>
+        <f t="shared" si="28"/>
         <v>490</v>
       </c>
       <c r="G61" s="8">
-        <f>F61+20</f>
+        <f t="shared" si="29"/>
         <v>510</v>
       </c>
       <c r="H61" s="8">
         <v>470</v>
       </c>
       <c r="I61" s="8">
-        <f>H61-10</f>
+        <f t="shared" si="30"/>
         <v>460</v>
       </c>
       <c r="J61" s="8">
-        <f>I61-10</f>
+        <f t="shared" si="31"/>
         <v>450</v>
       </c>
       <c r="K61" s="8">
         <v>470</v>
       </c>
       <c r="L61" s="8">
-        <f>K61+20</f>
+        <f t="shared" si="23"/>
         <v>490</v>
       </c>
       <c r="M61" s="8">
-        <f>L61+10</f>
+        <f t="shared" si="24"/>
         <v>500</v>
       </c>
       <c r="N61" s="8">
@@ -8890,11 +8879,11 @@
         <v>520</v>
       </c>
       <c r="O61" s="8">
-        <f>N61+20</f>
+        <f t="shared" si="26"/>
         <v>540</v>
       </c>
       <c r="P61" s="8">
-        <f>O61-10</f>
+        <f t="shared" si="27"/>
         <v>530</v>
       </c>
       <c r="Q61" s="8" t="s">
@@ -8905,8 +8894,8 @@
       <c r="B62" s="13" t="s">
         <v>158</v>
       </c>
-      <c r="C62" s="8">
-        <v>410</v>
+      <c r="C62" s="8" t="s">
+        <v>158</v>
       </c>
       <c r="D62" s="8">
         <v>430</v>
@@ -8915,33 +8904,33 @@
         <v>450</v>
       </c>
       <c r="F62" s="8">
-        <f>E62+20</f>
+        <f t="shared" si="28"/>
         <v>470</v>
       </c>
       <c r="G62" s="8">
-        <f>F62+20</f>
+        <f t="shared" si="29"/>
         <v>490</v>
       </c>
       <c r="H62" s="8">
         <v>450</v>
       </c>
       <c r="I62" s="8">
-        <f>H62-10</f>
+        <f t="shared" si="30"/>
         <v>440</v>
       </c>
       <c r="J62" s="8">
-        <f>I62-10</f>
+        <f t="shared" si="31"/>
         <v>430</v>
       </c>
       <c r="K62" s="15">
         <v>440</v>
       </c>
       <c r="L62" s="14">
-        <f>K62+20</f>
+        <f t="shared" si="23"/>
         <v>460</v>
       </c>
       <c r="M62" s="8">
-        <f>L62+10</f>
+        <f t="shared" si="24"/>
         <v>470</v>
       </c>
       <c r="N62" s="8">
@@ -8949,11 +8938,11 @@
         <v>490</v>
       </c>
       <c r="O62" s="8">
-        <f>N62+20</f>
+        <f t="shared" si="26"/>
         <v>510</v>
       </c>
       <c r="P62" s="8">
-        <f>O62-10</f>
+        <f t="shared" si="27"/>
         <v>500</v>
       </c>
       <c r="Q62" s="15" t="s">
@@ -8964,8 +8953,8 @@
       <c r="B63" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="C63" s="8">
-        <v>435</v>
+      <c r="C63" s="8" t="s">
+        <v>29</v>
       </c>
       <c r="D63" s="8">
         <v>455</v>
@@ -8974,33 +8963,33 @@
         <v>475</v>
       </c>
       <c r="F63" s="8">
-        <f>E63+20</f>
+        <f t="shared" si="28"/>
         <v>495</v>
       </c>
       <c r="G63" s="8">
-        <f>F63+20</f>
+        <f t="shared" si="29"/>
         <v>515</v>
       </c>
       <c r="H63" s="8">
         <v>475</v>
       </c>
       <c r="I63" s="8">
-        <f>H63-10</f>
+        <f t="shared" si="30"/>
         <v>465</v>
       </c>
       <c r="J63" s="8">
-        <f>I63-10</f>
+        <f t="shared" si="31"/>
         <v>455</v>
       </c>
       <c r="K63" s="8">
         <v>465</v>
       </c>
       <c r="L63" s="8">
-        <f>K63+20</f>
+        <f t="shared" si="23"/>
         <v>485</v>
       </c>
       <c r="M63" s="8">
-        <f>L63+10</f>
+        <f t="shared" si="24"/>
         <v>495</v>
       </c>
       <c r="N63" s="8">
@@ -9008,11 +8997,11 @@
         <v>515</v>
       </c>
       <c r="O63" s="8">
-        <f>N63+20</f>
+        <f t="shared" si="26"/>
         <v>535</v>
       </c>
       <c r="P63" s="8">
-        <f>O63-10</f>
+        <f t="shared" si="27"/>
         <v>525</v>
       </c>
       <c r="Q63" s="8" t="s">
@@ -9030,8 +9019,8 @@
       <c r="B65" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="C65" s="8">
-        <v>440</v>
+      <c r="C65" s="8" t="s">
+        <v>160</v>
       </c>
       <c r="D65" s="11">
         <v>460</v>
@@ -9058,22 +9047,22 @@
         <v>470</v>
       </c>
       <c r="L65" s="8">
-        <f>K65+20</f>
+        <f t="shared" ref="L65:L73" si="32">K65+20</f>
         <v>490</v>
       </c>
       <c r="M65" s="8">
-        <f>L65+10</f>
+        <f t="shared" ref="M65:M73" si="33">L65+10</f>
         <v>500</v>
       </c>
       <c r="N65" s="8">
-        <f>M65+20</f>
+        <f t="shared" ref="N65:N73" si="34">M65+20</f>
         <v>520</v>
       </c>
       <c r="O65" s="8">
         <v>540</v>
       </c>
       <c r="P65" s="8">
-        <f>O65-10</f>
+        <f t="shared" ref="P65:P73" si="35">O65-10</f>
         <v>530</v>
       </c>
       <c r="Q65" s="8" t="s">
@@ -9084,8 +9073,8 @@
       <c r="B66" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="C66" s="8">
-        <v>440</v>
+      <c r="C66" s="8" t="s">
+        <v>84</v>
       </c>
       <c r="D66" s="11">
         <v>460</v>
@@ -9112,22 +9101,22 @@
         <v>470</v>
       </c>
       <c r="L66" s="8">
-        <f>K66+20</f>
+        <f t="shared" si="32"/>
         <v>490</v>
       </c>
       <c r="M66" s="8">
-        <f>L66+10</f>
+        <f t="shared" si="33"/>
         <v>500</v>
       </c>
       <c r="N66" s="8">
-        <f>M66+20</f>
+        <f t="shared" si="34"/>
         <v>520</v>
       </c>
       <c r="O66" s="8">
         <v>540</v>
       </c>
       <c r="P66" s="8">
-        <f>O66-10</f>
+        <f t="shared" si="35"/>
         <v>530</v>
       </c>
       <c r="Q66" s="8" t="s">
@@ -9138,8 +9127,8 @@
       <c r="B67" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="C67" s="8">
-        <v>430</v>
+      <c r="C67" s="8" t="s">
+        <v>78</v>
       </c>
       <c r="D67" s="11">
         <v>450</v>
@@ -9166,22 +9155,22 @@
         <v>460</v>
       </c>
       <c r="L67" s="8">
-        <f>K67+20</f>
+        <f t="shared" si="32"/>
         <v>480</v>
       </c>
       <c r="M67" s="8">
-        <f>L67+10</f>
+        <f t="shared" si="33"/>
         <v>490</v>
       </c>
       <c r="N67" s="8">
-        <f>M67+20</f>
+        <f t="shared" si="34"/>
         <v>510</v>
       </c>
       <c r="O67" s="8">
         <v>530</v>
       </c>
       <c r="P67" s="8">
-        <f>O67-10</f>
+        <f t="shared" si="35"/>
         <v>520</v>
       </c>
       <c r="Q67" s="8" t="s">
@@ -9192,8 +9181,8 @@
       <c r="B68" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="C68" s="8">
-        <v>440</v>
+      <c r="C68" s="8" t="s">
+        <v>80</v>
       </c>
       <c r="D68" s="8">
         <v>460</v>
@@ -9220,22 +9209,22 @@
         <v>470</v>
       </c>
       <c r="L68" s="8">
-        <f>K68+20</f>
+        <f t="shared" si="32"/>
         <v>490</v>
       </c>
       <c r="M68" s="8">
-        <f>L68+10</f>
+        <f t="shared" si="33"/>
         <v>500</v>
       </c>
       <c r="N68" s="8">
-        <f>M68+20</f>
+        <f t="shared" si="34"/>
         <v>520</v>
       </c>
       <c r="O68" s="8">
         <v>540</v>
       </c>
       <c r="P68" s="8">
-        <f>O68-10</f>
+        <f t="shared" si="35"/>
         <v>530</v>
       </c>
       <c r="Q68" s="8" t="s">
@@ -9246,8 +9235,8 @@
       <c r="B69" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="C69" s="8">
-        <v>430</v>
+      <c r="C69" s="8" t="s">
+        <v>161</v>
       </c>
       <c r="D69" s="8">
         <v>460</v>
@@ -9274,22 +9263,22 @@
         <v>480</v>
       </c>
       <c r="L69" s="8">
-        <f>K69+20</f>
+        <f t="shared" si="32"/>
         <v>500</v>
       </c>
       <c r="M69" s="8">
-        <f>L69+10</f>
+        <f t="shared" si="33"/>
         <v>510</v>
       </c>
       <c r="N69" s="8">
-        <f>M69+20</f>
+        <f t="shared" si="34"/>
         <v>530</v>
       </c>
       <c r="O69" s="8">
         <v>550</v>
       </c>
       <c r="P69" s="8">
-        <f>O69-10</f>
+        <f t="shared" si="35"/>
         <v>540</v>
       </c>
       <c r="Q69" s="8" t="s">
@@ -9300,6 +9289,9 @@
       <c r="B70" s="7" t="s">
         <v>162</v>
       </c>
+      <c r="C70" s="8" t="s">
+        <v>162</v>
+      </c>
       <c r="E70" s="8">
         <v>490</v>
       </c>
@@ -9322,22 +9314,22 @@
         <v>480</v>
       </c>
       <c r="L70" s="8">
-        <f>K70+20</f>
+        <f t="shared" si="32"/>
         <v>500</v>
       </c>
       <c r="M70" s="8">
-        <f>L70+10</f>
+        <f t="shared" si="33"/>
         <v>510</v>
       </c>
       <c r="N70" s="8">
-        <f>M70+20</f>
+        <f t="shared" si="34"/>
         <v>530</v>
       </c>
       <c r="O70" s="8">
         <v>550</v>
       </c>
       <c r="P70" s="8">
-        <f>O70-10</f>
+        <f t="shared" si="35"/>
         <v>540</v>
       </c>
       <c r="Q70" s="8" t="s">
@@ -9348,6 +9340,9 @@
       <c r="B71" s="7" t="s">
         <v>85</v>
       </c>
+      <c r="C71" s="8" t="s">
+        <v>85</v>
+      </c>
       <c r="E71" s="8">
         <v>450</v>
       </c>
@@ -9370,22 +9365,22 @@
         <v>450</v>
       </c>
       <c r="L71" s="8">
-        <f>K71+20</f>
+        <f t="shared" si="32"/>
         <v>470</v>
       </c>
       <c r="M71" s="8">
-        <f>L71+10</f>
+        <f t="shared" si="33"/>
         <v>480</v>
       </c>
       <c r="N71" s="8">
-        <f>M71+20</f>
+        <f t="shared" si="34"/>
         <v>500</v>
       </c>
       <c r="O71" s="8">
         <v>520</v>
       </c>
       <c r="P71" s="8">
-        <f>O71-10</f>
+        <f t="shared" si="35"/>
         <v>510</v>
       </c>
       <c r="Q71" s="8" t="s">
@@ -9396,8 +9391,11 @@
       <c r="B72" s="7" t="s">
         <v>163</v>
       </c>
+      <c r="C72" s="8" t="s">
+        <v>164</v>
+      </c>
       <c r="F72" s="8" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I72" s="8">
         <v>470</v>
@@ -9409,49 +9407,52 @@
         <v>470</v>
       </c>
       <c r="L72" s="8">
-        <f>K72+20</f>
+        <f t="shared" si="32"/>
         <v>490</v>
       </c>
       <c r="M72" s="8">
-        <f>L72+10</f>
+        <f t="shared" si="33"/>
         <v>500</v>
       </c>
       <c r="N72" s="8">
-        <f>M72+20</f>
+        <f t="shared" si="34"/>
         <v>520</v>
       </c>
       <c r="O72" s="8">
         <v>540</v>
       </c>
       <c r="P72" s="8">
-        <f>O72-10</f>
+        <f t="shared" si="35"/>
         <v>530</v>
       </c>
       <c r="Q72" s="8" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="73" spans="2:17">
+      <c r="C73" s="8" t="s">
+        <v>77</v>
+      </c>
       <c r="K73" s="8">
         <v>460</v>
       </c>
       <c r="L73" s="8">
-        <f>K73+20</f>
+        <f t="shared" si="32"/>
         <v>480</v>
       </c>
       <c r="M73" s="8">
-        <f>L73+10</f>
+        <f t="shared" si="33"/>
         <v>490</v>
       </c>
       <c r="N73" s="8">
-        <f>M73+20</f>
+        <f t="shared" si="34"/>
         <v>510</v>
       </c>
       <c r="O73" s="8">
         <v>530</v>
       </c>
       <c r="P73" s="8">
-        <f>O73-10</f>
+        <f t="shared" si="35"/>
         <v>520</v>
       </c>
       <c r="Q73" s="8" t="s">
@@ -9459,6 +9460,9 @@
       </c>
     </row>
     <row r="74" spans="2:17">
+      <c r="C74" s="8" t="s">
+        <v>76</v>
+      </c>
       <c r="Q74" s="8" t="s">
         <v>76</v>
       </c>

--- a/11.xlsx
+++ b/11.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11655" firstSheet="2"/>
+    <workbookView windowWidth="28800" windowHeight="11655" firstSheet="2" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -346,7 +346,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="154">
   <si>
     <t>客户名称</t>
   </si>
@@ -763,9 +763,6 @@
   </si>
   <si>
     <t>DWN</t>
-  </si>
-  <si>
-    <t>客户编码</t>
   </si>
   <si>
     <t>日期</t>
@@ -1605,19 +1602,19 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -9492,320 +9489,287 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:G14"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
+  <dimension ref="A1:F14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="10.875" customWidth="1"/>
-    <col min="2" max="2" width="19" customWidth="1"/>
-    <col min="3" max="4" width="8.875" customWidth="1"/>
-    <col min="5" max="5" width="12.75" customWidth="1"/>
-    <col min="6" max="6" width="11.5" customWidth="1"/>
-    <col min="7" max="7" width="11.5" style="1" customWidth="1"/>
+    <col min="1" max="1" width="19" customWidth="1"/>
+    <col min="2" max="3" width="8.875" customWidth="1"/>
+    <col min="4" max="4" width="12.75" customWidth="1"/>
+    <col min="5" max="5" width="11.5" customWidth="1"/>
+    <col min="6" max="6" width="11.5" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" spans="1:7">
+    <row r="1" ht="15" spans="1:6">
       <c r="A1" s="2" t="s">
         <v>139</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="4" t="s">
         <v>143</v>
       </c>
       <c r="F1" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="G1" s="4" t="s">
+    </row>
+    <row r="2" ht="16.5" spans="1:6">
+      <c r="A2" s="5">
+        <v>46161</v>
+      </c>
+      <c r="B2" s="6" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="2" ht="16.5" spans="1:7">
-      <c r="A2" s="5">
+      <c r="C2" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D2" s="7">
         <v>196</v>
       </c>
-      <c r="B2" s="6">
+      <c r="E2" s="8">
+        <v>15521645</v>
+      </c>
+      <c r="F2" s="8">
+        <v>510000</v>
+      </c>
+    </row>
+    <row r="3" ht="16.5" spans="1:6">
+      <c r="A3" s="5">
         <v>46161</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="B3" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="D3" s="7">
+        <v>198</v>
+      </c>
+      <c r="E3" s="8">
+        <v>58752000</v>
+      </c>
+      <c r="F3" s="8">
+        <v>510000</v>
+      </c>
+    </row>
+    <row r="4" ht="16.5" spans="1:6">
+      <c r="A4" s="5">
+        <v>46161</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="D4" s="7">
+        <v>192</v>
+      </c>
+      <c r="E4" s="8">
+        <v>100000000</v>
+      </c>
+      <c r="F4" s="8">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="5" ht="16.5" spans="1:6">
+      <c r="A5" s="5">
+        <v>46161</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="D2" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="E2" s="5">
-        <v>196</v>
-      </c>
-      <c r="F2" s="8">
-        <v>15521645</v>
-      </c>
-      <c r="G2" s="8">
+      <c r="C5" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="D5" s="7">
+        <v>36</v>
+      </c>
+      <c r="E5" s="8">
+        <v>5832000</v>
+      </c>
+      <c r="F5" s="8">
+        <v>540000</v>
+      </c>
+    </row>
+    <row r="6" ht="16.5" spans="1:6">
+      <c r="A6" s="5">
+        <v>46161</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D6" s="7">
+        <v>195</v>
+      </c>
+      <c r="E6" s="8">
+        <v>57000000</v>
+      </c>
+      <c r="F6" s="8">
+        <v>520000</v>
+      </c>
+    </row>
+    <row r="7" ht="16.5" spans="1:6">
+      <c r="A7" s="5">
+        <v>46161</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D7" s="7">
+        <v>195</v>
+      </c>
+      <c r="E7" s="8">
+        <v>150000000</v>
+      </c>
+      <c r="F7" s="8">
+        <v>520000</v>
+      </c>
+    </row>
+    <row r="8" ht="16.5" spans="1:6">
+      <c r="A8" s="5">
+        <v>46161</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8" s="7">
+        <v>63</v>
+      </c>
+      <c r="E8" s="8">
+        <v>50000000</v>
+      </c>
+      <c r="F8" s="8">
+        <v>530000</v>
+      </c>
+    </row>
+    <row r="9" ht="16.5" spans="1:6">
+      <c r="A9" s="5">
+        <v>46161</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" s="7">
+        <v>187</v>
+      </c>
+      <c r="E9" s="8">
+        <v>6741000</v>
+      </c>
+      <c r="F9" s="8">
+        <v>535000</v>
+      </c>
+    </row>
+    <row r="10" ht="16.5" spans="1:6">
+      <c r="A10" s="5">
+        <v>46161</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="D10" s="7">
+        <v>150</v>
+      </c>
+      <c r="E10" s="8">
+        <v>150000000</v>
+      </c>
+      <c r="F10" s="8">
         <v>510000</v>
       </c>
     </row>
-    <row r="3" ht="16.5" spans="1:7">
-      <c r="A3" s="5">
-        <v>198</v>
-      </c>
-      <c r="B3" s="6">
+    <row r="11" ht="16.5" spans="1:6">
+      <c r="A11" s="5">
         <v>46161</v>
       </c>
-      <c r="C3" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="E3" s="5">
-        <v>198</v>
-      </c>
-      <c r="F3" s="8">
-        <v>58752000</v>
-      </c>
-      <c r="G3" s="8">
-        <v>510000</v>
-      </c>
-    </row>
-    <row r="4" ht="16.5" spans="1:7">
-      <c r="A4" s="5">
-        <v>192</v>
-      </c>
-      <c r="B4" s="6">
+      <c r="B11" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D11" s="7">
+        <v>65</v>
+      </c>
+      <c r="E11" s="8">
+        <v>5616000</v>
+      </c>
+      <c r="F11" s="8"/>
+    </row>
+    <row r="12" ht="16.5" spans="1:6">
+      <c r="A12" s="5">
         <v>46161</v>
       </c>
-      <c r="C4" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="E4" s="5">
-        <v>192</v>
-      </c>
-      <c r="F4" s="8">
-        <v>100000000</v>
-      </c>
-      <c r="G4" s="8">
-        <v>500000</v>
-      </c>
-    </row>
-    <row r="5" ht="16.5" spans="1:7">
-      <c r="A5" s="5">
-        <v>36</v>
-      </c>
-      <c r="B5" s="6">
+      <c r="B12" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="D12" s="7">
+        <v>65</v>
+      </c>
+      <c r="E12" s="8">
+        <v>5616000</v>
+      </c>
+      <c r="F12" s="8"/>
+    </row>
+    <row r="13" ht="16.5" spans="1:6">
+      <c r="A13" s="5">
         <v>46161</v>
       </c>
-      <c r="C5" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="E5" s="5">
-        <v>36</v>
-      </c>
-      <c r="F5" s="8">
-        <v>5832000</v>
-      </c>
-      <c r="G5" s="8">
-        <v>540000</v>
-      </c>
-    </row>
-    <row r="6" ht="16.5" spans="1:7">
-      <c r="A6" s="5">
-        <v>195</v>
-      </c>
-      <c r="B6" s="6">
+      <c r="B13" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="D13" s="7">
+        <v>65</v>
+      </c>
+      <c r="E13" s="8">
+        <v>5616000</v>
+      </c>
+      <c r="F13" s="8"/>
+    </row>
+    <row r="14" ht="16.5" spans="1:6">
+      <c r="A14" s="5">
         <v>46161</v>
       </c>
-      <c r="C6" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="E6" s="5">
-        <v>195</v>
-      </c>
-      <c r="F6" s="8">
-        <v>57000000</v>
-      </c>
-      <c r="G6" s="8">
-        <v>520000</v>
-      </c>
-    </row>
-    <row r="7" ht="16.5" spans="1:7">
-      <c r="A7" s="5">
-        <v>195</v>
-      </c>
-      <c r="B7" s="6">
-        <v>46161</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="E7" s="5">
-        <v>195</v>
-      </c>
-      <c r="F7" s="8">
-        <v>150000000</v>
-      </c>
-      <c r="G7" s="8">
-        <v>520000</v>
-      </c>
-    </row>
-    <row r="8" ht="16.5" spans="1:7">
-      <c r="A8" s="5">
-        <v>63</v>
-      </c>
-      <c r="B8" s="6">
-        <v>46161</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="E8" s="5">
-        <v>63</v>
-      </c>
-      <c r="F8" s="8">
-        <v>50000000</v>
-      </c>
-      <c r="G8" s="8">
-        <v>530000</v>
-      </c>
-    </row>
-    <row r="9" ht="16.5" spans="1:7">
-      <c r="A9" s="5">
-        <v>187</v>
-      </c>
-      <c r="B9" s="6">
-        <v>46161</v>
-      </c>
-      <c r="C9" s="7" t="s">
+      <c r="B14" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="D9" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="E9" s="5">
-        <v>187</v>
-      </c>
-      <c r="F9" s="8">
-        <v>6741000</v>
-      </c>
-      <c r="G9" s="8">
-        <v>535000</v>
-      </c>
-    </row>
-    <row r="10" ht="16.5" spans="1:7">
-      <c r="A10" s="5"/>
-      <c r="B10" s="6">
-        <v>46161</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>150</v>
-      </c>
-      <c r="D10" s="7" t="s">
+      <c r="C14" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="D14" s="7">
         <v>65</v>
       </c>
-      <c r="E10" s="5">
-        <v>150</v>
-      </c>
-      <c r="F10" s="8">
-        <v>150000000</v>
-      </c>
-      <c r="G10" s="8">
-        <v>510000</v>
-      </c>
-    </row>
-    <row r="11" ht="16.5" spans="1:7">
-      <c r="A11" s="5"/>
-      <c r="B11" s="6">
-        <v>46161</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>150</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="E11" s="5">
-        <v>65</v>
-      </c>
-      <c r="F11" s="8">
-        <v>5616000</v>
-      </c>
-      <c r="G11" s="8"/>
-    </row>
-    <row r="12" ht="16.5" spans="1:7">
-      <c r="A12" s="5"/>
-      <c r="B12" s="6">
-        <v>46161</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>150</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="E12" s="5">
-        <v>65</v>
-      </c>
-      <c r="F12" s="8">
-        <v>5616000</v>
-      </c>
-      <c r="G12" s="8"/>
-    </row>
-    <row r="13" ht="16.5" spans="1:7">
-      <c r="A13" s="5"/>
-      <c r="B13" s="6">
-        <v>46161</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>150</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>153</v>
-      </c>
-      <c r="E13" s="5">
-        <v>65</v>
-      </c>
-      <c r="F13" s="8">
-        <v>5616000</v>
-      </c>
-      <c r="G13" s="8"/>
-    </row>
-    <row r="14" ht="16.5" spans="1:7">
-      <c r="A14" s="5"/>
-      <c r="B14" s="6">
-        <v>46161</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>150</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="E14" s="5">
-        <v>65</v>
-      </c>
-      <c r="F14" s="8">
+      <c r="E14" s="8">
         <v>7371000</v>
       </c>
-      <c r="G14" s="8"/>
+      <c r="F14" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
